--- a/database/event/4162/event_4162_evp_summary.xlsx
+++ b/database/event/4162/event_4162_evp_summary.xlsx
@@ -496,25 +496,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5656</v>
+        <v>7.5527</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0708</v>
+        <v>1.0689</v>
       </c>
       <c r="D2" t="n">
-        <v>2.635</v>
+        <v>2.5651</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5656</v>
+        <v>7.5527</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7428</v>
+        <v>1.7299</v>
       </c>
       <c r="G2" t="n">
         <v>5.8228</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7428</v>
+        <v>1.7299</v>
       </c>
       <c r="I2" t="n">
         <v>1.7591</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4059</v>
+        <v>5.3657</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7651</v>
+        <v>0.7594</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7625</v>
+        <v>1.6938</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4059</v>
+        <v>5.3657</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7137</v>
+        <v>2.6735</v>
       </c>
       <c r="G3" t="n">
         <v>2.6922</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7137</v>
+        <v>2.6735</v>
       </c>
       <c r="I3" t="n">
         <v>2.7646</v>
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2963</v>
+        <v>5.2834</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7496</v>
+        <v>0.7478</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7182</v>
+        <v>1.661</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2963</v>
+        <v>5.2834</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7326</v>
+        <v>1.7197</v>
       </c>
       <c r="G4" t="n">
         <v>3.5637</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7326</v>
+        <v>1.7197</v>
       </c>
       <c r="I4" t="n">
         <v>1.7487</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6784</v>
+        <v>4.6741</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6621</v>
+        <v>0.6615</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4686</v>
+        <v>1.4183</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6784</v>
+        <v>4.6741</v>
       </c>
       <c r="F5" t="n">
-        <v>1.155</v>
+        <v>1.1507</v>
       </c>
       <c r="G5" t="n">
         <v>3.5234</v>
       </c>
       <c r="H5" t="n">
-        <v>1.155</v>
+        <v>1.1507</v>
       </c>
       <c r="I5" t="n">
         <v>1.1604</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6774</v>
+        <v>4.665</v>
       </c>
       <c r="C6" t="n">
-        <v>0.662</v>
+        <v>0.6602</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4682</v>
+        <v>1.4146</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6774</v>
+        <v>4.665</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6702</v>
+        <v>1.6578</v>
       </c>
       <c r="G6" t="n">
         <v>3.0072</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6702</v>
+        <v>1.6578</v>
       </c>
       <c r="I6" t="n">
         <v>1.6858</v>
@@ -726,25 +726,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2185</v>
+        <v>4.1693</v>
       </c>
       <c r="C7" t="n">
-        <v>0.597</v>
+        <v>0.5901</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2828</v>
+        <v>1.2171</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2185</v>
+        <v>4.1693</v>
       </c>
       <c r="F7" t="n">
-        <v>3.3177</v>
+        <v>3.2685</v>
       </c>
       <c r="G7" t="n">
         <v>0.9008</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3177</v>
+        <v>3.2685</v>
       </c>
       <c r="I7" t="n">
         <v>3.3799</v>
@@ -778,7 +778,7 @@
         <v>0.5731000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2144</v>
+        <v>1.1693</v>
       </c>
       <c r="E8" t="n">
         <v>4.0491</v>
@@ -818,25 +818,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.9037</v>
+        <v>3.8907</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5525</v>
+        <v>0.5506</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1556</v>
+        <v>1.1061</v>
       </c>
       <c r="E9" t="n">
-        <v>3.9037</v>
+        <v>3.8907</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7479</v>
+        <v>1.7349</v>
       </c>
       <c r="G9" t="n">
         <v>2.1558</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7479</v>
+        <v>1.7349</v>
       </c>
       <c r="I9" t="n">
         <v>1.7642</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.707</v>
+        <v>3.7076</v>
       </c>
       <c r="C10" t="n">
         <v>0.5247000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0762</v>
+        <v>1.0332</v>
       </c>
       <c r="E10" t="n">
-        <v>3.707</v>
+        <v>3.7076</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0911</v>
+        <v>-0.0905</v>
       </c>
       <c r="G10" t="n">
         <v>3.7981</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0911</v>
+        <v>-0.0905</v>
       </c>
       <c r="I10" t="n">
         <v>-0.092</v>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.337</v>
+        <v>3.3262</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4723</v>
+        <v>0.4708</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9267</v>
+        <v>0.8812</v>
       </c>
       <c r="E11" t="n">
-        <v>3.337</v>
+        <v>3.3262</v>
       </c>
       <c r="F11" t="n">
-        <v>1.453</v>
+        <v>1.4422</v>
       </c>
       <c r="G11" t="n">
         <v>1.884</v>
       </c>
       <c r="H11" t="n">
-        <v>1.453</v>
+        <v>1.4422</v>
       </c>
       <c r="I11" t="n">
         <v>1.4666</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5512</v>
+        <v>2.5332</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3611</v>
+        <v>0.3585</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6093</v>
+        <v>0.5653</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5512</v>
+        <v>2.5332</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2161</v>
+        <v>1.1981</v>
       </c>
       <c r="G12" t="n">
         <v>1.3351</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2161</v>
+        <v>1.1981</v>
       </c>
       <c r="I12" t="n">
         <v>1.2389</v>
@@ -1008,7 +1008,7 @@
         <v>0.3437</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5598</v>
+        <v>0.5237000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>2.4288</v>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0642</v>
+        <v>2.0463</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2921</v>
+        <v>0.2896</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4125</v>
+        <v>0.3713</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0642</v>
+        <v>2.0463</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2062</v>
+        <v>1.1883</v>
       </c>
       <c r="G14" t="n">
         <v>0.858</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2062</v>
+        <v>1.1883</v>
       </c>
       <c r="I14" t="n">
         <v>1.2288</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6712</v>
+        <v>1.6662</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2365</v>
+        <v>0.2358</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2538</v>
+        <v>0.2199</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6712</v>
+        <v>1.6662</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3444</v>
+        <v>1.3394</v>
       </c>
       <c r="G15" t="n">
         <v>0.3268</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3444</v>
+        <v>1.3394</v>
       </c>
       <c r="I15" t="n">
         <v>1.3507</v>
@@ -1140,25 +1140,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1414</v>
+        <v>1.1465</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1615</v>
+        <v>0.1623</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0397</v>
+        <v>0.0129</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1414</v>
+        <v>1.1465</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3575</v>
+        <v>-1.3524</v>
       </c>
       <c r="G16" t="n">
         <v>2.4989</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3575</v>
+        <v>-1.3524</v>
       </c>
       <c r="I16" t="n">
         <v>-1.3638</v>
@@ -1192,7 +1192,7 @@
         <v>0.1524</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0137</v>
+        <v>-0.0148</v>
       </c>
       <c r="E17" t="n">
         <v>1.077</v>
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8761</v>
+        <v>0.8683</v>
       </c>
       <c r="C18" t="n">
-        <v>0.124</v>
+        <v>0.1229</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0674</v>
+        <v>-0.098</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8761</v>
+        <v>0.8683</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0462</v>
+        <v>1.0384</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1701</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0462</v>
+        <v>1.0384</v>
       </c>
       <c r="I18" t="n">
         <v>1.056</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7821</v>
+        <v>0.7788</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1107</v>
+        <v>0.1102</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1054</v>
+        <v>-0.1336</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7821</v>
+        <v>0.7788</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4497</v>
+        <v>0.4464</v>
       </c>
       <c r="G19" t="n">
         <v>0.3324</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4497</v>
+        <v>0.4464</v>
       </c>
       <c r="I19" t="n">
         <v>0.4539</v>
@@ -1324,25 +1324,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0832</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1837</v>
+        <v>-0.21</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2902</v>
+        <v>0.2892</v>
       </c>
       <c r="G20" t="n">
         <v>0.298</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2902</v>
+        <v>0.2892</v>
       </c>
       <c r="I20" t="n">
         <v>0.2916</v>
@@ -1370,25 +1370,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4318</v>
+        <v>0.443</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0611</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2469</v>
+        <v>-0.2674</v>
       </c>
       <c r="E21" t="n">
-        <v>0.4318</v>
+        <v>0.443</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5055</v>
+        <v>-1.4942</v>
       </c>
       <c r="G21" t="n">
         <v>1.9373</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.5055</v>
+        <v>-1.4942</v>
       </c>
       <c r="I21" t="n">
         <v>-1.5195</v>
@@ -1422,7 +1422,7 @@
         <v>0.0156</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3768</v>
+        <v>-0.4</v>
       </c>
       <c r="E22" t="n">
         <v>0.1103</v>
@@ -1468,7 +1468,7 @@
         <v>0.0078</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3992</v>
+        <v>-0.422</v>
       </c>
       <c r="E23" t="n">
         <v>0.0549</v>
@@ -1514,7 +1514,7 @@
         <v>0.0041</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4095</v>
+        <v>-0.4322</v>
       </c>
       <c r="E24" t="n">
         <v>0.0293</v>
@@ -1560,7 +1560,7 @@
         <v>0.0001</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4212</v>
+        <v>-0.4437</v>
       </c>
       <c r="E25" t="n">
         <v>0.0005</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1474</v>
+        <v>-0.1579</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0209</v>
+        <v>-0.0223</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4809</v>
+        <v>-0.5068</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1474</v>
+        <v>-0.1579</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4122</v>
+        <v>1.4017</v>
       </c>
       <c r="G26" t="n">
         <v>-1.5596</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4122</v>
+        <v>1.4017</v>
       </c>
       <c r="I26" t="n">
         <v>1.4254</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3817</v>
+        <v>-0.3777</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.054</v>
+        <v>-0.0535</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5756</v>
+        <v>-0.5944</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3817</v>
+        <v>-0.3777</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0631</v>
+        <v>-1.0591</v>
       </c>
       <c r="G27" t="n">
         <v>0.6814</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0631</v>
+        <v>-1.0591</v>
       </c>
       <c r="I27" t="n">
         <v>-1.068</v>
@@ -1692,25 +1692,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4682</v>
+        <v>-0.4674</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0663</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6105</v>
+        <v>-0.6301</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4682</v>
+        <v>-0.4674</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.2288</v>
+        <v>-0.228</v>
       </c>
       <c r="G28" t="n">
         <v>-0.2394</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.2288</v>
+        <v>-0.228</v>
       </c>
       <c r="I28" t="n">
         <v>-0.2299</v>
@@ -1738,25 +1738,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4893</v>
+        <v>-0.4829</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0693</v>
+        <v>-0.0683</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.619</v>
+        <v>-0.6363</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4893</v>
+        <v>-0.4829</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4352</v>
+        <v>-0.4288</v>
       </c>
       <c r="G29" t="n">
         <v>-0.0541</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4352</v>
+        <v>-0.4288</v>
       </c>
       <c r="I29" t="n">
         <v>-0.4434</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4921</v>
+        <v>-0.494</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0696</v>
+        <v>-0.0699</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6202</v>
+        <v>-0.6407</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4921</v>
+        <v>-0.494</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2511</v>
+        <v>0.2492</v>
       </c>
       <c r="G30" t="n">
         <v>-0.7432</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2511</v>
+        <v>0.2492</v>
       </c>
       <c r="I30" t="n">
         <v>0.2534</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.5827</v>
+        <v>-0.587</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0825</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6778</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.5827</v>
+        <v>-0.587</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5796</v>
+        <v>0.5753</v>
       </c>
       <c r="G31" t="n">
         <v>-1.1623</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5796</v>
+        <v>0.5753</v>
       </c>
       <c r="I31" t="n">
         <v>0.585</v>
@@ -1876,25 +1876,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8587</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="C32" t="n">
         <v>-0.1215</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7683</v>
+        <v>-0.7859</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8587</v>
+        <v>-0.8584000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0707</v>
+        <v>-0.0704</v>
       </c>
       <c r="G32" t="n">
         <v>-0.788</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0707</v>
+        <v>-0.0704</v>
       </c>
       <c r="I32" t="n">
         <v>-0.07099999999999999</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8849</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1252</v>
+        <v>-0.1242</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7788</v>
+        <v>-0.7935</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8849</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="G33" t="n">
         <v>1.1058</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.9907</v>
+        <v>-1.9833</v>
       </c>
       <c r="I33" t="n">
         <v>-2</v>
@@ -1968,25 +1968,25 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9304</v>
+        <v>-0.9307</v>
       </c>
       <c r="C34" t="n">
         <v>-0.1317</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7972</v>
+        <v>-0.8147</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9304</v>
+        <v>-0.9307</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0696</v>
+        <v>0.0693</v>
       </c>
       <c r="G34" t="n">
         <v>-1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0696</v>
+        <v>0.0693</v>
       </c>
       <c r="I34" t="n">
         <v>0.0699</v>
@@ -2014,25 +2014,25 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.0628</v>
+        <v>-1.061</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1504</v>
+        <v>-0.1502</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8507</v>
+        <v>-0.8666</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.0628</v>
+        <v>-1.061</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2357</v>
+        <v>-0.2339</v>
       </c>
       <c r="G35" t="n">
         <v>-0.8270999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2357</v>
+        <v>-0.2339</v>
       </c>
       <c r="I35" t="n">
         <v>-0.2379</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1523</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8561</v>
+        <v>-0.8726</v>
       </c>
       <c r="E36" t="n">
         <v>-1.0761</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1709</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9092</v>
+        <v>-0.9251</v>
       </c>
       <c r="E37" t="n">
         <v>-1.2077</v>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3015</v>
+        <v>-1.2945</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1842</v>
+        <v>-0.1832</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9471000000000001</v>
+        <v>-0.9596</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3015</v>
+        <v>-1.2945</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8682</v>
+        <v>-1.8612</v>
       </c>
       <c r="G38" t="n">
         <v>0.5667</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8682</v>
+        <v>-1.8612</v>
       </c>
       <c r="I38" t="n">
         <v>-1.8769</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.3141</v>
+        <v>-1.303</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.186</v>
+        <v>-0.1844</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9522</v>
+        <v>-0.963</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.3141</v>
+        <v>-1.303</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4885</v>
+        <v>-1.4774</v>
       </c>
       <c r="G39" t="n">
         <v>0.1744</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4885</v>
+        <v>-1.4774</v>
       </c>
       <c r="I39" t="n">
         <v>-1.5024</v>
@@ -2250,7 +2250,7 @@
         <v>-0.2546</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1482</v>
+        <v>-1.1607</v>
       </c>
       <c r="E40" t="n">
         <v>-1.7991</v>
@@ -2290,25 +2290,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3807</v>
+        <v>-2.3784</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3369</v>
+        <v>-0.3366</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3831</v>
+        <v>-1.3915</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3807</v>
+        <v>-2.3784</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3121</v>
+        <v>-0.3098</v>
       </c>
       <c r="G41" t="n">
         <v>-2.0686</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3121</v>
+        <v>-0.3098</v>
       </c>
       <c r="I41" t="n">
         <v>-0.315</v>

--- a/database/event/4162/event_4162_evp_summary.xlsx
+++ b/database/event/4162/event_4162_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5527</v>
+        <v>7.2112</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0689</v>
+        <v>1.0206</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5651</v>
+        <v>2.6175</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5527</v>
+        <v>7.2112</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7299</v>
+        <v>2.3078</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8228</v>
+        <v>4.9034</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7299</v>
+        <v>2.3078</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7591</v>
+        <v>2.5015</v>
       </c>
       <c r="J2" t="n">
-        <v>5.8228</v>
+        <v>4.9034</v>
       </c>
       <c r="K2" t="n">
         <v>66</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.5819</v>
+        <v>7.4049</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -538,311 +538,311 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cajunb</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3657</v>
+        <v>5.4352</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7594</v>
+        <v>0.7692</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6938</v>
+        <v>1.8157</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3657</v>
+        <v>5.4352</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6735</v>
+        <v>2.2035</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6922</v>
+        <v>3.2317</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6735</v>
+        <v>2.2035</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7646</v>
+        <v>2.3885</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6922</v>
+        <v>3.2317</v>
       </c>
       <c r="K3" t="n">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="L3" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4568</v>
+        <v>5.620200000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>390</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>cajunb</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.2834</v>
+        <v>5.308</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7478</v>
+        <v>0.7512</v>
       </c>
       <c r="D4" t="n">
-        <v>1.661</v>
+        <v>1.7583</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2834</v>
+        <v>5.308</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7197</v>
+        <v>3.1044</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5637</v>
+        <v>2.2036</v>
       </c>
       <c r="H4" t="n">
-        <v>1.7197</v>
+        <v>3.4569</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7487</v>
+        <v>4.0617</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5637</v>
+        <v>2.2036</v>
       </c>
       <c r="K4" t="n">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="L4" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="M4" t="n">
-        <v>5.3124</v>
+        <v>6.2653</v>
       </c>
       <c r="N4" t="n">
-        <v>266</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.6741</v>
+        <v>4.8899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6615</v>
+        <v>0.6921</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4183</v>
+        <v>1.5695</v>
       </c>
       <c r="E5" t="n">
-        <v>4.6741</v>
+        <v>4.8899</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1507</v>
+        <v>2.7179</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5234</v>
+        <v>2.172</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1507</v>
+        <v>2.7179</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1604</v>
+        <v>2.9461</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5234</v>
+        <v>2.172</v>
       </c>
       <c r="K5" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="L5" t="n">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6838</v>
+        <v>5.1181</v>
       </c>
       <c r="N5" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>k0nfig</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.665</v>
+        <v>4.3894</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6602</v>
+        <v>0.6212</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4146</v>
+        <v>1.3436</v>
       </c>
       <c r="E6" t="n">
-        <v>4.665</v>
+        <v>4.3894</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6578</v>
+        <v>3.0593</v>
       </c>
       <c r="G6" t="n">
-        <v>3.0072</v>
+        <v>1.3301</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6578</v>
+        <v>3.3579</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6858</v>
+        <v>3.9453</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0072</v>
+        <v>1.3301</v>
       </c>
       <c r="K6" t="n">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="L6" t="n">
-        <v>163</v>
+        <v>275</v>
       </c>
       <c r="M6" t="n">
-        <v>4.693</v>
+        <v>5.2754</v>
       </c>
       <c r="N6" t="n">
-        <v>325</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>k0nfig</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1693</v>
+        <v>4.1101</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5901</v>
+        <v>0.5817</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2171</v>
+        <v>1.2175</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1693</v>
+        <v>4.1101</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2685</v>
+        <v>1.8027</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9008</v>
+        <v>2.3074</v>
       </c>
       <c r="H7" t="n">
-        <v>3.2685</v>
+        <v>1.8027</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3799</v>
+        <v>1.954</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9008</v>
+        <v>2.3074</v>
       </c>
       <c r="K7" t="n">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="L7" t="n">
-        <v>275</v>
+        <v>163</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2807</v>
+        <v>4.2614</v>
       </c>
       <c r="N7" t="n">
-        <v>390</v>
+        <v>325</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.0491</v>
+        <v>3.8283</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5731000000000001</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1693</v>
+        <v>1.0903</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0491</v>
+        <v>3.8283</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.0998</v>
       </c>
       <c r="G8" t="n">
-        <v>4.0491</v>
+        <v>2.7285</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.0998</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1.145</v>
       </c>
       <c r="J8" t="n">
-        <v>4.0491</v>
+        <v>2.7285</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="L8" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0491</v>
+        <v>3.8735</v>
       </c>
       <c r="N8" t="n">
-        <v>174</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.8907</v>
+        <v>3.7458</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5506</v>
+        <v>0.5301</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1061</v>
+        <v>1.053</v>
       </c>
       <c r="E9" t="n">
-        <v>3.8907</v>
+        <v>3.7458</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7349</v>
+        <v>0.1888</v>
       </c>
       <c r="G9" t="n">
-        <v>2.1558</v>
+        <v>3.557</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7349</v>
+        <v>0.1888</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7642</v>
+        <v>0.2047</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1558</v>
+        <v>3.557</v>
       </c>
       <c r="K9" t="n">
         <v>66</v>
@@ -851,7 +851,7 @@
         <v>200</v>
       </c>
       <c r="M9" t="n">
-        <v>3.92</v>
+        <v>3.7617</v>
       </c>
       <c r="N9" t="n">
         <v>266</v>
@@ -860,47 +860,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.7076</v>
+        <v>3.5099</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5247000000000001</v>
+        <v>0.4968</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0332</v>
+        <v>0.9465</v>
       </c>
       <c r="E10" t="n">
-        <v>3.7076</v>
+        <v>3.5099</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0905</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.7981</v>
+        <v>3.5099</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0905</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7981</v>
+        <v>3.5099</v>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7061</v>
+        <v>3.5099</v>
       </c>
       <c r="N10" t="n">
-        <v>266</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.3262</v>
+        <v>3.1169</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4708</v>
+        <v>0.4411</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8812</v>
+        <v>0.7691</v>
       </c>
       <c r="E11" t="n">
-        <v>3.3262</v>
+        <v>3.1169</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4422</v>
+        <v>1.3096</v>
       </c>
       <c r="G11" t="n">
-        <v>1.884</v>
+        <v>1.8073</v>
       </c>
       <c r="H11" t="n">
-        <v>1.4422</v>
+        <v>1.3096</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4666</v>
+        <v>1.4195</v>
       </c>
       <c r="J11" t="n">
-        <v>1.884</v>
+        <v>1.8073</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -943,7 +943,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3506</v>
+        <v>3.2268</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.5332</v>
+        <v>2.6777</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3585</v>
+        <v>0.379</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5653</v>
+        <v>0.5708</v>
       </c>
       <c r="E12" t="n">
-        <v>2.5332</v>
+        <v>2.6777</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1981</v>
+        <v>1.2722</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3351</v>
+        <v>1.4055</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1981</v>
+        <v>1.2722</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2389</v>
+        <v>1.4947</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3351</v>
+        <v>1.4055</v>
       </c>
       <c r="K12" t="n">
         <v>115</v>
@@ -989,7 +989,7 @@
         <v>275</v>
       </c>
       <c r="M12" t="n">
-        <v>2.574</v>
+        <v>2.9002</v>
       </c>
       <c r="N12" t="n">
         <v>390</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>JUGi</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4288</v>
+        <v>2.4932</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3437</v>
+        <v>0.3529</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.4875</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4288</v>
+        <v>2.4932</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.2738</v>
       </c>
       <c r="G13" t="n">
-        <v>2.4288</v>
+        <v>1.2194</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1.2738</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1.4966</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4288</v>
+        <v>1.2194</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L13" t="n">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4288</v>
+        <v>2.716</v>
       </c>
       <c r="N13" t="n">
-        <v>174</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>JUGi</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0463</v>
+        <v>2.2116</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2896</v>
+        <v>0.313</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3713</v>
+        <v>0.3604</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0463</v>
+        <v>2.2116</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1883</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.858</v>
+        <v>2.2116</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1883</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2288</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0.858</v>
+        <v>2.2116</v>
       </c>
       <c r="K14" t="n">
-        <v>115</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>275</v>
+        <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.0868</v>
+        <v>2.2116</v>
       </c>
       <c r="N14" t="n">
-        <v>390</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6662</v>
+        <v>1.7603</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2358</v>
+        <v>0.2491</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2199</v>
+        <v>0.1567</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6662</v>
+        <v>1.7603</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3394</v>
+        <v>1.4171</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3268</v>
+        <v>0.3432</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3394</v>
+        <v>1.4171</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3507</v>
+        <v>1.4754</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3268</v>
+        <v>0.3432</v>
       </c>
       <c r="K15" t="n">
         <v>94</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6775</v>
+        <v>1.8186</v>
       </c>
       <c r="N15" t="n">
         <v>158</v>
@@ -1136,139 +1136,139 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.1465</v>
+        <v>1.2721</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1623</v>
+        <v>0.18</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0129</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1465</v>
+        <v>1.2721</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3524</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4989</v>
+        <v>1.2721</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3524</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.3638</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4989</v>
+        <v>1.2721</v>
       </c>
       <c r="K16" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1351</v>
+        <v>1.2721</v>
       </c>
       <c r="N16" t="n">
-        <v>257</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.077</v>
+        <v>1.2691</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1524</v>
+        <v>0.1796</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0148</v>
+        <v>-0.06510000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.077</v>
+        <v>1.2691</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.063</v>
       </c>
       <c r="G17" t="n">
-        <v>1.077</v>
+        <v>0.2061</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1.063</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1.1522</v>
       </c>
       <c r="J17" t="n">
-        <v>1.077</v>
+        <v>0.2061</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>162</v>
       </c>
       <c r="L17" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="M17" t="n">
-        <v>1.077</v>
+        <v>1.3583</v>
       </c>
       <c r="N17" t="n">
-        <v>174</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8683</v>
+        <v>1.1152</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1229</v>
+        <v>0.1578</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.098</v>
+        <v>-0.1346</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8683</v>
+        <v>1.1152</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0384</v>
+        <v>-0.9225</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1701</v>
+        <v>2.0377</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0384</v>
+        <v>-0.9225</v>
       </c>
       <c r="I18" t="n">
-        <v>1.056</v>
+        <v>-0.9604</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1701</v>
+        <v>2.0377</v>
       </c>
       <c r="K18" t="n">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="L18" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8859</v>
+        <v>1.0773</v>
       </c>
       <c r="N18" t="n">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7788</v>
+        <v>0.8809</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1102</v>
+        <v>0.1247</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1336</v>
+        <v>-0.2403</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7788</v>
+        <v>0.8809</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4464</v>
+        <v>0.4183</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3324</v>
+        <v>0.4626</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4464</v>
+        <v>0.4183</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4539</v>
+        <v>0.4534</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3324</v>
+        <v>0.4626</v>
       </c>
       <c r="K19" t="n">
         <v>57</v>
@@ -1311,7 +1311,7 @@
         <v>152</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7863</v>
+        <v>0.916</v>
       </c>
       <c r="N19" t="n">
         <v>209</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.1092</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.21</v>
+        <v>-0.2896</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2892</v>
+        <v>0.4669</v>
       </c>
       <c r="G20" t="n">
-        <v>0.298</v>
+        <v>0.3048</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2892</v>
+        <v>0.4669</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2916</v>
+        <v>0.4861</v>
       </c>
       <c r="J20" t="n">
-        <v>0.298</v>
+        <v>0.3048</v>
       </c>
       <c r="K20" t="n">
         <v>94</v>
@@ -1357,7 +1357,7 @@
         <v>64</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5896</v>
+        <v>0.7908999999999999</v>
       </c>
       <c r="N20" t="n">
         <v>158</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.443</v>
+        <v>0.7346</v>
       </c>
       <c r="C21" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.104</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2674</v>
+        <v>-0.3064</v>
       </c>
       <c r="E21" t="n">
-        <v>0.443</v>
+        <v>0.7346</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4942</v>
+        <v>-0.8611</v>
       </c>
       <c r="G21" t="n">
-        <v>1.9373</v>
+        <v>1.5957</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4942</v>
+        <v>-0.8611</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5195</v>
+        <v>-0.9334</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9373</v>
+        <v>1.5957</v>
       </c>
       <c r="K21" t="n">
         <v>162</v>
@@ -1403,7 +1403,7 @@
         <v>163</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4177999999999999</v>
+        <v>0.6622999999999999</v>
       </c>
       <c r="N21" t="n">
         <v>325</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1103</v>
+        <v>0.4115</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0156</v>
+        <v>0.0582</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4</v>
+        <v>-0.4522</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1103</v>
+        <v>0.4115</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1103</v>
+        <v>0.4115</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1103</v>
+        <v>0.4115</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>174</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1103</v>
+        <v>0.4115</v>
       </c>
       <c r="N22" t="n">
         <v>174</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0549</v>
+        <v>0.3595</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0078</v>
+        <v>0.0509</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.422</v>
+        <v>-0.4757</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0549</v>
+        <v>0.3595</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0549</v>
+        <v>0.3595</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0549</v>
+        <v>0.3595</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>174</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0549</v>
+        <v>0.3595</v>
       </c>
       <c r="N23" t="n">
         <v>174</v>
@@ -1504,35 +1504,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>MINISE</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0293</v>
+        <v>0.2152</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0041</v>
+        <v>0.0305</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4322</v>
+        <v>-0.5409</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0293</v>
+        <v>0.2152</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3519</v>
+        <v>0.6576</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3226</v>
+        <v>-0.4424</v>
       </c>
       <c r="H24" t="n">
-        <v>0.3519</v>
+        <v>0.6576</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3519</v>
+        <v>0.6576</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3226</v>
+        <v>-0.4424</v>
       </c>
       <c r="K24" t="n">
         <v>57</v>
@@ -1541,7 +1541,7 @@
         <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>0.02929999999999999</v>
+        <v>0.2151999999999999</v>
       </c>
       <c r="N24" t="n">
         <v>97</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MINISE</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0005</v>
+        <v>0.1442</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0001</v>
+        <v>0.0204</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4437</v>
+        <v>-0.5729</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0005</v>
+        <v>0.1442</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5956</v>
+        <v>0.4459</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5951</v>
+        <v>-0.3017</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5956</v>
+        <v>0.4459</v>
       </c>
       <c r="I25" t="n">
-        <v>0.5956</v>
+        <v>0.4459</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.5951</v>
+        <v>-0.3017</v>
       </c>
       <c r="K25" t="n">
         <v>57</v>
@@ -1587,7 +1587,7 @@
         <v>40</v>
       </c>
       <c r="M25" t="n">
-        <v>0.000500000000000056</v>
+        <v>0.1442</v>
       </c>
       <c r="N25" t="n">
         <v>97</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1579</v>
+        <v>0.04</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0223</v>
+        <v>0.0057</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5068</v>
+        <v>-0.62</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1579</v>
+        <v>0.04</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4017</v>
+        <v>1.377</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.5596</v>
+        <v>-1.337</v>
       </c>
       <c r="H26" t="n">
-        <v>1.4017</v>
+        <v>1.377</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4254</v>
+        <v>1.4926</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.5596</v>
+        <v>-1.337</v>
       </c>
       <c r="K26" t="n">
         <v>162</v>
@@ -1633,7 +1633,7 @@
         <v>163</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1342000000000001</v>
+        <v>0.1556</v>
       </c>
       <c r="N26" t="n">
         <v>325</v>
@@ -1642,231 +1642,231 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3777</v>
+        <v>-0.0124</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0535</v>
+        <v>-0.0018</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5944</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3777</v>
+        <v>-0.0124</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.0591</v>
+        <v>-0.1308</v>
       </c>
       <c r="G27" t="n">
-        <v>0.6814</v>
+        <v>0.1184</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.0591</v>
+        <v>-0.1308</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.068</v>
+        <v>-0.1537</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6814</v>
+        <v>0.1184</v>
       </c>
       <c r="K27" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L27" t="n">
-        <v>144</v>
+        <v>275</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3866000000000001</v>
+        <v>-0.0353</v>
       </c>
       <c r="N27" t="n">
-        <v>257</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4674</v>
+        <v>-0.0548</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0078</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6301</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4674</v>
+        <v>-0.0548</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.228</v>
+        <v>0.3156</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2394</v>
+        <v>-0.3704</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.228</v>
+        <v>0.3156</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2299</v>
+        <v>0.3421</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2394</v>
+        <v>-0.3704</v>
       </c>
       <c r="K28" t="n">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="L28" t="n">
-        <v>64</v>
+        <v>152</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4693</v>
+        <v>-0.02829999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>158</v>
+        <v>209</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4829</v>
+        <v>-0.1248</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0683</v>
+        <v>-0.0177</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6363</v>
+        <v>-0.6944</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4829</v>
+        <v>-0.1248</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.4288</v>
+        <v>0.5641</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.0541</v>
+        <v>-0.6889</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4288</v>
+        <v>0.5641</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.4434</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.0541</v>
+        <v>-0.6889</v>
       </c>
       <c r="K29" t="n">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="L29" t="n">
-        <v>275</v>
+        <v>152</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.4975</v>
+        <v>-0.0774999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>390</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.494</v>
+        <v>-0.2001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0699</v>
+        <v>-0.0283</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6407</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.494</v>
+        <v>-0.2001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.2492</v>
+        <v>-0.6902</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.7432</v>
+        <v>0.4901</v>
       </c>
       <c r="H30" t="n">
-        <v>0.2492</v>
+        <v>-0.6902</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2534</v>
+        <v>-0.7186</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.7432</v>
+        <v>0.4901</v>
       </c>
       <c r="K30" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="L30" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.4898</v>
+        <v>-0.2285</v>
       </c>
       <c r="N30" t="n">
-        <v>209</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.587</v>
+        <v>-0.212</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-0.03</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6778</v>
+        <v>-0.7337</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.587</v>
+        <v>-0.212</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5753</v>
+        <v>-0.0309</v>
       </c>
       <c r="G31" t="n">
-        <v>-1.1623</v>
+        <v>-0.1811</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5753</v>
+        <v>-0.0309</v>
       </c>
       <c r="I31" t="n">
-        <v>0.585</v>
+        <v>-0.0322</v>
       </c>
       <c r="J31" t="n">
-        <v>-1.1623</v>
+        <v>-0.1811</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L31" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.5773000000000001</v>
+        <v>-0.2133</v>
       </c>
       <c r="N31" t="n">
-        <v>209</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.2759</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.1215</v>
+        <v>-0.039</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7859</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.2759</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.0704</v>
+        <v>0.2323</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.788</v>
+        <v>-0.5082</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.0704</v>
+        <v>0.2323</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.07099999999999999</v>
+        <v>0.2419</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.788</v>
+        <v>-0.5082</v>
       </c>
       <c r="K32" t="n">
         <v>94</v>
@@ -1909,7 +1909,7 @@
         <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.859</v>
+        <v>-0.2663</v>
       </c>
       <c r="N32" t="n">
         <v>158</v>
@@ -1918,139 +1918,139 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>neptune</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.571</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1242</v>
+        <v>-0.0808</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7935</v>
+        <v>-0.8958</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.571</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.9833</v>
+        <v>-0.2039</v>
       </c>
       <c r="G33" t="n">
-        <v>1.1058</v>
+        <v>-0.3671</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.9833</v>
+        <v>-0.2039</v>
       </c>
       <c r="I33" t="n">
-        <v>-2</v>
+        <v>-0.221</v>
       </c>
       <c r="J33" t="n">
-        <v>1.1058</v>
+        <v>-0.3671</v>
       </c>
       <c r="K33" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="L33" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.8942000000000001</v>
+        <v>-0.5881</v>
       </c>
       <c r="N33" t="n">
-        <v>257</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SmithZz</t>
+          <t>yay</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.9307</v>
+        <v>-0.6249</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1317</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8147</v>
+        <v>-0.9201</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9307</v>
+        <v>-0.6249</v>
       </c>
       <c r="F34" t="n">
-        <v>0.0693</v>
+        <v>-0.9086</v>
       </c>
       <c r="G34" t="n">
-        <v>-1</v>
+        <v>0.2837</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0693</v>
+        <v>-0.9086</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0699</v>
+        <v>-0.9849</v>
       </c>
       <c r="J34" t="n">
-        <v>-1</v>
+        <v>0.2837</v>
       </c>
       <c r="K34" t="n">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="L34" t="n">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.9301</v>
+        <v>-0.7012</v>
       </c>
       <c r="N34" t="n">
-        <v>158</v>
+        <v>325</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>neptune</t>
+          <t>SmithZz</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.061</v>
+        <v>-0.7013</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1502</v>
+        <v>-0.0993</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8666</v>
+        <v>-0.9546</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.061</v>
+        <v>-0.7013</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.2339</v>
+        <v>0.1823</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.2339</v>
+        <v>0.1823</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2379</v>
+        <v>0.1898</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="L35" t="n">
-        <v>152</v>
+        <v>64</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.065</v>
+        <v>-0.6938000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>209</v>
+        <v>158</v>
       </c>
     </row>
     <row r="36">
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.0761</v>
+        <v>-0.8398</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1523</v>
+        <v>-0.1189</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8726</v>
+        <v>-1.0171</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.0761</v>
+        <v>-0.8398</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.0761</v>
+        <v>0.0481</v>
       </c>
       <c r="G36" t="n">
-        <v>-1</v>
+        <v>-0.8879</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.0761</v>
+        <v>0.0481</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.0761</v>
+        <v>0.0481</v>
       </c>
       <c r="J36" t="n">
-        <v>-1</v>
+        <v>-0.8879</v>
       </c>
       <c r="K36" t="n">
         <v>57</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.0761</v>
+        <v>-0.8398</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.2077</v>
+        <v>-0.8529</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1709</v>
+        <v>-0.1207</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9251</v>
+        <v>-1.0231</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.2077</v>
+        <v>-0.8529</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.2932</v>
+        <v>-0.1896</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.9145</v>
+        <v>-0.6633</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2932</v>
+        <v>-0.1896</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.2932</v>
+        <v>-0.1896</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9145</v>
+        <v>-0.6633</v>
       </c>
       <c r="K37" t="n">
         <v>57</v>
@@ -2139,7 +2139,7 @@
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.2077</v>
+        <v>-0.8529</v>
       </c>
       <c r="N37" t="n">
         <v>97</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.2945</v>
+        <v>-1.0126</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1832</v>
+        <v>-0.1433</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9596</v>
+        <v>-1.0952</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.2945</v>
+        <v>-1.0126</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.8612</v>
+        <v>-1.1904</v>
       </c>
       <c r="G38" t="n">
-        <v>0.5667</v>
+        <v>0.1778</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.8612</v>
+        <v>-1.1904</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.8769</v>
+        <v>-1.2394</v>
       </c>
       <c r="J38" t="n">
-        <v>0.5667</v>
+        <v>0.1778</v>
       </c>
       <c r="K38" t="n">
         <v>113</v>
@@ -2185,7 +2185,7 @@
         <v>144</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3102</v>
+        <v>-1.0616</v>
       </c>
       <c r="N38" t="n">
         <v>257</v>
@@ -2194,47 +2194,47 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yay</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.303</v>
+        <v>-1.0838</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1844</v>
+        <v>-0.1534</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.963</v>
+        <v>-1.1273</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.303</v>
+        <v>-1.0838</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.4774</v>
+        <v>-1.9047</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1744</v>
+        <v>0.8209</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.4774</v>
+        <v>-1.9047</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5024</v>
+        <v>-1.983</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1744</v>
+        <v>0.8209</v>
       </c>
       <c r="K39" t="n">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="L39" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.328</v>
+        <v>-1.1621</v>
       </c>
       <c r="N39" t="n">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40">
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7991</v>
+        <v>-1.438</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2546</v>
+        <v>-0.2035</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1607</v>
+        <v>-1.2872</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7991</v>
+        <v>-1.438</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7991</v>
+        <v>-0.5019</v>
       </c>
       <c r="G40" t="n">
-        <v>-1</v>
+        <v>-0.9361</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7991</v>
+        <v>-0.5019</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.7991</v>
+        <v>-0.5019</v>
       </c>
       <c r="J40" t="n">
-        <v>-1</v>
+        <v>-0.9361</v>
       </c>
       <c r="K40" t="n">
         <v>57</v>
@@ -2277,7 +2277,7 @@
         <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.7991</v>
+        <v>-1.438</v>
       </c>
       <c r="N40" t="n">
         <v>97</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3784</v>
+        <v>-1.8892</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3366</v>
+        <v>-0.2674</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3915</v>
+        <v>-1.4909</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3784</v>
+        <v>-1.8892</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.3098</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>-2.0686</v>
+        <v>-1.9674</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.3098</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.315</v>
+        <v>0.0848</v>
       </c>
       <c r="J41" t="n">
-        <v>-2.0686</v>
+        <v>-1.9674</v>
       </c>
       <c r="K41" t="n">
         <v>66</v>
@@ -2323,7 +2323,7 @@
         <v>200</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3836</v>
+        <v>-1.8826</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9745</v>
+        <v>0.9534</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9745</v>
+        <v>0.9534</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9304</v>
+        <v>0.9091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9304</v>
+        <v>0.9091</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1157</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.1157</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.403</v>
+        <v>-0.3407</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.403</v>
+        <v>-0.3407</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8132</v>
+        <v>-0.7703</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8132</v>
+        <v>-0.7703</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.474</v>
+        <v>0.5619</v>
       </c>
       <c r="J7" t="n">
-        <v>0.474</v>
+        <v>0.5619</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1657</v>
+        <v>0.1934</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1657</v>
+        <v>0.1934</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1306</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1306</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0518</v>
+        <v>0.0839</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0518</v>
+        <v>0.0839</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3084</v>
+        <v>-0.1842</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3084</v>
+        <v>-0.1842</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8811</v>
+        <v>0.8579</v>
       </c>
       <c r="J12" t="n">
-        <v>26.433</v>
+        <v>25.737</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.21</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>0.3131</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>9.393000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.17</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2377</v>
+        <v>0.2601</v>
       </c>
       <c r="J14" t="n">
-        <v>7.131</v>
+        <v>7.803</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1596</v>
+        <v>0.1894</v>
       </c>
       <c r="J15" t="n">
-        <v>4.788</v>
+        <v>5.682</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1108</v>
+        <v>-0.0429</v>
       </c>
       <c r="J16" t="n">
-        <v>-3.324</v>
+        <v>-1.287</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2194</v>
+        <v>0.1545</v>
       </c>
       <c r="J17" t="n">
-        <v>6.582</v>
+        <v>4.635</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0588</v>
+        <v>0.0177</v>
       </c>
       <c r="J18" t="n">
-        <v>1.764</v>
+        <v>0.531</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2862</v>
+        <v>-0.185</v>
       </c>
       <c r="J19" t="n">
-        <v>-8.586</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3029</v>
+        <v>-0.1951</v>
       </c>
       <c r="J20" t="n">
-        <v>-9.087</v>
+        <v>-5.853</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5094</v>
+        <v>-0.3319</v>
       </c>
       <c r="J21" t="n">
-        <v>-15.282</v>
+        <v>-9.957000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.13</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1179</v>
+        <v>1.8466</v>
       </c>
       <c r="J22" t="n">
-        <v>50.8296</v>
+        <v>44.3184</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6458</v>
+        <v>0.7411</v>
       </c>
       <c r="J23" t="n">
-        <v>15.4992</v>
+        <v>17.7864</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.5271</v>
+        <v>0.6254</v>
       </c>
       <c r="J24" t="n">
-        <v>12.6504</v>
+        <v>15.0096</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2551</v>
+        <v>0.3484</v>
       </c>
       <c r="J25" t="n">
-        <v>6.1224</v>
+        <v>8.361599999999999</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1145</v>
+        <v>-0.0314</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.748</v>
+        <v>-0.7536</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1639</v>
+        <v>0.1381</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9336</v>
+        <v>3.3144</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2346</v>
+        <v>-0.1943</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.6304</v>
+        <v>-4.6632</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.68</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.466</v>
+        <v>-0.3181</v>
       </c>
       <c r="J29" t="n">
-        <v>-11.184</v>
+        <v>-7.6344</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.67</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4818</v>
+        <v>-0.3274</v>
       </c>
       <c r="J30" t="n">
-        <v>-11.5632</v>
+        <v>-7.8576</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.793</v>
+        <v>-0.5421</v>
       </c>
       <c r="J31" t="n">
-        <v>-19.032</v>
+        <v>-13.0104</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3239</v>
+        <v>-0.2722</v>
       </c>
       <c r="J32" t="n">
-        <v>-6.478</v>
+        <v>-5.444</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.68</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3392</v>
+        <v>-0.2828</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.784</v>
+        <v>-5.656</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4321</v>
+        <v>-0.3444</v>
       </c>
       <c r="J34" t="n">
-        <v>-8.641999999999999</v>
+        <v>-6.888</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.43</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7556</v>
+        <v>-0.5204</v>
       </c>
       <c r="J35" t="n">
-        <v>-15.112</v>
+        <v>-10.408</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.31</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9167</v>
+        <v>-0.6373</v>
       </c>
       <c r="J36" t="n">
-        <v>-18.334</v>
+        <v>-12.746</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.11</v>
       </c>
       <c r="I37" t="n">
-        <v>2.0302</v>
+        <v>1.7504</v>
       </c>
       <c r="J37" t="n">
-        <v>40.604</v>
+        <v>35.008</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.03</v>
       </c>
       <c r="I38" t="n">
-        <v>1.9555</v>
+        <v>1.6649</v>
       </c>
       <c r="J38" t="n">
-        <v>39.11</v>
+        <v>33.298</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.0738</v>
+        <v>1.1389</v>
       </c>
       <c r="J39" t="n">
-        <v>21.476</v>
+        <v>22.778</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.53</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0341</v>
+        <v>1.1154</v>
       </c>
       <c r="J40" t="n">
-        <v>20.682</v>
+        <v>22.308</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.025</v>
+        <v>0.1193</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5</v>
+        <v>2.386</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4817</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>13.0059</v>
+        <v>15.12</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.89</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1626</v>
+        <v>-0.1299</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.3902</v>
+        <v>-3.5073</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3188</v>
+        <v>-0.2106</v>
       </c>
       <c r="J44" t="n">
-        <v>-8.6076</v>
+        <v>-5.6862</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5266999999999999</v>
+        <v>-0.3457</v>
       </c>
       <c r="J45" t="n">
-        <v>-14.2209</v>
+        <v>-9.3339</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.5669</v>
+        <v>-0.374</v>
       </c>
       <c r="J46" t="n">
-        <v>-15.3063</v>
+        <v>-10.098</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.68</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5366</v>
+        <v>1.3496</v>
       </c>
       <c r="J47" t="n">
-        <v>41.4882</v>
+        <v>36.4392</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7764</v>
+        <v>0.8007</v>
       </c>
       <c r="J48" t="n">
-        <v>20.9628</v>
+        <v>21.6189</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6997</v>
+        <v>0.7337</v>
       </c>
       <c r="J49" t="n">
-        <v>18.8919</v>
+        <v>19.8099</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0905</v>
+        <v>0.1686</v>
       </c>
       <c r="J50" t="n">
-        <v>2.4435</v>
+        <v>4.5522</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2031</v>
+        <v>-0.1193</v>
       </c>
       <c r="J51" t="n">
-        <v>-5.4837</v>
+        <v>-3.2211</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4335</v>
+        <v>0.3946</v>
       </c>
       <c r="J52" t="n">
-        <v>17.7735</v>
+        <v>16.1786</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1686</v>
+        <v>0.1571</v>
       </c>
       <c r="J53" t="n">
-        <v>6.9126</v>
+        <v>6.4411</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1196</v>
+        <v>0.124</v>
       </c>
       <c r="J54" t="n">
-        <v>4.9036</v>
+        <v>5.084</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0988</v>
+        <v>-0.0604</v>
       </c>
       <c r="J55" t="n">
-        <v>-4.0508</v>
+        <v>-2.4764</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1437</v>
+        <v>-0.101</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.8917</v>
+        <v>-4.141</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.474</v>
+        <v>0.5619</v>
       </c>
       <c r="J57" t="n">
-        <v>19.434</v>
+        <v>23.0379</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3628</v>
+        <v>0.4214</v>
       </c>
       <c r="J58" t="n">
-        <v>14.8748</v>
+        <v>17.2774</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3332</v>
+        <v>0.3851</v>
       </c>
       <c r="J59" t="n">
-        <v>13.6612</v>
+        <v>15.7891</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2448</v>
+        <v>-0.1409</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.0368</v>
+        <v>-5.7769</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4783</v>
+        <v>-0.3046</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.6103</v>
+        <v>-12.4886</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5497</v>
+        <v>1.3557</v>
       </c>
       <c r="J62" t="n">
-        <v>41.8419</v>
+        <v>36.6039</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5666</v>
+        <v>0.5671</v>
       </c>
       <c r="J63" t="n">
-        <v>15.2982</v>
+        <v>15.3117</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.258</v>
+        <v>0.3117</v>
       </c>
       <c r="J64" t="n">
-        <v>6.966</v>
+        <v>8.415900000000001</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1665</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.4955</v>
+        <v>-2.5191</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5966</v>
+        <v>-0.5331</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.1082</v>
+        <v>-14.3937</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3261</v>
+        <v>0.3519</v>
       </c>
       <c r="J67" t="n">
-        <v>8.8047</v>
+        <v>9.501300000000001</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0594</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.6038</v>
+        <v>-1.6956</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.195</v>
+        <v>-0.143</v>
       </c>
       <c r="J69" t="n">
-        <v>-5.265</v>
+        <v>-3.861</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4637</v>
+        <v>-0.3011</v>
       </c>
       <c r="J70" t="n">
-        <v>-12.5199</v>
+        <v>-8.1297</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5324</v>
+        <v>-0.3487</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.3748</v>
+        <v>-9.414899999999999</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.9131</v>
+        <v>1.6174</v>
       </c>
       <c r="J72" t="n">
-        <v>38.262</v>
+        <v>32.348</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.6</v>
       </c>
       <c r="I73" t="n">
-        <v>1.2751</v>
+        <v>1.209</v>
       </c>
       <c r="J73" t="n">
-        <v>25.502</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1718</v>
+        <v>1.1511</v>
       </c>
       <c r="J74" t="n">
-        <v>23.436</v>
+        <v>23.022</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.31</v>
       </c>
       <c r="I75" t="n">
-        <v>0.6319</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J75" t="n">
-        <v>12.638</v>
+        <v>15.152</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.11</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1633</v>
+        <v>0.2629</v>
       </c>
       <c r="J76" t="n">
-        <v>3.266</v>
+        <v>5.258</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.91</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.033</v>
+        <v>-0.0596</v>
       </c>
       <c r="J77" t="n">
-        <v>-0.66</v>
+        <v>-1.192</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.86</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1178</v>
+        <v>-0.1205</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.356</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.62</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.5226</v>
+        <v>-0.363</v>
       </c>
       <c r="J79" t="n">
-        <v>-10.452</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.52</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6705</v>
+        <v>-0.4558</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.41</v>
+        <v>-9.116</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.35</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.8895</v>
+        <v>-0.6161</v>
       </c>
       <c r="J81" t="n">
-        <v>-17.79</v>
+        <v>-12.322</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.5389</v>
+        <v>0.4894</v>
       </c>
       <c r="J82" t="n">
-        <v>12.9336</v>
+        <v>11.7456</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.196</v>
+        <v>0.151</v>
       </c>
       <c r="J83" t="n">
-        <v>4.704</v>
+        <v>3.624</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.2433</v>
+        <v>-0.15</v>
       </c>
       <c r="J84" t="n">
-        <v>-5.8392</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.2433</v>
+        <v>-0.15</v>
       </c>
       <c r="J85" t="n">
-        <v>-5.8392</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6375</v>
+        <v>-0.4234</v>
       </c>
       <c r="J86" t="n">
-        <v>-15.3</v>
+        <v>-10.1616</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.82</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0316</v>
+        <v>0.9469</v>
       </c>
       <c r="J87" t="n">
-        <v>24.7584</v>
+        <v>22.7256</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4095</v>
+        <v>0.3704</v>
       </c>
       <c r="J88" t="n">
-        <v>9.827999999999999</v>
+        <v>8.8896</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1233</v>
+        <v>0.1464</v>
       </c>
       <c r="J89" t="n">
-        <v>2.9592</v>
+        <v>3.5136</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.05</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0372</v>
+        <v>0.0707</v>
       </c>
       <c r="J90" t="n">
-        <v>0.8928</v>
+        <v>1.6968</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1138</v>
+        <v>-0.0444</v>
       </c>
       <c r="J91" t="n">
-        <v>-2.7312</v>
+        <v>-1.0656</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.77</v>
       </c>
       <c r="I92" t="n">
-        <v>1.6732</v>
+        <v>1.4425</v>
       </c>
       <c r="J92" t="n">
-        <v>36.8104</v>
+        <v>31.735</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.55</v>
       </c>
       <c r="I93" t="n">
-        <v>1.2629</v>
+        <v>1.1777</v>
       </c>
       <c r="J93" t="n">
-        <v>27.7838</v>
+        <v>25.9094</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.29</v>
       </c>
       <c r="I94" t="n">
-        <v>0.668</v>
+        <v>0.748</v>
       </c>
       <c r="J94" t="n">
-        <v>14.696</v>
+        <v>16.456</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1592</v>
+        <v>0.2453</v>
       </c>
       <c r="J95" t="n">
-        <v>3.5024</v>
+        <v>5.3966</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4806</v>
+        <v>-0.4029</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.5732</v>
+        <v>-8.863799999999999</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.96</v>
       </c>
       <c r="I97" t="n">
-        <v>0.004</v>
+        <v>-0.0301</v>
       </c>
       <c r="J97" t="n">
-        <v>0.08799999999999999</v>
+        <v>-0.6622</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0725</v>
+        <v>-0.0819</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.595</v>
+        <v>-1.8018</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.76</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.3607</v>
+        <v>-0.2501</v>
       </c>
       <c r="J99" t="n">
-        <v>-7.9354</v>
+        <v>-5.5022</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.63</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.5594</v>
+        <v>-0.3725</v>
       </c>
       <c r="J100" t="n">
-        <v>-12.3068</v>
+        <v>-8.195</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.6135</v>
+        <v>-0.4099</v>
       </c>
       <c r="J101" t="n">
-        <v>-13.497</v>
+        <v>-9.017799999999999</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4014</v>
+        <v>0.4085</v>
       </c>
       <c r="J102" t="n">
-        <v>11.6406</v>
+        <v>11.8465</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3127</v>
+        <v>0.341</v>
       </c>
       <c r="J103" t="n">
-        <v>9.068300000000001</v>
+        <v>9.888999999999999</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1785</v>
+        <v>0.1859</v>
       </c>
       <c r="J104" t="n">
-        <v>5.1765</v>
+        <v>5.3911</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2746</v>
+        <v>-0.1657</v>
       </c>
       <c r="J105" t="n">
-        <v>-7.9634</v>
+        <v>-4.8053</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.5825</v>
+        <v>-0.3821</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.8925</v>
+        <v>-11.0809</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>1.2205</v>
+        <v>0.8621</v>
       </c>
       <c r="J107" t="n">
-        <v>35.3945</v>
+        <v>25.0009</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.9029</v>
+        <v>0.6606</v>
       </c>
       <c r="J108" t="n">
-        <v>26.1841</v>
+        <v>19.1574</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1936</v>
+        <v>-0.1251</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.6144</v>
+        <v>-3.6279</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1936</v>
+        <v>-0.1251</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.6144</v>
+        <v>-3.6279</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5855</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="J111" t="n">
-        <v>-16.9795</v>
+        <v>-15.1873</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.5869</v>
+        <v>0.4386</v>
       </c>
       <c r="J112" t="n">
-        <v>15.8463</v>
+        <v>11.8422</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4453</v>
+        <v>0.3632</v>
       </c>
       <c r="J113" t="n">
-        <v>12.0231</v>
+        <v>9.8064</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2826</v>
+        <v>0.2493</v>
       </c>
       <c r="J114" t="n">
-        <v>7.6302</v>
+        <v>6.7311</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.12</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1876</v>
+        <v>0.1855</v>
       </c>
       <c r="J115" t="n">
-        <v>5.0652</v>
+        <v>5.0085</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.439</v>
+        <v>-0.2746</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.853</v>
+        <v>-7.4142</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.4475</v>
+        <v>0.3713</v>
       </c>
       <c r="J117" t="n">
-        <v>12.0825</v>
+        <v>10.0251</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.2015</v>
+        <v>0.1609</v>
       </c>
       <c r="J118" t="n">
-        <v>5.4405</v>
+        <v>4.3443</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1461</v>
+        <v>-0.0859</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.9447</v>
+        <v>-2.3193</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3488</v>
+        <v>-0.2163</v>
       </c>
       <c r="J120" t="n">
-        <v>-9.4176</v>
+        <v>-5.8401</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3637</v>
+        <v>-0.2264</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.819900000000001</v>
+        <v>-6.1128</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5116000000000001</v>
+        <v>0.4952</v>
       </c>
       <c r="J122" t="n">
-        <v>13.3016</v>
+        <v>12.8752</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2678</v>
+        <v>0.2995</v>
       </c>
       <c r="J123" t="n">
-        <v>6.9628</v>
+        <v>7.787</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2347</v>
+        <v>0.2603</v>
       </c>
       <c r="J124" t="n">
-        <v>6.1022</v>
+        <v>6.7678</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2523</v>
+        <v>-0.1482</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.5598</v>
+        <v>-3.8532</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.5248</v>
+        <v>-0.3391</v>
       </c>
       <c r="J126" t="n">
-        <v>-13.6448</v>
+        <v>-8.816599999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0888</v>
+        <v>0.7856</v>
       </c>
       <c r="J127" t="n">
-        <v>28.3088</v>
+        <v>20.4256</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.9608</v>
+        <v>0.7075</v>
       </c>
       <c r="J128" t="n">
-        <v>24.9808</v>
+        <v>18.395</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.8025</v>
+        <v>0.6147</v>
       </c>
       <c r="J129" t="n">
-        <v>20.865</v>
+        <v>15.9822</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.4931</v>
       </c>
       <c r="J130" t="n">
-        <v>14.612</v>
+        <v>12.8206</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.8275</v>
+        <v>-0.7818000000000001</v>
       </c>
       <c r="J131" t="n">
-        <v>-21.515</v>
+        <v>-20.3268</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6401</v>
+        <v>0.5129</v>
       </c>
       <c r="J132" t="n">
-        <v>21.7634</v>
+        <v>17.4386</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5605</v>
+        <v>0.4703</v>
       </c>
       <c r="J133" t="n">
-        <v>19.057</v>
+        <v>15.9902</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4702</v>
+        <v>0.4274</v>
       </c>
       <c r="J134" t="n">
-        <v>15.9868</v>
+        <v>14.5316</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3712</v>
+        <v>0.3833</v>
       </c>
       <c r="J135" t="n">
-        <v>12.6208</v>
+        <v>13.0322</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.1</v>
       </c>
       <c r="I136" t="n">
-        <v>0.2532</v>
+        <v>0.3095</v>
       </c>
       <c r="J136" t="n">
-        <v>8.6088</v>
+        <v>10.523</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6131</v>
+        <v>0.5743</v>
       </c>
       <c r="J137" t="n">
-        <v>20.8454</v>
+        <v>19.5262</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.97</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0568</v>
+        <v>-0.0465</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.9312</v>
+        <v>-1.581</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1733</v>
+        <v>-0.1067</v>
       </c>
       <c r="J139" t="n">
-        <v>-5.8922</v>
+        <v>-3.6278</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3416</v>
+        <v>-0.2131</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.6144</v>
+        <v>-7.2454</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5241</v>
+        <v>-0.3401</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.8194</v>
+        <v>-11.5634</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>1.0611</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="J142" t="n">
-        <v>26.5275</v>
+        <v>19.14</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.595</v>
+        <v>0.4955</v>
       </c>
       <c r="J143" t="n">
-        <v>14.875</v>
+        <v>12.3875</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.468</v>
+        <v>0.4397</v>
       </c>
       <c r="J144" t="n">
-        <v>11.7</v>
+        <v>10.9925</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2682</v>
+        <v>0.3289</v>
       </c>
       <c r="J145" t="n">
-        <v>6.705</v>
+        <v>8.2225</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.0525</v>
+        <v>0.1207</v>
       </c>
       <c r="J146" t="n">
-        <v>1.3125</v>
+        <v>3.0175</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4782</v>
+        <v>0.4653</v>
       </c>
       <c r="J147" t="n">
-        <v>11.955</v>
+        <v>11.6325</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1233</v>
+        <v>0.1076</v>
       </c>
       <c r="J148" t="n">
-        <v>3.0825</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1608</v>
+        <v>-0.1048</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.02</v>
+        <v>-2.62</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.2006</v>
+        <v>-0.1268</v>
       </c>
       <c r="J150" t="n">
-        <v>-5.015</v>
+        <v>-3.17</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6959</v>
+        <v>-0.4674</v>
       </c>
       <c r="J151" t="n">
-        <v>-17.3975</v>
+        <v>-11.685</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.02</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1619</v>
+        <v>0.1041</v>
       </c>
       <c r="J152" t="n">
-        <v>3.8856</v>
+        <v>2.4984</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1303</v>
+        <v>-0.1193</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.1272</v>
+        <v>-2.8632</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.76</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3675</v>
+        <v>-0.2512</v>
       </c>
       <c r="J154" t="n">
-        <v>-8.82</v>
+        <v>-6.0288</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4776</v>
+        <v>-0.3174</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.4624</v>
+        <v>-7.6176</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6681</v>
+        <v>-0.4487</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.0344</v>
+        <v>-10.7688</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.86</v>
       </c>
       <c r="I157" t="n">
-        <v>1.0578</v>
+        <v>0.9705</v>
       </c>
       <c r="J157" t="n">
-        <v>25.3872</v>
+        <v>23.292</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4456</v>
+        <v>0.4104</v>
       </c>
       <c r="J158" t="n">
-        <v>10.6944</v>
+        <v>9.849600000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3783</v>
+        <v>0.3667</v>
       </c>
       <c r="J159" t="n">
-        <v>9.0792</v>
+        <v>8.800800000000001</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0083</v>
+        <v>0.0478</v>
       </c>
       <c r="J160" t="n">
-        <v>0.1992</v>
+        <v>1.1472</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0896</v>
+        <v>-0.028</v>
       </c>
       <c r="J161" t="n">
-        <v>-2.1504</v>
+        <v>-0.672</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>1.0072</v>
+        <v>0.9898</v>
       </c>
       <c r="J162" t="n">
-        <v>34.2448</v>
+        <v>33.6532</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5031</v>
+        <v>0.4986</v>
       </c>
       <c r="J163" t="n">
-        <v>17.1054</v>
+        <v>16.9524</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3384</v>
+        <v>0.3715</v>
       </c>
       <c r="J164" t="n">
-        <v>11.5056</v>
+        <v>12.631</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.09</v>
       </c>
       <c r="I165" t="n">
-        <v>0.244</v>
+        <v>0.2892</v>
       </c>
       <c r="J165" t="n">
-        <v>8.295999999999999</v>
+        <v>9.832800000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4265</v>
+        <v>-0.3572</v>
       </c>
       <c r="J166" t="n">
-        <v>-14.501</v>
+        <v>-12.1448</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5536</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="J167" t="n">
-        <v>18.8224</v>
+        <v>22.4672</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0496</v>
+        <v>-0.0346</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.6864</v>
+        <v>-1.1764</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1658</v>
+        <v>-0.0978</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.6372</v>
+        <v>-3.3252</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1846</v>
+        <v>-0.1093</v>
       </c>
       <c r="J170" t="n">
-        <v>-6.2764</v>
+        <v>-3.7162</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4627</v>
+        <v>-0.2954</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.7318</v>
+        <v>-10.0436</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0307</v>
+        <v>1.0087</v>
       </c>
       <c r="J172" t="n">
-        <v>37.1052</v>
+        <v>36.3132</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8772</v>
+        <v>0.8627</v>
       </c>
       <c r="J173" t="n">
-        <v>31.5792</v>
+        <v>31.0572</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6389</v>
+        <v>0.6237</v>
       </c>
       <c r="J174" t="n">
-        <v>23.0004</v>
+        <v>22.4532</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.89</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4813</v>
+        <v>-0.4142</v>
       </c>
       <c r="J175" t="n">
-        <v>-17.3268</v>
+        <v>-14.9112</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.83</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.638</v>
+        <v>-0.579</v>
       </c>
       <c r="J176" t="n">
-        <v>-22.968</v>
+        <v>-20.844</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.4813</v>
+        <v>0.5653</v>
       </c>
       <c r="J177" t="n">
-        <v>17.3268</v>
+        <v>20.3508</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4679</v>
+        <v>0.5476</v>
       </c>
       <c r="J178" t="n">
-        <v>16.8444</v>
+        <v>19.7136</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.91</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2099</v>
+        <v>-0.1228</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.5564</v>
+        <v>-4.4208</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2607</v>
+        <v>-0.1559</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.385199999999999</v>
+        <v>-5.6124</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.5586</v>
+        <v>-0.3643</v>
       </c>
       <c r="J181" t="n">
-        <v>-20.1096</v>
+        <v>-13.1148</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5494</v>
+        <v>0.5059</v>
       </c>
       <c r="J182" t="n">
-        <v>16.482</v>
+        <v>15.177</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.4389</v>
+        <v>0.3972</v>
       </c>
       <c r="J183" t="n">
-        <v>13.167</v>
+        <v>11.916</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2513</v>
+        <v>0.2224</v>
       </c>
       <c r="J184" t="n">
-        <v>7.539</v>
+        <v>6.672</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1381</v>
+        <v>-0.099</v>
       </c>
       <c r="J185" t="n">
-        <v>-4.143</v>
+        <v>-2.97</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.8</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6768</v>
+        <v>-0.6283</v>
       </c>
       <c r="J186" t="n">
-        <v>-20.304</v>
+        <v>-18.849</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.25</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4401</v>
+        <v>0.5159</v>
       </c>
       <c r="J187" t="n">
-        <v>13.203</v>
+        <v>15.477</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3403</v>
+        <v>0.3902</v>
       </c>
       <c r="J188" t="n">
-        <v>10.209</v>
+        <v>11.706</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.194</v>
+        <v>0.2172</v>
       </c>
       <c r="J189" t="n">
-        <v>5.82</v>
+        <v>6.516</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.3341</v>
+        <v>-0.2029</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.023</v>
+        <v>-6.087</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.3341</v>
+        <v>-0.2029</v>
       </c>
       <c r="J191" t="n">
-        <v>-10.023</v>
+        <v>-6.087</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.1307</v>
+        <v>1.0817</v>
       </c>
       <c r="J192" t="n">
-        <v>30.5289</v>
+        <v>29.2059</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.35</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9172</v>
+        <v>0.9136</v>
       </c>
       <c r="J193" t="n">
-        <v>24.7644</v>
+        <v>24.6672</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.15</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3915</v>
+        <v>0.4411</v>
       </c>
       <c r="J194" t="n">
-        <v>10.5705</v>
+        <v>11.9097</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.13</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3337</v>
+        <v>0.389</v>
       </c>
       <c r="J195" t="n">
-        <v>9.0099</v>
+        <v>10.503</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6768</v>
+        <v>-0.6182</v>
       </c>
       <c r="J196" t="n">
-        <v>-18.2736</v>
+        <v>-16.6914</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.1</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2553</v>
+        <v>0.2674</v>
       </c>
       <c r="J197" t="n">
-        <v>6.8931</v>
+        <v>7.2198</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0409</v>
+        <v>0.0133</v>
       </c>
       <c r="J198" t="n">
-        <v>1.1043</v>
+        <v>0.3591</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.0882</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.3814</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.2701</v>
+        <v>-0.1691</v>
       </c>
       <c r="J200" t="n">
-        <v>-7.2927</v>
+        <v>-4.5657</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.73</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.465</v>
+        <v>-0.299</v>
       </c>
       <c r="J201" t="n">
-        <v>-12.555</v>
+        <v>-8.073</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.65</v>
       </c>
       <c r="I202" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.6105</v>
       </c>
       <c r="J202" t="n">
-        <v>25.7404</v>
+        <v>17.7045</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.3361</v>
+        <v>0.2883</v>
       </c>
       <c r="J203" t="n">
-        <v>9.7469</v>
+        <v>8.3607</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.06</v>
       </c>
       <c r="I204" t="n">
-        <v>0.0852</v>
+        <v>0.1007</v>
       </c>
       <c r="J204" t="n">
-        <v>2.4708</v>
+        <v>2.9203</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0553</v>
+        <v>-0.0122</v>
       </c>
       <c r="J205" t="n">
-        <v>-1.6037</v>
+        <v>-0.3538</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.4636</v>
+        <v>-0.2928</v>
       </c>
       <c r="J206" t="n">
-        <v>-13.4444</v>
+        <v>-8.491199999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.3243</v>
+        <v>0.2704</v>
       </c>
       <c r="J207" t="n">
-        <v>9.4047</v>
+        <v>7.8416</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.3243</v>
+        <v>0.2704</v>
       </c>
       <c r="J208" t="n">
-        <v>9.4047</v>
+        <v>7.8416</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0461</v>
+        <v>0.0125</v>
       </c>
       <c r="J209" t="n">
-        <v>1.3369</v>
+        <v>0.3625</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.5165</v>
+        <v>-0.3357</v>
       </c>
       <c r="J210" t="n">
-        <v>-14.9785</v>
+        <v>-9.735300000000001</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.61</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.6199</v>
+        <v>-0.4107</v>
       </c>
       <c r="J211" t="n">
-        <v>-17.9771</v>
+        <v>-11.9103</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3154</v>
+        <v>0.3354</v>
       </c>
       <c r="J212" t="n">
-        <v>8.2004</v>
+        <v>8.7204</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2833</v>
+        <v>0.299</v>
       </c>
       <c r="J213" t="n">
-        <v>7.3658</v>
+        <v>7.774</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0297</v>
+        <v>-0.0402</v>
       </c>
       <c r="J214" t="n">
-        <v>-0.7722</v>
+        <v>-1.0452</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.539</v>
+        <v>-0.3524</v>
       </c>
       <c r="J215" t="n">
-        <v>-14.014</v>
+        <v>-9.1624</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.61</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.6165</v>
+        <v>-0.4085</v>
       </c>
       <c r="J216" t="n">
-        <v>-16.029</v>
+        <v>-10.621</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.8125</v>
+        <v>0.611</v>
       </c>
       <c r="J217" t="n">
-        <v>21.125</v>
+        <v>15.886</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.7175</v>
+        <v>0.5557</v>
       </c>
       <c r="J218" t="n">
-        <v>18.655</v>
+        <v>14.4482</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.25</v>
       </c>
       <c r="I219" t="n">
-        <v>0.6929</v>
+        <v>0.5417</v>
       </c>
       <c r="J219" t="n">
-        <v>18.0154</v>
+        <v>14.0842</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.08</v>
       </c>
       <c r="I220" t="n">
-        <v>0.1951</v>
+        <v>0.2534</v>
       </c>
       <c r="J220" t="n">
-        <v>5.0726</v>
+        <v>6.5884</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.93</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3784</v>
+        <v>-0.3047</v>
       </c>
       <c r="J221" t="n">
-        <v>-9.8384</v>
+        <v>-7.9222</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.174</v>
+        <v>-0.1496</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.35</v>
+        <v>-3.74</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.79</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2929</v>
+        <v>-0.2217</v>
       </c>
       <c r="J223" t="n">
-        <v>-7.3225</v>
+        <v>-5.5425</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.76</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.3557</v>
+        <v>-0.2496</v>
       </c>
       <c r="J224" t="n">
-        <v>-8.8925</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.4089</v>
+        <v>-0.2775</v>
       </c>
       <c r="J225" t="n">
-        <v>-10.2225</v>
+        <v>-6.9375</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.4713</v>
+        <v>-0.3151</v>
       </c>
       <c r="J226" t="n">
-        <v>-11.7825</v>
+        <v>-7.8775</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.65</v>
       </c>
       <c r="I227" t="n">
-        <v>1.4691</v>
+        <v>1.0328</v>
       </c>
       <c r="J227" t="n">
-        <v>36.7275</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.42</v>
       </c>
       <c r="I228" t="n">
-        <v>1.0118</v>
+        <v>0.7474</v>
       </c>
       <c r="J228" t="n">
-        <v>25.295</v>
+        <v>18.685</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.38</v>
       </c>
       <c r="I229" t="n">
-        <v>0.924</v>
+        <v>0.6963</v>
       </c>
       <c r="J229" t="n">
-        <v>23.1</v>
+        <v>17.4075</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.1529</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J230" t="n">
-        <v>-3.8225</v>
+        <v>-1.7625</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.1529</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>-3.8225</v>
+        <v>-1.7625</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.7628</v>
+        <v>1.2544</v>
       </c>
       <c r="J232" t="n">
-        <v>52.884</v>
+        <v>37.632</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4415</v>
+        <v>0.3899</v>
       </c>
       <c r="J233" t="n">
-        <v>13.245</v>
+        <v>11.697</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0808</v>
+        <v>-0.0234</v>
       </c>
       <c r="J234" t="n">
-        <v>-2.424</v>
+        <v>-0.702</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.85</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5782</v>
+        <v>-0.5178</v>
       </c>
       <c r="J235" t="n">
-        <v>-17.346</v>
+        <v>-15.534</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.844</v>
+        <v>-0.8028</v>
       </c>
       <c r="J236" t="n">
-        <v>-25.32</v>
+        <v>-24.084</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5353</v>
+        <v>0.5124</v>
       </c>
       <c r="J237" t="n">
-        <v>16.059</v>
+        <v>15.372</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0443</v>
+        <v>0.0385</v>
       </c>
       <c r="J238" t="n">
-        <v>1.329</v>
+        <v>1.155</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.226</v>
+        <v>-0.1336</v>
       </c>
       <c r="J239" t="n">
-        <v>-6.78</v>
+        <v>-4.008</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.2595</v>
+        <v>-0.1554</v>
       </c>
       <c r="J240" t="n">
-        <v>-7.785</v>
+        <v>-4.662</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.2758</v>
+        <v>-0.1662</v>
       </c>
       <c r="J241" t="n">
-        <v>-8.273999999999999</v>
+        <v>-4.986</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.9</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7885</v>
+        <v>1.2872</v>
       </c>
       <c r="J242" t="n">
-        <v>39.347</v>
+        <v>28.3184</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.84</v>
       </c>
       <c r="I243" t="n">
-        <v>1.7244</v>
+        <v>1.2191</v>
       </c>
       <c r="J243" t="n">
-        <v>37.9368</v>
+        <v>26.8202</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>1.1783</v>
+        <v>0.8711</v>
       </c>
       <c r="J244" t="n">
-        <v>25.9226</v>
+        <v>19.1642</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.065</v>
+        <v>0.1569</v>
       </c>
       <c r="J245" t="n">
-        <v>1.43</v>
+        <v>3.4518</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.4524</v>
+        <v>-0.3704</v>
       </c>
       <c r="J246" t="n">
-        <v>-9.9528</v>
+        <v>-8.1488</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.0718</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.5796</v>
+        <v>-1.9228</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.3292</v>
+        <v>-0.2629</v>
       </c>
       <c r="J248" t="n">
-        <v>-7.2424</v>
+        <v>-5.7838</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.6</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.5586</v>
+        <v>-0.3826</v>
       </c>
       <c r="J249" t="n">
-        <v>-12.2892</v>
+        <v>-8.417199999999999</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.6175</v>
+        <v>-0.4198</v>
       </c>
       <c r="J250" t="n">
-        <v>-13.585</v>
+        <v>-9.2356</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.52</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.6733</v>
+        <v>-0.4572</v>
       </c>
       <c r="J251" t="n">
-        <v>-14.8126</v>
+        <v>-10.0584</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.865</v>
+        <v>0.6284</v>
       </c>
       <c r="J252" t="n">
-        <v>35.465</v>
+        <v>25.7644</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.7235</v>
+        <v>0.5406</v>
       </c>
       <c r="J253" t="n">
-        <v>29.6635</v>
+        <v>22.1646</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1825</v>
+        <v>-0.1374</v>
       </c>
       <c r="J254" t="n">
-        <v>-7.4825</v>
+        <v>-5.6334</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2549</v>
+        <v>-0.2052</v>
       </c>
       <c r="J255" t="n">
-        <v>-10.4509</v>
+        <v>-8.4132</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8918</v>
+        <v>-0.8577</v>
       </c>
       <c r="J256" t="n">
-        <v>-36.5638</v>
+        <v>-35.1657</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5407</v>
+        <v>0.5163</v>
       </c>
       <c r="J257" t="n">
-        <v>22.1687</v>
+        <v>21.1683</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.3913</v>
+        <v>0.4</v>
       </c>
       <c r="J258" t="n">
-        <v>16.0433</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.1461</v>
+        <v>-0.0859</v>
       </c>
       <c r="J259" t="n">
-        <v>-5.9901</v>
+        <v>-3.5219</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.2545</v>
+        <v>-0.1536</v>
       </c>
       <c r="J260" t="n">
-        <v>-10.4345</v>
+        <v>-6.2976</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.6908</v>
+        <v>-0.4634</v>
       </c>
       <c r="J261" t="n">
-        <v>-28.3228</v>
+        <v>-18.9994</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.81</v>
       </c>
       <c r="I262" t="n">
-        <v>1.7249</v>
+        <v>1.2139</v>
       </c>
       <c r="J262" t="n">
-        <v>39.6727</v>
+        <v>27.9197</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.55</v>
       </c>
       <c r="I263" t="n">
-        <v>1.2592</v>
+        <v>0.9024</v>
       </c>
       <c r="J263" t="n">
-        <v>28.9616</v>
+        <v>20.7552</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7709</v>
+        <v>0.6284</v>
       </c>
       <c r="J264" t="n">
-        <v>17.7307</v>
+        <v>14.4532</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5893</v>
+        <v>0.5369</v>
       </c>
       <c r="J265" t="n">
-        <v>13.5539</v>
+        <v>12.3487</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.7</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9784</v>
+        <v>-0.9507</v>
       </c>
       <c r="J266" t="n">
-        <v>-22.5032</v>
+        <v>-21.8661</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.91</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.1459</v>
+        <v>-2.1896</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.09520000000000001</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.1459</v>
+        <v>-2.1896</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.2139</v>
+        <v>-0.1731</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.9197</v>
+        <v>-3.9813</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.5335</v>
+        <v>-0.3546</v>
       </c>
       <c r="J270" t="n">
-        <v>-12.2705</v>
+        <v>-8.155799999999999</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.6283</v>
+        <v>-0.4202</v>
       </c>
       <c r="J271" t="n">
-        <v>-14.4509</v>
+        <v>-9.6646</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.85</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.1495</v>
+        <v>-0.1412</v>
       </c>
       <c r="J272" t="n">
-        <v>-3.1395</v>
+        <v>-2.9652</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.68</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.4367</v>
+        <v>-0.3132</v>
       </c>
       <c r="J273" t="n">
-        <v>-9.1707</v>
+        <v>-6.5772</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.67</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.4571</v>
+        <v>-0.322</v>
       </c>
       <c r="J274" t="n">
-        <v>-9.5991</v>
+        <v>-6.762</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.554</v>
+        <v>-0.3769</v>
       </c>
       <c r="J275" t="n">
-        <v>-11.634</v>
+        <v>-7.9149</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.5688</v>
+        <v>-0.3862</v>
       </c>
       <c r="J276" t="n">
-        <v>-11.9448</v>
+        <v>-8.110200000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.93</v>
       </c>
       <c r="I277" t="n">
-        <v>1.8169</v>
+        <v>1.3215</v>
       </c>
       <c r="J277" t="n">
-        <v>38.1549</v>
+        <v>27.7515</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.85</v>
       </c>
       <c r="I278" t="n">
-        <v>1.7373</v>
+        <v>1.2309</v>
       </c>
       <c r="J278" t="n">
-        <v>36.4833</v>
+        <v>25.8489</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.4924</v>
+        <v>0.4941</v>
       </c>
       <c r="J279" t="n">
-        <v>10.3404</v>
+        <v>10.3761</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.19</v>
       </c>
       <c r="I280" t="n">
-        <v>0.3756</v>
+        <v>0.4223</v>
       </c>
       <c r="J280" t="n">
-        <v>7.8876</v>
+        <v>8.8683</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.06</v>
       </c>
       <c r="I281" t="n">
-        <v>0.0361</v>
+        <v>0.1265</v>
       </c>
       <c r="J281" t="n">
-        <v>0.7581</v>
+        <v>2.6565</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0411</v>
+        <v>-0.0655</v>
       </c>
       <c r="J282" t="n">
-        <v>-0.7809</v>
+        <v>-1.2445</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1731</v>
+        <v>-0.1605</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.2889</v>
+        <v>-3.0495</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.71</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3457</v>
+        <v>-0.2771</v>
       </c>
       <c r="J284" t="n">
-        <v>-6.5683</v>
+        <v>-5.2649</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.4</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.8234</v>
+        <v>-0.5659</v>
       </c>
       <c r="J285" t="n">
-        <v>-15.6446</v>
+        <v>-10.7521</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.8982</v>
+        <v>-0.6229</v>
       </c>
       <c r="J286" t="n">
-        <v>-17.0658</v>
+        <v>-11.8351</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.88</v>
       </c>
       <c r="I287" t="n">
-        <v>1.765</v>
+        <v>1.2607</v>
       </c>
       <c r="J287" t="n">
-        <v>33.535</v>
+        <v>23.9533</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.54</v>
       </c>
       <c r="I288" t="n">
-        <v>1.1687</v>
+        <v>0.869</v>
       </c>
       <c r="J288" t="n">
-        <v>22.2053</v>
+        <v>16.511</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>0.9765</v>
+        <v>0.7758</v>
       </c>
       <c r="J289" t="n">
-        <v>18.5535</v>
+        <v>14.7402</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.42</v>
       </c>
       <c r="I290" t="n">
-        <v>0.8845</v>
+        <v>0.7277</v>
       </c>
       <c r="J290" t="n">
-        <v>16.8055</v>
+        <v>13.8263</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.07</v>
       </c>
       <c r="I291" t="n">
-        <v>0.0609</v>
+        <v>0.1532</v>
       </c>
       <c r="J291" t="n">
-        <v>1.1571</v>
+        <v>2.9108</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1833</v>
+        <v>0.1445</v>
       </c>
       <c r="J292" t="n">
-        <v>6.2322</v>
+        <v>4.913</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1245</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="J293" t="n">
-        <v>4.233</v>
+        <v>3.1382</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.1028</v>
+        <v>0.0735</v>
       </c>
       <c r="J294" t="n">
-        <v>3.4952</v>
+        <v>2.499</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1658</v>
+        <v>-0.0978</v>
       </c>
       <c r="J295" t="n">
-        <v>-5.6372</v>
+        <v>-3.3252</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.3488</v>
+        <v>-0.2163</v>
       </c>
       <c r="J296" t="n">
-        <v>-11.8592</v>
+        <v>-7.3542</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.32</v>
       </c>
       <c r="I297" t="n">
-        <v>0.5187</v>
+        <v>0.3984</v>
       </c>
       <c r="J297" t="n">
-        <v>17.6358</v>
+        <v>13.5456</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.19</v>
       </c>
       <c r="I298" t="n">
-        <v>0.3395</v>
+        <v>0.2831</v>
       </c>
       <c r="J298" t="n">
-        <v>11.543</v>
+        <v>9.625400000000001</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>-0.0062</v>
+        <v>0.018</v>
       </c>
       <c r="J299" t="n">
-        <v>-0.2108</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.1003</v>
+        <v>-0.0441</v>
       </c>
       <c r="J300" t="n">
-        <v>-3.4102</v>
+        <v>-1.4994</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.217</v>
+        <v>-0.1207</v>
       </c>
       <c r="J301" t="n">
-        <v>-7.378</v>
+        <v>-4.1038</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.5273</v>
+        <v>0.436</v>
       </c>
       <c r="J302" t="n">
-        <v>15.2917</v>
+        <v>12.644</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4718</v>
+        <v>0.4056</v>
       </c>
       <c r="J303" t="n">
-        <v>13.6822</v>
+        <v>11.7624</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.4133</v>
+        <v>0.3747</v>
       </c>
       <c r="J304" t="n">
-        <v>11.9857</v>
+        <v>10.8663</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.09</v>
       </c>
       <c r="I305" t="n">
-        <v>0.272</v>
+        <v>0.2958</v>
       </c>
       <c r="J305" t="n">
-        <v>7.888</v>
+        <v>8.578200000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.2566</v>
+        <v>-0.1909</v>
       </c>
       <c r="J306" t="n">
-        <v>-7.4414</v>
+        <v>-5.5361</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.29</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5195</v>
+        <v>0.499</v>
       </c>
       <c r="J307" t="n">
-        <v>15.0655</v>
+        <v>14.471</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.03</v>
       </c>
       <c r="I308" t="n">
-        <v>0.109</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="J308" t="n">
-        <v>3.161</v>
+        <v>2.8739</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.86</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.2827</v>
+        <v>-0.1733</v>
       </c>
       <c r="J309" t="n">
-        <v>-8.1983</v>
+        <v>-5.0257</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.84</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.3144</v>
+        <v>-0.1941</v>
       </c>
       <c r="J310" t="n">
-        <v>-9.117599999999999</v>
+        <v>-5.6289</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.3747</v>
+        <v>-0.2348</v>
       </c>
       <c r="J311" t="n">
-        <v>-10.8663</v>
+        <v>-6.8092</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.8077</v>
+        <v>0.5986</v>
       </c>
       <c r="J312" t="n">
-        <v>24.231</v>
+        <v>17.958</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.5607</v>
+        <v>0.4528</v>
       </c>
       <c r="J313" t="n">
-        <v>16.821</v>
+        <v>13.584</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.4213</v>
+        <v>0.3761</v>
       </c>
       <c r="J314" t="n">
-        <v>12.639</v>
+        <v>11.283</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.212</v>
+        <v>0.2402</v>
       </c>
       <c r="J315" t="n">
-        <v>6.36</v>
+        <v>7.206</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.79</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.7237</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="J316" t="n">
-        <v>-21.711</v>
+        <v>-20.187</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.41</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.6041</v>
       </c>
       <c r="J317" t="n">
-        <v>19.461</v>
+        <v>18.123</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.4</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6366000000000001</v>
+        <v>0.5943000000000001</v>
       </c>
       <c r="J318" t="n">
-        <v>19.098</v>
+        <v>17.829</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1621</v>
+        <v>0.1779</v>
       </c>
       <c r="J319" t="n">
-        <v>4.863</v>
+        <v>5.337</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.74</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.4726</v>
+        <v>-0.3011</v>
       </c>
       <c r="J320" t="n">
-        <v>-14.178</v>
+        <v>-9.032999999999999</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.52</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.7439</v>
+        <v>-0.5041</v>
       </c>
       <c r="J321" t="n">
-        <v>-22.317</v>
+        <v>-15.123</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.35</v>
       </c>
       <c r="I322" t="n">
-        <v>0.537</v>
+        <v>0.4115</v>
       </c>
       <c r="J322" t="n">
-        <v>15.573</v>
+        <v>11.9335</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.28</v>
       </c>
       <c r="I323" t="n">
-        <v>0.4453</v>
+        <v>0.3632</v>
       </c>
       <c r="J323" t="n">
-        <v>12.9137</v>
+        <v>10.5328</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.09</v>
       </c>
       <c r="I324" t="n">
-        <v>0.135</v>
+        <v>0.1439</v>
       </c>
       <c r="J324" t="n">
-        <v>3.915</v>
+        <v>4.1731</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0216</v>
+        <v>0.049</v>
       </c>
       <c r="J325" t="n">
-        <v>0.6264</v>
+        <v>1.421</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0347</v>
       </c>
       <c r="J326" t="n">
-        <v>-2.6912</v>
+        <v>-1.0063</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0366</v>
       </c>
       <c r="J327" t="n">
-        <v>1.9749</v>
+        <v>1.0614</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.0328</v>
+        <v>0.0069</v>
       </c>
       <c r="J328" t="n">
-        <v>0.9512</v>
+        <v>0.2001</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.99</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0028</v>
+        <v>-0.0161</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.4669</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.9</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.208</v>
+        <v>-0.1284</v>
       </c>
       <c r="J330" t="n">
-        <v>-6.032</v>
+        <v>-3.7236</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.83</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.3245</v>
+        <v>-0.2022</v>
       </c>
       <c r="J331" t="n">
-        <v>-9.410500000000001</v>
+        <v>-5.8638</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.13</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3269</v>
+        <v>0.3444</v>
       </c>
       <c r="J332" t="n">
-        <v>8.4994</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1485</v>
+        <v>0.1272</v>
       </c>
       <c r="J333" t="n">
-        <v>3.861</v>
+        <v>3.3072</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.79</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.3597</v>
+        <v>-0.2328</v>
       </c>
       <c r="J334" t="n">
-        <v>-9.3522</v>
+        <v>-6.0528</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.491</v>
+        <v>-0.32</v>
       </c>
       <c r="J335" t="n">
-        <v>-12.766</v>
+        <v>-8.32</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.5048</v>
+        <v>-0.3295</v>
       </c>
       <c r="J336" t="n">
-        <v>-13.1248</v>
+        <v>-8.567</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.37</v>
       </c>
       <c r="I337" t="n">
-        <v>0.9474</v>
+        <v>0.6973</v>
       </c>
       <c r="J337" t="n">
-        <v>24.6324</v>
+        <v>18.1298</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.34</v>
       </c>
       <c r="I338" t="n">
-        <v>0.8807</v>
+        <v>0.6575</v>
       </c>
       <c r="J338" t="n">
-        <v>22.8982</v>
+        <v>17.095</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.25</v>
       </c>
       <c r="I339" t="n">
-        <v>0.6656</v>
+        <v>0.5356</v>
       </c>
       <c r="J339" t="n">
-        <v>17.3056</v>
+        <v>13.9256</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3464</v>
+        <v>0.3787</v>
       </c>
       <c r="J340" t="n">
-        <v>9.006399999999999</v>
+        <v>9.8462</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.93</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3922</v>
+        <v>-0.3154</v>
       </c>
       <c r="J341" t="n">
-        <v>-10.1972</v>
+        <v>-8.2004</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I342" t="n">
-        <v>0.1678</v>
+        <v>0.1513</v>
       </c>
       <c r="J342" t="n">
-        <v>4.3628</v>
+        <v>3.9338</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0293</v>
       </c>
       <c r="J343" t="n">
-        <v>1.6822</v>
+        <v>0.7618</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.2215</v>
+        <v>-0.1532</v>
       </c>
       <c r="J344" t="n">
-        <v>-5.759</v>
+        <v>-3.9832</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.2427</v>
+        <v>-0.1632</v>
       </c>
       <c r="J345" t="n">
-        <v>-6.3102</v>
+        <v>-4.2432</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.59</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.6367</v>
+        <v>-0.4238</v>
       </c>
       <c r="J346" t="n">
-        <v>-16.5542</v>
+        <v>-11.0188</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.66</v>
       </c>
       <c r="I347" t="n">
-        <v>1.5309</v>
+        <v>1.0699</v>
       </c>
       <c r="J347" t="n">
-        <v>39.8034</v>
+        <v>27.8174</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.2661</v>
+        <v>0.3281</v>
       </c>
       <c r="J348" t="n">
-        <v>6.9186</v>
+        <v>8.5306</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.11</v>
       </c>
       <c r="I349" t="n">
-        <v>0.2661</v>
+        <v>0.3281</v>
       </c>
       <c r="J349" t="n">
-        <v>6.9186</v>
+        <v>8.5306</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.08</v>
       </c>
       <c r="I350" t="n">
-        <v>0.1781</v>
+        <v>0.2453</v>
       </c>
       <c r="J350" t="n">
-        <v>4.6306</v>
+        <v>6.3778</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.03</v>
       </c>
       <c r="I351" t="n">
-        <v>0.0157</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>0.4082</v>
+        <v>2.21</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4162/event_4162_evp_summary.xlsx
+++ b/database/event/4162/event_4162_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.2112</v>
+        <v>7.5044</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0206</v>
+        <v>1.0621</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6175</v>
+        <v>2.792</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2112</v>
+        <v>7.5044</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3078</v>
+        <v>2.31</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9034</v>
+        <v>5.1943</v>
       </c>
       <c r="H2" t="n">
-        <v>2.3078</v>
+        <v>2.331</v>
       </c>
       <c r="I2" t="n">
-        <v>2.5015</v>
+        <v>2.4527</v>
       </c>
       <c r="J2" t="n">
-        <v>4.9034</v>
+        <v>5.1943</v>
       </c>
       <c r="K2" t="n">
         <v>66</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.4049</v>
+        <v>7.647</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4352</v>
+        <v>5.5518</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7692</v>
+        <v>0.7857</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8157</v>
+        <v>1.9031</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4352</v>
+        <v>5.5518</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2035</v>
+        <v>2.2081</v>
       </c>
       <c r="G3" t="n">
-        <v>3.2317</v>
+        <v>3.3437</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2035</v>
+        <v>2.2081</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3885</v>
+        <v>2.3234</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2317</v>
+        <v>3.3437</v>
       </c>
       <c r="K3" t="n">
         <v>66</v>
@@ -575,7 +575,7 @@
         <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>5.620200000000001</v>
+        <v>5.6671</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.308</v>
+        <v>5.3166</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7512</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7583</v>
+        <v>1.796</v>
       </c>
       <c r="E4" t="n">
-        <v>5.308</v>
+        <v>5.3166</v>
       </c>
       <c r="F4" t="n">
-        <v>3.1044</v>
+        <v>2.908</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2036</v>
+        <v>2.4086</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4569</v>
+        <v>3.6399</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0617</v>
+        <v>4.0298</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2036</v>
+        <v>2.4086</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>275</v>
       </c>
       <c r="M4" t="n">
-        <v>6.2653</v>
+        <v>6.4384</v>
       </c>
       <c r="N4" t="n">
         <v>390</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8899</v>
+        <v>4.8619</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6921</v>
+        <v>0.6881</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5695</v>
+        <v>1.589</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8899</v>
+        <v>4.8619</v>
       </c>
       <c r="F5" t="n">
-        <v>2.7179</v>
+        <v>2.5159</v>
       </c>
       <c r="G5" t="n">
-        <v>2.172</v>
+        <v>2.346</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7179</v>
+        <v>2.7815</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9461</v>
+        <v>2.9267</v>
       </c>
       <c r="J5" t="n">
-        <v>2.172</v>
+        <v>2.346</v>
       </c>
       <c r="K5" t="n">
         <v>66</v>
@@ -667,7 +667,7 @@
         <v>200</v>
       </c>
       <c r="M5" t="n">
-        <v>5.1181</v>
+        <v>5.2727</v>
       </c>
       <c r="N5" t="n">
         <v>266</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3894</v>
+        <v>4.2774</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6212</v>
+        <v>0.6054</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3436</v>
+        <v>1.323</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3894</v>
+        <v>4.2774</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0593</v>
+        <v>2.8541</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3301</v>
+        <v>1.4233</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3579</v>
+        <v>3.5219</v>
       </c>
       <c r="I6" t="n">
-        <v>3.9453</v>
+        <v>3.8992</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3301</v>
+        <v>1.4233</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>275</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2754</v>
+        <v>5.3225</v>
       </c>
       <c r="N6" t="n">
         <v>390</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.1101</v>
+        <v>4.2278</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5817</v>
+        <v>0.5984</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2175</v>
+        <v>1.3004</v>
       </c>
       <c r="E7" t="n">
-        <v>4.1101</v>
+        <v>4.2278</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8027</v>
+        <v>1.7055</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3074</v>
+        <v>2.5223</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8027</v>
+        <v>1.7055</v>
       </c>
       <c r="I7" t="n">
-        <v>1.954</v>
+        <v>1.7945</v>
       </c>
       <c r="J7" t="n">
-        <v>2.3074</v>
+        <v>2.5223</v>
       </c>
       <c r="K7" t="n">
         <v>162</v>
@@ -759,7 +759,7 @@
         <v>163</v>
       </c>
       <c r="M7" t="n">
-        <v>4.2614</v>
+        <v>4.3168</v>
       </c>
       <c r="N7" t="n">
         <v>325</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8283</v>
+        <v>3.9975</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5658</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0903</v>
+        <v>1.1955</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8283</v>
+        <v>3.9975</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0998</v>
+        <v>1.0013</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7285</v>
+        <v>2.9962</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0998</v>
+        <v>1.0013</v>
       </c>
       <c r="I8" t="n">
-        <v>1.145</v>
+        <v>1.0271</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7285</v>
+        <v>2.9962</v>
       </c>
       <c r="K8" t="n">
         <v>113</v>
@@ -805,7 +805,7 @@
         <v>144</v>
       </c>
       <c r="M8" t="n">
-        <v>3.8735</v>
+        <v>4.0233</v>
       </c>
       <c r="N8" t="n">
         <v>257</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.7458</v>
+        <v>3.824</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5301</v>
+        <v>0.5412</v>
       </c>
       <c r="D9" t="n">
-        <v>1.053</v>
+        <v>1.1166</v>
       </c>
       <c r="E9" t="n">
-        <v>3.7458</v>
+        <v>3.824</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1888</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>3.557</v>
+        <v>3.824</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1888</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2047</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.557</v>
+        <v>3.824</v>
       </c>
       <c r="K9" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7617</v>
+        <v>3.824</v>
       </c>
       <c r="N9" t="n">
-        <v>266</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.5099</v>
+        <v>3.779</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4968</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9465</v>
+        <v>1.0961</v>
       </c>
       <c r="E10" t="n">
-        <v>3.5099</v>
+        <v>3.779</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5099</v>
+        <v>3.5939</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.1851</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.1948</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5099</v>
+        <v>3.5939</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="L10" t="n">
-        <v>174</v>
+        <v>200</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5099</v>
+        <v>3.7887</v>
       </c>
       <c r="N10" t="n">
-        <v>174</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.1169</v>
+        <v>3.2973</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4411</v>
+        <v>0.4667</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7691</v>
+        <v>0.8768</v>
       </c>
       <c r="E11" t="n">
-        <v>3.1169</v>
+        <v>3.2973</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3096</v>
+        <v>1.2772</v>
       </c>
       <c r="G11" t="n">
-        <v>1.8073</v>
+        <v>2.0201</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3096</v>
+        <v>1.2772</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4195</v>
+        <v>1.3439</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8073</v>
+        <v>2.0201</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -943,7 +943,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="n">
-        <v>3.2268</v>
+        <v>3.364</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.6777</v>
+        <v>2.8741</v>
       </c>
       <c r="C12" t="n">
-        <v>0.379</v>
+        <v>0.4068</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5708</v>
+        <v>0.6841</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6777</v>
+        <v>2.8741</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2722</v>
+        <v>1.3461</v>
       </c>
       <c r="G12" t="n">
-        <v>1.4055</v>
+        <v>1.528</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2722</v>
+        <v>1.3461</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4947</v>
+        <v>1.4903</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4055</v>
+        <v>1.528</v>
       </c>
       <c r="K12" t="n">
         <v>115</v>
@@ -989,7 +989,7 @@
         <v>275</v>
       </c>
       <c r="M12" t="n">
-        <v>2.9002</v>
+        <v>3.0183</v>
       </c>
       <c r="N12" t="n">
         <v>390</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4932</v>
+        <v>2.6531</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3529</v>
+        <v>0.3755</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4875</v>
+        <v>0.5835</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4932</v>
+        <v>2.6531</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2738</v>
+        <v>1.3381</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2194</v>
+        <v>1.315</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2738</v>
+        <v>1.3381</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4966</v>
+        <v>1.4814</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2194</v>
+        <v>1.315</v>
       </c>
       <c r="K13" t="n">
         <v>115</v>
@@ -1035,7 +1035,7 @@
         <v>275</v>
       </c>
       <c r="M13" t="n">
-        <v>2.716</v>
+        <v>2.7964</v>
       </c>
       <c r="N13" t="n">
         <v>390</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="C14" t="n">
-        <v>0.313</v>
+        <v>0.3464</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3604</v>
+        <v>0.4899</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2116</v>
+        <v>2.4475</v>
       </c>
       <c r="N14" t="n">
         <v>174</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7603</v>
+        <v>1.7624</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2491</v>
+        <v>0.2494</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1567</v>
+        <v>0.1781</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7603</v>
+        <v>1.7624</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4171</v>
+        <v>1.3824</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3432</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4171</v>
+        <v>1.3824</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4754</v>
+        <v>1.418</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3432</v>
+        <v>0.38</v>
       </c>
       <c r="K15" t="n">
         <v>94</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8186</v>
+        <v>1.798</v>
       </c>
       <c r="N15" t="n">
         <v>158</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2721</v>
+        <v>1.4294</v>
       </c>
       <c r="C16" t="n">
-        <v>0.18</v>
+        <v>0.2023</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.06370000000000001</v>
+        <v>0.0265</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2721</v>
+        <v>1.4294</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2721</v>
+        <v>1.4294</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2721</v>
+        <v>1.4294</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>174</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2721</v>
+        <v>1.4294</v>
       </c>
       <c r="N16" t="n">
         <v>174</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.2691</v>
+        <v>1.3006</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1796</v>
+        <v>0.1841</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.06510000000000001</v>
+        <v>-0.0321</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2691</v>
+        <v>1.3006</v>
       </c>
       <c r="F17" t="n">
-        <v>1.063</v>
+        <v>1.0454</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2061</v>
+        <v>0.2552</v>
       </c>
       <c r="H17" t="n">
-        <v>1.063</v>
+        <v>1.0454</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1522</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2061</v>
+        <v>0.2552</v>
       </c>
       <c r="K17" t="n">
         <v>162</v>
@@ -1219,7 +1219,7 @@
         <v>163</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3583</v>
+        <v>1.3552</v>
       </c>
       <c r="N17" t="n">
         <v>325</v>
@@ -1232,31 +1232,31 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.1152</v>
+        <v>1.2466</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1578</v>
+        <v>0.1764</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1346</v>
+        <v>-0.0567</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1152</v>
+        <v>1.2466</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9225</v>
+        <v>-0.9946</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0377</v>
+        <v>2.2411</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9225</v>
+        <v>-0.9946</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.9604</v>
+        <v>-1.0202</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0377</v>
+        <v>2.2411</v>
       </c>
       <c r="K18" t="n">
         <v>113</v>
@@ -1265,7 +1265,7 @@
         <v>144</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0773</v>
+        <v>1.2209</v>
       </c>
       <c r="N18" t="n">
         <v>257</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8809</v>
+        <v>0.9581</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1247</v>
+        <v>0.1356</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2403</v>
+        <v>-0.1881</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8809</v>
+        <v>0.9581</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4183</v>
+        <v>0.4226</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4626</v>
+        <v>0.5355</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4183</v>
+        <v>0.4226</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4534</v>
+        <v>0.4447</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4626</v>
+        <v>0.5355</v>
       </c>
       <c r="K19" t="n">
         <v>57</v>
@@ -1311,7 +1311,7 @@
         <v>152</v>
       </c>
       <c r="M19" t="n">
-        <v>0.916</v>
+        <v>0.9802</v>
       </c>
       <c r="N19" t="n">
         <v>209</v>
@@ -1320,93 +1320,93 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>ANDROID</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.8509</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1092</v>
+        <v>0.1204</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2896</v>
+        <v>-0.2369</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.8509</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4669</v>
+        <v>-0.9048</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3048</v>
+        <v>1.7557</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4669</v>
+        <v>-0.9048</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4861</v>
+        <v>-0.952</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3048</v>
+        <v>1.7557</v>
       </c>
       <c r="K20" t="n">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="L20" t="n">
-        <v>64</v>
+        <v>163</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7908999999999999</v>
+        <v>0.8037000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>158</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ANDROID</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7346</v>
+        <v>0.7887</v>
       </c>
       <c r="C21" t="n">
-        <v>0.104</v>
+        <v>0.1116</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3064</v>
+        <v>-0.2652</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7346</v>
+        <v>0.7887</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8611</v>
+        <v>0.4665</v>
       </c>
       <c r="G21" t="n">
-        <v>1.5957</v>
+        <v>0.3222</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8611</v>
+        <v>0.4665</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9334</v>
+        <v>0.4785</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5957</v>
+        <v>0.3222</v>
       </c>
       <c r="K21" t="n">
-        <v>162</v>
+        <v>94</v>
       </c>
       <c r="L21" t="n">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6622999999999999</v>
+        <v>0.8007</v>
       </c>
       <c r="N21" t="n">
-        <v>325</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4115</v>
+        <v>0.546</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0582</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4522</v>
+        <v>-0.3757</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4115</v>
+        <v>0.546</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4115</v>
+        <v>0.546</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4115</v>
+        <v>0.546</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>174</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4115</v>
+        <v>0.546</v>
       </c>
       <c r="N22" t="n">
         <v>174</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3595</v>
+        <v>0.4433</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0509</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4757</v>
+        <v>-0.4224</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3595</v>
+        <v>0.4433</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3595</v>
+        <v>0.4433</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.3595</v>
+        <v>0.4433</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>174</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3595</v>
+        <v>0.4433</v>
       </c>
       <c r="N23" t="n">
         <v>174</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2152</v>
+        <v>0.1706</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0305</v>
+        <v>0.0241</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5409</v>
+        <v>-0.5465</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2152</v>
+        <v>0.1706</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6576</v>
+        <v>0.6586</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4424</v>
+        <v>-0.488</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6576</v>
+        <v>0.6586</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6576</v>
+        <v>0.6586</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.4424</v>
+        <v>-0.488</v>
       </c>
       <c r="K24" t="n">
         <v>57</v>
@@ -1541,7 +1541,7 @@
         <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2151999999999999</v>
+        <v>0.1706</v>
       </c>
       <c r="N24" t="n">
         <v>97</v>
@@ -1550,219 +1550,219 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>reatz</t>
+          <t>Snappi</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1442</v>
+        <v>0.1326</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0204</v>
+        <v>0.0188</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5729</v>
+        <v>-0.5638</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1442</v>
+        <v>0.1326</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4459</v>
+        <v>-0.0835</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.3017</v>
+        <v>0.2161</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4459</v>
+        <v>-0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4459</v>
+        <v>-0.0925</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.3017</v>
+        <v>0.2161</v>
       </c>
       <c r="K25" t="n">
-        <v>57</v>
+        <v>115</v>
       </c>
       <c r="L25" t="n">
-        <v>40</v>
+        <v>275</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1442</v>
+        <v>0.1236</v>
       </c>
       <c r="N25" t="n">
-        <v>97</v>
+        <v>390</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dephh</t>
+          <t>reatz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.04</v>
+        <v>0.0733</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0057</v>
+        <v>0.0104</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.62</v>
+        <v>-0.5908</v>
       </c>
       <c r="E26" t="n">
-        <v>0.04</v>
+        <v>0.0733</v>
       </c>
       <c r="F26" t="n">
-        <v>1.377</v>
+        <v>0.4258</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.337</v>
+        <v>-0.3525</v>
       </c>
       <c r="H26" t="n">
-        <v>1.377</v>
+        <v>0.4258</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4926</v>
+        <v>0.4258</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.337</v>
+        <v>-0.3525</v>
       </c>
       <c r="K26" t="n">
-        <v>162</v>
+        <v>57</v>
       </c>
       <c r="L26" t="n">
-        <v>163</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1556</v>
+        <v>0.07330000000000003</v>
       </c>
       <c r="N26" t="n">
-        <v>325</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Snappi</t>
+          <t>dephh</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0124</v>
+        <v>0.0065</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0018</v>
+        <v>0.0009</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-0.6212</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0124</v>
+        <v>0.0065</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1308</v>
+        <v>1.3638</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1184</v>
+        <v>-1.3573</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1308</v>
+        <v>1.3638</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.1537</v>
+        <v>1.435</v>
       </c>
       <c r="J27" t="n">
-        <v>0.1184</v>
+        <v>-1.3573</v>
       </c>
       <c r="K27" t="n">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="L27" t="n">
-        <v>275</v>
+        <v>163</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0353</v>
+        <v>0.0777000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>390</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>nex</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0548</v>
+        <v>-0.0591</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0078</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.6511</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0548</v>
+        <v>-0.0591</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3156</v>
+        <v>-0.7649</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.3704</v>
+        <v>0.7058</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3156</v>
+        <v>-0.7649</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3421</v>
+        <v>-0.7846</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3704</v>
+        <v>0.7058</v>
       </c>
       <c r="K28" t="n">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="L28" t="n">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02829999999999999</v>
+        <v>-0.07879999999999998</v>
       </c>
       <c r="N28" t="n">
-        <v>209</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Subroza</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1248</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0177</v>
+        <v>-0.0136</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6944</v>
+        <v>-0.668</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1248</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5641</v>
+        <v>0.3166</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6889</v>
+        <v>-0.4128</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5641</v>
+        <v>0.3166</v>
       </c>
       <c r="I29" t="n">
-        <v>0.6114000000000001</v>
+        <v>0.3331</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6889</v>
+        <v>-0.4128</v>
       </c>
       <c r="K29" t="n">
         <v>57</v>
@@ -1771,7 +1771,7 @@
         <v>152</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.0774999999999999</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>209</v>
@@ -1780,47 +1780,47 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nex</t>
+          <t>Subroza</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2001</v>
+        <v>-0.1318</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0283</v>
+        <v>-0.0187</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7282999999999999</v>
+        <v>-0.6842</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2001</v>
+        <v>-0.1318</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.6902</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4901</v>
+        <v>-0.716</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6902</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.7186</v>
+        <v>0.6147</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4901</v>
+        <v>-0.716</v>
       </c>
       <c r="K30" t="n">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="L30" t="n">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2285</v>
+        <v>-0.1012999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>257</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31">
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.212</v>
+        <v>-0.243</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.03</v>
+        <v>-0.0344</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7337</v>
+        <v>-0.7348</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.212</v>
+        <v>-0.243</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0309</v>
+        <v>-0.0317</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.1811</v>
+        <v>-0.2113</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0309</v>
+        <v>-0.0317</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0322</v>
+        <v>-0.0325</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.1811</v>
+        <v>-0.2113</v>
       </c>
       <c r="K31" t="n">
         <v>94</v>
@@ -1863,7 +1863,7 @@
         <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2133</v>
+        <v>-0.2438</v>
       </c>
       <c r="N31" t="n">
         <v>158</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.2759</v>
+        <v>-0.3235</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.039</v>
+        <v>-0.0458</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7625999999999999</v>
+        <v>-0.7715</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.2759</v>
+        <v>-0.3235</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2323</v>
+        <v>0.2145</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.5082</v>
+        <v>-0.538</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2323</v>
+        <v>0.2145</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2419</v>
+        <v>0.22</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.5082</v>
+        <v>-0.538</v>
       </c>
       <c r="K32" t="n">
         <v>94</v>
@@ -1909,7 +1909,7 @@
         <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.2663</v>
+        <v>-0.3180000000000001</v>
       </c>
       <c r="N32" t="n">
         <v>158</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.571</v>
+        <v>-0.5292</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0808</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8958</v>
+        <v>-0.8651</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.571</v>
+        <v>-0.5292</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2039</v>
+        <v>-0.1781</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3671</v>
+        <v>-0.3511</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.2039</v>
+        <v>-0.1781</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.221</v>
+        <v>-0.1874</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3671</v>
+        <v>-0.3511</v>
       </c>
       <c r="K33" t="n">
         <v>57</v>
@@ -1955,7 +1955,7 @@
         <v>152</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5881</v>
+        <v>-0.5385</v>
       </c>
       <c r="N33" t="n">
         <v>209</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6249</v>
+        <v>-0.6086</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.08840000000000001</v>
+        <v>-0.0861</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9201</v>
+        <v>-0.9013</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6249</v>
+        <v>-0.6086</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9086</v>
+        <v>-0.9545</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2837</v>
+        <v>0.3459</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9086</v>
+        <v>-0.9545</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9849</v>
+        <v>-1.0043</v>
       </c>
       <c r="J34" t="n">
-        <v>0.2837</v>
+        <v>0.3459</v>
       </c>
       <c r="K34" t="n">
         <v>162</v>
@@ -2001,7 +2001,7 @@
         <v>163</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7012</v>
+        <v>-0.6584</v>
       </c>
       <c r="N34" t="n">
         <v>325</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7013</v>
+        <v>-0.7265</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0993</v>
+        <v>-0.1028</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9546</v>
+        <v>-0.9549</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7013</v>
+        <v>-0.7265</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1823</v>
+        <v>0.1767</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.9032</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1823</v>
+        <v>0.1767</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1898</v>
+        <v>0.1813</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-0.9032</v>
       </c>
       <c r="K35" t="n">
         <v>94</v>
@@ -2047,7 +2047,7 @@
         <v>64</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.6938000000000001</v>
+        <v>-0.7219</v>
       </c>
       <c r="N35" t="n">
         <v>158</v>
@@ -2060,31 +2060,31 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8398</v>
+        <v>-0.8729</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1189</v>
+        <v>-0.1235</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0171</v>
+        <v>-1.0216</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8398</v>
+        <v>-0.8729</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0481</v>
+        <v>0.042</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.8879</v>
+        <v>-0.9149</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0481</v>
+        <v>0.042</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0481</v>
+        <v>0.042</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8879</v>
+        <v>-0.9149</v>
       </c>
       <c r="K36" t="n">
         <v>57</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8398</v>
+        <v>-0.8729</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2106,31 +2106,31 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8529</v>
+        <v>-0.9095</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1207</v>
+        <v>-0.1287</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0231</v>
+        <v>-1.0382</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8529</v>
+        <v>-0.9095</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.1896</v>
+        <v>-0.206</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.6633</v>
+        <v>-0.7035</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.1896</v>
+        <v>-0.206</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1896</v>
+        <v>-0.206</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.6633</v>
+        <v>-0.7035</v>
       </c>
       <c r="K37" t="n">
         <v>57</v>
@@ -2139,7 +2139,7 @@
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8529</v>
+        <v>-0.9095</v>
       </c>
       <c r="N37" t="n">
         <v>97</v>
@@ -2152,31 +2152,31 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0126</v>
+        <v>-0.9202</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1433</v>
+        <v>-0.1302</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0952</v>
+        <v>-1.0431</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0126</v>
+        <v>-0.9202</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.1904</v>
+        <v>-1.2517</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1778</v>
+        <v>0.3315</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.1904</v>
+        <v>-1.2517</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2394</v>
+        <v>-1.284</v>
       </c>
       <c r="J38" t="n">
-        <v>0.1778</v>
+        <v>0.3315</v>
       </c>
       <c r="K38" t="n">
         <v>113</v>
@@ -2185,7 +2185,7 @@
         <v>144</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0616</v>
+        <v>-0.9525</v>
       </c>
       <c r="N38" t="n">
         <v>257</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.0838</v>
+        <v>-0.9555</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1534</v>
+        <v>-0.1352</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1273</v>
+        <v>-1.0592</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.0838</v>
+        <v>-0.9555</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9047</v>
+        <v>-1.9498</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8209</v>
+        <v>0.9943</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9047</v>
+        <v>-1.9498</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.983</v>
+        <v>-2</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8209</v>
+        <v>0.9943</v>
       </c>
       <c r="K39" t="n">
         <v>113</v>
@@ -2231,7 +2231,7 @@
         <v>144</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1621</v>
+        <v>-1.0057</v>
       </c>
       <c r="N39" t="n">
         <v>257</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.438</v>
+        <v>-1.4874</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2035</v>
+        <v>-0.2105</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2872</v>
+        <v>-1.3013</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.438</v>
+        <v>-1.4874</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5019</v>
+        <v>-0.5286</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9361</v>
+        <v>-0.9588</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5019</v>
+        <v>-0.5286</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5019</v>
+        <v>-0.5286</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9361</v>
+        <v>-0.9588</v>
       </c>
       <c r="K40" t="n">
         <v>57</v>
@@ -2277,7 +2277,7 @@
         <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.438</v>
+        <v>-1.4874</v>
       </c>
       <c r="N40" t="n">
         <v>97</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8892</v>
+        <v>-1.6771</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2674</v>
+        <v>-0.2374</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4909</v>
+        <v>-1.3877</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8892</v>
+        <v>-1.6771</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.1141</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.9674</v>
+        <v>-1.7912</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.1141</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0848</v>
+        <v>0.1201</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.9674</v>
+        <v>-1.7912</v>
       </c>
       <c r="K41" t="n">
         <v>66</v>
@@ -2323,7 +2323,7 @@
         <v>200</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.8826</v>
+        <v>-1.6711</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9534</v>
+        <v>0.8872</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9534</v>
+        <v>0.8872</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9091</v>
+        <v>0.8462</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9091</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1157</v>
+        <v>0.1257</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1157</v>
+        <v>0.1257</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3407</v>
+        <v>-0.3297</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3407</v>
+        <v>-0.3297</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7703</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7703</v>
+        <v>-0.7151999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5619</v>
+        <v>0.5507</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5619</v>
+        <v>0.5507</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1934</v>
+        <v>0.2042</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1934</v>
+        <v>0.2042</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1306</v>
+        <v>0.1417</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1306</v>
+        <v>0.1417</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0839</v>
+        <v>0.0944</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0839</v>
+        <v>0.0944</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1842</v>
+        <v>-0.1962</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1842</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8579</v>
+        <v>0.8307</v>
       </c>
       <c r="J12" t="n">
-        <v>25.737</v>
+        <v>24.921</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.21</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3131</v>
+        <v>0.3259</v>
       </c>
       <c r="J13" t="n">
-        <v>9.393000000000001</v>
+        <v>9.776999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.17</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2601</v>
+        <v>0.2748</v>
       </c>
       <c r="J14" t="n">
-        <v>7.803</v>
+        <v>8.244</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1894</v>
+        <v>0.2059</v>
       </c>
       <c r="J15" t="n">
-        <v>5.682</v>
+        <v>6.177</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0429</v>
+        <v>-0.0425</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.287</v>
+        <v>-1.275</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1545</v>
+        <v>0.1604</v>
       </c>
       <c r="J17" t="n">
-        <v>4.635</v>
+        <v>4.812</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0177</v>
+        <v>0.0133</v>
       </c>
       <c r="J18" t="n">
-        <v>0.531</v>
+        <v>0.399</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.185</v>
+        <v>-0.2015</v>
       </c>
       <c r="J19" t="n">
-        <v>-5.55</v>
+        <v>-6.045</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1951</v>
+        <v>-0.2117</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.853</v>
+        <v>-6.351</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3319</v>
+        <v>-0.346</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.957000000000001</v>
+        <v>-10.38</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.13</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8466</v>
+        <v>1.8453</v>
       </c>
       <c r="J22" t="n">
-        <v>44.3184</v>
+        <v>44.2872</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7411</v>
+        <v>0.7127</v>
       </c>
       <c r="J23" t="n">
-        <v>17.7864</v>
+        <v>17.1048</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6254</v>
+        <v>0.61</v>
       </c>
       <c r="J24" t="n">
-        <v>15.0096</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3484</v>
+        <v>0.3606</v>
       </c>
       <c r="J25" t="n">
-        <v>8.361599999999999</v>
+        <v>8.654400000000001</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0314</v>
+        <v>-0.0002</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7536</v>
+        <v>-0.0048</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1381</v>
+        <v>0.1167</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3144</v>
+        <v>2.8008</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1943</v>
+        <v>-0.2157</v>
       </c>
       <c r="J28" t="n">
-        <v>-4.6632</v>
+        <v>-5.1768</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.68</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3181</v>
+        <v>-0.3371</v>
       </c>
       <c r="J29" t="n">
-        <v>-7.6344</v>
+        <v>-8.090400000000001</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.67</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3274</v>
+        <v>-0.3461</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.8576</v>
+        <v>-8.3064</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5421</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.0104</v>
+        <v>-13.1736</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2722</v>
+        <v>-0.2998</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.444</v>
+        <v>-5.996</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.68</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2828</v>
+        <v>-0.3098</v>
       </c>
       <c r="J33" t="n">
-        <v>-5.656</v>
+        <v>-6.196</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3444</v>
+        <v>-0.3679</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.888</v>
+        <v>-7.358</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.43</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5204</v>
+        <v>-0.5333</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.408</v>
+        <v>-10.666</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.31</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6373</v>
+        <v>-0.6405</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.746</v>
+        <v>-12.81</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.11</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7504</v>
+        <v>1.7647</v>
       </c>
       <c r="J37" t="n">
-        <v>35.008</v>
+        <v>35.294</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.03</v>
       </c>
       <c r="I38" t="n">
-        <v>1.6649</v>
+        <v>1.6753</v>
       </c>
       <c r="J38" t="n">
-        <v>33.298</v>
+        <v>33.506</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1389</v>
+        <v>1.1147</v>
       </c>
       <c r="J39" t="n">
-        <v>22.778</v>
+        <v>22.294</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.53</v>
       </c>
       <c r="I40" t="n">
-        <v>1.1154</v>
+        <v>1.0893</v>
       </c>
       <c r="J40" t="n">
-        <v>22.308</v>
+        <v>21.786</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1193</v>
+        <v>0.1616</v>
       </c>
       <c r="J41" t="n">
-        <v>2.386</v>
+        <v>3.232</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5334</v>
       </c>
       <c r="J42" t="n">
-        <v>15.12</v>
+        <v>14.4018</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.89</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1299</v>
+        <v>-0.1465</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.5073</v>
+        <v>-3.9555</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2106</v>
+        <v>-0.2282</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.6862</v>
+        <v>-6.1614</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3457</v>
+        <v>-0.3603</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.3339</v>
+        <v>-9.7281</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.374</v>
+        <v>-0.3874</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.098</v>
+        <v>-10.4598</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.68</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3496</v>
+        <v>1.329</v>
       </c>
       <c r="J47" t="n">
-        <v>36.4392</v>
+        <v>35.883</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.8007</v>
+        <v>0.7623</v>
       </c>
       <c r="J48" t="n">
-        <v>21.6189</v>
+        <v>20.5821</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7337</v>
+        <v>0.703</v>
       </c>
       <c r="J49" t="n">
-        <v>19.8099</v>
+        <v>18.981</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1686</v>
+        <v>0.1889</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5522</v>
+        <v>5.1003</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1193</v>
+        <v>-0.1044</v>
       </c>
       <c r="J51" t="n">
-        <v>-3.2211</v>
+        <v>-2.8188</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3946</v>
+        <v>0.3862</v>
       </c>
       <c r="J52" t="n">
-        <v>16.1786</v>
+        <v>15.8342</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1571</v>
+        <v>0.1639</v>
       </c>
       <c r="J53" t="n">
-        <v>6.4411</v>
+        <v>6.7199</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.124</v>
+        <v>0.1314</v>
       </c>
       <c r="J54" t="n">
-        <v>5.084</v>
+        <v>5.3874</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0604</v>
+        <v>-0.0634</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.4764</v>
+        <v>-2.5994</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.101</v>
+        <v>-0.1045</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.141</v>
+        <v>-4.2845</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5619</v>
+        <v>0.5507</v>
       </c>
       <c r="J57" t="n">
-        <v>23.0379</v>
+        <v>22.5787</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4214</v>
+        <v>0.4211</v>
       </c>
       <c r="J58" t="n">
-        <v>17.2774</v>
+        <v>17.2651</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3851</v>
+        <v>0.3872</v>
       </c>
       <c r="J59" t="n">
-        <v>15.7891</v>
+        <v>15.8752</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1409</v>
+        <v>-0.1521</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.7769</v>
+        <v>-6.2361</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3046</v>
+        <v>-0.3156</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.4886</v>
+        <v>-12.9396</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3557</v>
+        <v>1.3302</v>
       </c>
       <c r="J62" t="n">
-        <v>36.6039</v>
+        <v>35.9154</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5671</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>15.3117</v>
+        <v>14.8473</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3117</v>
+        <v>0.3166</v>
       </c>
       <c r="J64" t="n">
-        <v>8.415900000000001</v>
+        <v>8.5482</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.09329999999999999</v>
+        <v>-0.0863</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.5191</v>
+        <v>-2.3301</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5331</v>
+        <v>-0.5002</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.3937</v>
+        <v>-13.5054</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3519</v>
+        <v>0.3431</v>
       </c>
       <c r="J67" t="n">
-        <v>9.501300000000001</v>
+        <v>9.2637</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.076</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.6956</v>
+        <v>-2.052</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.143</v>
+        <v>-0.1593</v>
       </c>
       <c r="J69" t="n">
-        <v>-3.861</v>
+        <v>-4.3011</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3011</v>
+        <v>-0.3166</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.1297</v>
+        <v>-8.5482</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3487</v>
+        <v>-0.3626</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.414899999999999</v>
+        <v>-9.7902</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6174</v>
+        <v>1.6206</v>
       </c>
       <c r="J72" t="n">
-        <v>32.348</v>
+        <v>32.412</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.6</v>
       </c>
       <c r="I73" t="n">
-        <v>1.209</v>
+        <v>1.1875</v>
       </c>
       <c r="J73" t="n">
-        <v>24.18</v>
+        <v>23.75</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1511</v>
+        <v>1.1251</v>
       </c>
       <c r="J74" t="n">
-        <v>23.022</v>
+        <v>22.502</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.31</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7327</v>
       </c>
       <c r="J75" t="n">
-        <v>15.152</v>
+        <v>14.654</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.11</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2629</v>
+        <v>0.2888</v>
       </c>
       <c r="J76" t="n">
-        <v>5.258</v>
+        <v>5.776</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.91</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0596</v>
+        <v>-0.0861</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.192</v>
+        <v>-1.722</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.86</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1205</v>
+        <v>-0.1467</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.41</v>
+        <v>-2.934</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.62</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.363</v>
+        <v>-0.3822</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.26</v>
+        <v>-7.644</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.52</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4558</v>
+        <v>-0.47</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.116</v>
+        <v>-9.4</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.35</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6161</v>
+        <v>-0.6189</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.322</v>
+        <v>-12.378</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4894</v>
+        <v>0.4809</v>
       </c>
       <c r="J82" t="n">
-        <v>11.7456</v>
+        <v>11.5416</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.151</v>
+        <v>0.1579</v>
       </c>
       <c r="J83" t="n">
-        <v>3.624</v>
+        <v>3.7896</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.15</v>
+        <v>-0.1646</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.6</v>
+        <v>-3.9504</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.15</v>
+        <v>-0.1646</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.6</v>
+        <v>-3.9504</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4234</v>
+        <v>-0.4326</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.1616</v>
+        <v>-10.3824</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.82</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9469</v>
+        <v>0.9265</v>
       </c>
       <c r="J87" t="n">
-        <v>22.7256</v>
+        <v>22.236</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3704</v>
+        <v>0.3867</v>
       </c>
       <c r="J88" t="n">
-        <v>8.8896</v>
+        <v>9.280799999999999</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1464</v>
+        <v>0.1659</v>
       </c>
       <c r="J89" t="n">
-        <v>3.5136</v>
+        <v>3.9816</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.05</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0707</v>
+        <v>0.0885</v>
       </c>
       <c r="J90" t="n">
-        <v>1.6968</v>
+        <v>2.124</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0444</v>
+        <v>-0.0437</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.0656</v>
+        <v>-1.0488</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.77</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4425</v>
+        <v>1.4298</v>
       </c>
       <c r="J92" t="n">
-        <v>31.735</v>
+        <v>31.4556</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.55</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1777</v>
+        <v>1.1482</v>
       </c>
       <c r="J93" t="n">
-        <v>25.9094</v>
+        <v>25.2604</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.29</v>
       </c>
       <c r="I94" t="n">
-        <v>0.748</v>
+        <v>0.7174</v>
       </c>
       <c r="J94" t="n">
-        <v>16.456</v>
+        <v>15.7828</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2453</v>
+        <v>0.2639</v>
       </c>
       <c r="J95" t="n">
-        <v>5.3966</v>
+        <v>5.8058</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4029</v>
+        <v>-0.3733</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.863799999999999</v>
+        <v>-8.2126</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.96</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0301</v>
+        <v>-0.0469</v>
       </c>
       <c r="J97" t="n">
-        <v>-0.6622</v>
+        <v>-1.0318</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.0819</v>
+        <v>-0.1007</v>
       </c>
       <c r="J98" t="n">
-        <v>-1.8018</v>
+        <v>-2.2154</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.76</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2501</v>
+        <v>-0.2693</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.5022</v>
+        <v>-5.9246</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.63</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3725</v>
+        <v>-0.3879</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.195</v>
+        <v>-8.533799999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4099</v>
+        <v>-0.4236</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.017799999999999</v>
+        <v>-9.3192</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4085</v>
+        <v>0.4481</v>
       </c>
       <c r="J102" t="n">
-        <v>11.8465</v>
+        <v>12.9949</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.341</v>
+        <v>0.3483</v>
       </c>
       <c r="J103" t="n">
-        <v>9.888999999999999</v>
+        <v>10.1007</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1859</v>
+        <v>0.1932</v>
       </c>
       <c r="J104" t="n">
-        <v>5.3911</v>
+        <v>5.6028</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1657</v>
+        <v>-0.1793</v>
       </c>
       <c r="J105" t="n">
-        <v>-4.8053</v>
+        <v>-5.1997</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3821</v>
+        <v>-0.3922</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.0809</v>
+        <v>-11.3738</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.8621</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>25.0009</v>
+        <v>27.4659</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.6606</v>
+        <v>0.7291</v>
       </c>
       <c r="J108" t="n">
-        <v>19.1574</v>
+        <v>21.1439</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1251</v>
+        <v>-0.1212</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.6279</v>
+        <v>-3.5148</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1251</v>
+        <v>-0.1212</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.6279</v>
+        <v>-3.5148</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5237000000000001</v>
+        <v>-0.4936</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.1873</v>
+        <v>-14.3144</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4386</v>
+        <v>0.4974</v>
       </c>
       <c r="J112" t="n">
-        <v>11.8422</v>
+        <v>13.4298</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3632</v>
+        <v>0.3964</v>
       </c>
       <c r="J113" t="n">
-        <v>9.8064</v>
+        <v>10.7028</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2493</v>
+        <v>0.266</v>
       </c>
       <c r="J114" t="n">
-        <v>6.7311</v>
+        <v>7.182</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.12</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1855</v>
+        <v>0.2023</v>
       </c>
       <c r="J115" t="n">
-        <v>5.0085</v>
+        <v>5.4621</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2746</v>
+        <v>-0.2844</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.4142</v>
+        <v>-7.6788</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3713</v>
+        <v>0.3966</v>
       </c>
       <c r="J117" t="n">
-        <v>10.0251</v>
+        <v>10.7082</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1609</v>
+        <v>0.1694</v>
       </c>
       <c r="J118" t="n">
-        <v>4.3443</v>
+        <v>4.5738</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0859</v>
+        <v>-0.0973</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.3193</v>
+        <v>-2.6271</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2163</v>
+        <v>-0.2304</v>
       </c>
       <c r="J120" t="n">
-        <v>-5.8401</v>
+        <v>-6.2208</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2264</v>
+        <v>-0.2404</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.1128</v>
+        <v>-6.4908</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4952</v>
+        <v>0.5508</v>
       </c>
       <c r="J122" t="n">
-        <v>12.8752</v>
+        <v>14.3208</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.2995</v>
+        <v>0.3047</v>
       </c>
       <c r="J123" t="n">
-        <v>7.787</v>
+        <v>7.9222</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2603</v>
+        <v>0.2673</v>
       </c>
       <c r="J124" t="n">
-        <v>6.7678</v>
+        <v>6.9498</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1482</v>
+        <v>-0.1605</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.8532</v>
+        <v>-4.173</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3391</v>
+        <v>-0.3499</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.816599999999999</v>
+        <v>-9.0974</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7856</v>
+        <v>0.8694</v>
       </c>
       <c r="J127" t="n">
-        <v>20.4256</v>
+        <v>22.6044</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7075</v>
+        <v>0.7847</v>
       </c>
       <c r="J128" t="n">
-        <v>18.395</v>
+        <v>20.4022</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6147</v>
+        <v>0.6829</v>
       </c>
       <c r="J129" t="n">
-        <v>15.9822</v>
+        <v>17.7554</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4931</v>
+        <v>0.5472</v>
       </c>
       <c r="J130" t="n">
-        <v>12.8206</v>
+        <v>14.2272</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7818000000000001</v>
+        <v>-0.7189</v>
       </c>
       <c r="J131" t="n">
-        <v>-20.3268</v>
+        <v>-18.6914</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5129</v>
+        <v>0.5679</v>
       </c>
       <c r="J132" t="n">
-        <v>17.4386</v>
+        <v>19.3086</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4703</v>
+        <v>0.52</v>
       </c>
       <c r="J133" t="n">
-        <v>15.9902</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4274</v>
+        <v>0.4712</v>
       </c>
       <c r="J134" t="n">
-        <v>14.5316</v>
+        <v>16.0208</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.3833</v>
+        <v>0.4138</v>
       </c>
       <c r="J135" t="n">
-        <v>13.0322</v>
+        <v>14.0692</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.1</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3095</v>
+        <v>0.3153</v>
       </c>
       <c r="J136" t="n">
-        <v>10.523</v>
+        <v>10.7202</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5743</v>
+        <v>0.6367</v>
       </c>
       <c r="J137" t="n">
-        <v>19.5262</v>
+        <v>21.6478</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.97</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0465</v>
+        <v>-0.0556</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.581</v>
+        <v>-1.8904</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1067</v>
+        <v>-0.1198</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.6278</v>
+        <v>-4.0732</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2131</v>
+        <v>-0.2279</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.2454</v>
+        <v>-7.7486</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3401</v>
+        <v>-0.3525</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.5634</v>
+        <v>-11.985</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>0.7655999999999999</v>
+        <v>0.8466</v>
       </c>
       <c r="J142" t="n">
-        <v>19.14</v>
+        <v>21.165</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4955</v>
+        <v>0.5492</v>
       </c>
       <c r="J143" t="n">
-        <v>12.3875</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4397</v>
+        <v>0.4859</v>
       </c>
       <c r="J144" t="n">
-        <v>10.9925</v>
+        <v>12.1475</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3289</v>
+        <v>0.3369</v>
       </c>
       <c r="J145" t="n">
-        <v>8.2225</v>
+        <v>8.422499999999999</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1207</v>
+        <v>0.1388</v>
       </c>
       <c r="J146" t="n">
-        <v>3.0175</v>
+        <v>3.47</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.4653</v>
+        <v>0.5117</v>
       </c>
       <c r="J147" t="n">
-        <v>11.6325</v>
+        <v>12.7925</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1076</v>
+        <v>0.1114</v>
       </c>
       <c r="J148" t="n">
-        <v>2.69</v>
+        <v>2.785</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1048</v>
+        <v>-0.1183</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.62</v>
+        <v>-2.9575</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1268</v>
+        <v>-0.1412</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.17</v>
+        <v>-3.53</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4674</v>
+        <v>-0.4747</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.685</v>
+        <v>-11.8675</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.02</v>
       </c>
       <c r="I152" t="n">
-        <v>0.1041</v>
+        <v>0.0975</v>
       </c>
       <c r="J152" t="n">
-        <v>2.4984</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1193</v>
+        <v>-0.1383</v>
       </c>
       <c r="J153" t="n">
-        <v>-2.8632</v>
+        <v>-3.3192</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.76</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2512</v>
+        <v>-0.2701</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.0288</v>
+        <v>-6.4824</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3174</v>
+        <v>-0.3347</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.6176</v>
+        <v>-8.0328</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4487</v>
+        <v>-0.46</v>
       </c>
       <c r="J156" t="n">
-        <v>-10.7688</v>
+        <v>-11.04</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.86</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9705</v>
+        <v>0.9517</v>
       </c>
       <c r="J157" t="n">
-        <v>23.292</v>
+        <v>22.8408</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4104</v>
+        <v>0.4264</v>
       </c>
       <c r="J158" t="n">
-        <v>9.849600000000001</v>
+        <v>10.2336</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3667</v>
+        <v>0.384</v>
       </c>
       <c r="J159" t="n">
-        <v>8.800800000000001</v>
+        <v>9.215999999999999</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0478</v>
+        <v>0.0664</v>
       </c>
       <c r="J160" t="n">
-        <v>1.1472</v>
+        <v>1.5936</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.028</v>
+        <v>-0.0217</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.672</v>
+        <v>-0.5208</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9898</v>
+        <v>0.9283</v>
       </c>
       <c r="J162" t="n">
-        <v>33.6532</v>
+        <v>31.5622</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4986</v>
+        <v>0.4869</v>
       </c>
       <c r="J163" t="n">
-        <v>16.9524</v>
+        <v>16.5546</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3715</v>
+        <v>0.3705</v>
       </c>
       <c r="J164" t="n">
-        <v>12.631</v>
+        <v>12.597</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.09</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2892</v>
+        <v>0.2943</v>
       </c>
       <c r="J165" t="n">
-        <v>9.832800000000001</v>
+        <v>10.0062</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3572</v>
+        <v>-0.3412</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.1448</v>
+        <v>-11.6008</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6608000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J167" t="n">
-        <v>22.4672</v>
+        <v>21.6036</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0346</v>
+        <v>-0.0416</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.1764</v>
+        <v>-1.4144</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.0978</v>
+        <v>-0.1098</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.3252</v>
+        <v>-3.7332</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1093</v>
+        <v>-0.1218</v>
       </c>
       <c r="J170" t="n">
-        <v>-3.7162</v>
+        <v>-4.1412</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.2954</v>
+        <v>-0.3084</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.0436</v>
+        <v>-10.4856</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>1.0087</v>
+        <v>0.9484</v>
       </c>
       <c r="J172" t="n">
-        <v>36.3132</v>
+        <v>34.1424</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8627</v>
+        <v>0.8095</v>
       </c>
       <c r="J173" t="n">
-        <v>31.0572</v>
+        <v>29.142</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.6237</v>
+        <v>0.5989</v>
       </c>
       <c r="J174" t="n">
-        <v>22.4532</v>
+        <v>21.5604</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.89</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4142</v>
+        <v>-0.3938</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.9112</v>
+        <v>-14.1768</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.83</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.579</v>
+        <v>-0.5429</v>
       </c>
       <c r="J176" t="n">
-        <v>-20.844</v>
+        <v>-19.5444</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5653</v>
+        <v>0.5501</v>
       </c>
       <c r="J177" t="n">
-        <v>20.3508</v>
+        <v>19.8036</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5476</v>
+        <v>0.5339</v>
       </c>
       <c r="J178" t="n">
-        <v>19.7136</v>
+        <v>19.2204</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.91</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1228</v>
+        <v>-0.1353</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.4208</v>
+        <v>-4.8708</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1559</v>
+        <v>-0.1691</v>
       </c>
       <c r="J180" t="n">
-        <v>-5.6124</v>
+        <v>-6.0876</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3643</v>
+        <v>-0.3749</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.1148</v>
+        <v>-13.4964</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.5059</v>
+        <v>0.4865</v>
       </c>
       <c r="J182" t="n">
-        <v>15.177</v>
+        <v>14.595</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3972</v>
+        <v>0.3881</v>
       </c>
       <c r="J183" t="n">
-        <v>11.916</v>
+        <v>11.643</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2224</v>
+        <v>0.2259</v>
       </c>
       <c r="J184" t="n">
-        <v>6.672</v>
+        <v>6.777</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.099</v>
+        <v>-0.1032</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.97</v>
+        <v>-3.096</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.8</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6283</v>
+        <v>-0.5925</v>
       </c>
       <c r="J186" t="n">
-        <v>-18.849</v>
+        <v>-17.775</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.25</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5159</v>
+        <v>0.5074</v>
       </c>
       <c r="J187" t="n">
-        <v>15.477</v>
+        <v>15.222</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3902</v>
+        <v>0.3909</v>
       </c>
       <c r="J188" t="n">
-        <v>11.706</v>
+        <v>11.727</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2172</v>
+        <v>0.2265</v>
       </c>
       <c r="J189" t="n">
-        <v>6.516</v>
+        <v>6.795</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2029</v>
+        <v>-0.2155</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.087</v>
+        <v>-6.465</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2029</v>
+        <v>-0.2155</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.087</v>
+        <v>-6.465</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0817</v>
+        <v>1.0372</v>
       </c>
       <c r="J192" t="n">
-        <v>29.2059</v>
+        <v>28.0044</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.35</v>
       </c>
       <c r="I193" t="n">
-        <v>0.9136</v>
+        <v>0.8574000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>24.6672</v>
+        <v>23.1498</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.15</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4411</v>
+        <v>0.4363</v>
       </c>
       <c r="J194" t="n">
-        <v>11.9097</v>
+        <v>11.7801</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.13</v>
       </c>
       <c r="I195" t="n">
-        <v>0.389</v>
+        <v>0.3888</v>
       </c>
       <c r="J195" t="n">
-        <v>10.503</v>
+        <v>10.4976</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6182</v>
+        <v>-0.5755</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.6914</v>
+        <v>-15.5385</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.1</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2674</v>
+        <v>0.2677</v>
       </c>
       <c r="J197" t="n">
-        <v>7.2198</v>
+        <v>7.2279</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0133</v>
+        <v>0.0095</v>
       </c>
       <c r="J198" t="n">
-        <v>0.3591</v>
+        <v>0.2565</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="J199" t="n">
-        <v>-1.89</v>
+        <v>-2.2032</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1691</v>
+        <v>-0.1845</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.5657</v>
+        <v>-4.9815</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.73</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.299</v>
+        <v>-0.3131</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.073</v>
+        <v>-8.4537</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.65</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6105</v>
+        <v>0.6975</v>
       </c>
       <c r="J202" t="n">
-        <v>17.7045</v>
+        <v>20.2275</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.2883</v>
+        <v>0.304</v>
       </c>
       <c r="J203" t="n">
-        <v>8.3607</v>
+        <v>8.816000000000001</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.06</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1007</v>
+        <v>0.1156</v>
       </c>
       <c r="J204" t="n">
-        <v>2.9203</v>
+        <v>3.3524</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0122</v>
+        <v>-0.0094</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.3538</v>
+        <v>-0.2726</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.2928</v>
+        <v>-0.3026</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.491199999999999</v>
+        <v>-8.775399999999999</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2704</v>
+        <v>0.2727</v>
       </c>
       <c r="J207" t="n">
-        <v>7.8416</v>
+        <v>7.9083</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2704</v>
+        <v>0.2727</v>
       </c>
       <c r="J208" t="n">
-        <v>7.8416</v>
+        <v>7.9083</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0125</v>
+        <v>0.0092</v>
       </c>
       <c r="J209" t="n">
-        <v>0.3625</v>
+        <v>0.2668</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3357</v>
+        <v>-0.349</v>
       </c>
       <c r="J210" t="n">
-        <v>-9.735300000000001</v>
+        <v>-10.121</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.61</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4107</v>
+        <v>-0.421</v>
       </c>
       <c r="J211" t="n">
-        <v>-11.9103</v>
+        <v>-12.209</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3354</v>
+        <v>0.3344</v>
       </c>
       <c r="J212" t="n">
-        <v>8.7204</v>
+        <v>8.6944</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.299</v>
+        <v>0.2955</v>
       </c>
       <c r="J213" t="n">
-        <v>7.774</v>
+        <v>7.683</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0402</v>
+        <v>-0.0508</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.0452</v>
+        <v>-1.3208</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3524</v>
+        <v>-0.3655</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.1624</v>
+        <v>-9.503</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.61</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4085</v>
+        <v>-0.4193</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.621</v>
+        <v>-10.9018</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.611</v>
+        <v>0.6765</v>
       </c>
       <c r="J217" t="n">
-        <v>15.886</v>
+        <v>17.589</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5557</v>
+        <v>0.6153</v>
       </c>
       <c r="J218" t="n">
-        <v>14.4482</v>
+        <v>15.9978</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.25</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5417</v>
+        <v>0.5998</v>
       </c>
       <c r="J219" t="n">
-        <v>14.0842</v>
+        <v>15.5948</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.08</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2534</v>
+        <v>0.2626</v>
       </c>
       <c r="J220" t="n">
-        <v>6.5884</v>
+        <v>6.8276</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.93</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.3047</v>
+        <v>-0.2907</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.9222</v>
+        <v>-7.5582</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1496</v>
+        <v>-0.1695</v>
       </c>
       <c r="J222" t="n">
-        <v>-3.74</v>
+        <v>-4.2375</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.79</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2217</v>
+        <v>-0.2413</v>
       </c>
       <c r="J223" t="n">
-        <v>-5.5425</v>
+        <v>-6.0325</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.76</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2496</v>
+        <v>-0.2689</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.24</v>
+        <v>-6.7225</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2775</v>
+        <v>-0.2963</v>
       </c>
       <c r="J225" t="n">
-        <v>-6.9375</v>
+        <v>-7.4075</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3151</v>
+        <v>-0.3329</v>
       </c>
       <c r="J226" t="n">
-        <v>-7.8775</v>
+        <v>-8.3225</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.65</v>
       </c>
       <c r="I227" t="n">
-        <v>1.0328</v>
+        <v>1.1372</v>
       </c>
       <c r="J227" t="n">
-        <v>25.82</v>
+        <v>28.43</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.42</v>
       </c>
       <c r="I228" t="n">
-        <v>0.7474</v>
+        <v>0.8306</v>
       </c>
       <c r="J228" t="n">
-        <v>18.685</v>
+        <v>20.765</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.38</v>
       </c>
       <c r="I229" t="n">
-        <v>0.6963</v>
+        <v>0.7749</v>
       </c>
       <c r="J229" t="n">
-        <v>17.4075</v>
+        <v>19.3725</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0489</v>
       </c>
       <c r="J230" t="n">
-        <v>-1.7625</v>
+        <v>-1.2225</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0489</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.7625</v>
+        <v>-1.2225</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.2544</v>
+        <v>1.3606</v>
       </c>
       <c r="J232" t="n">
-        <v>37.632</v>
+        <v>40.818</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.3899</v>
+        <v>0.4209</v>
       </c>
       <c r="J233" t="n">
-        <v>11.697</v>
+        <v>12.627</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.0234</v>
+        <v>-0.016</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.702</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.85</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.5178</v>
+        <v>-0.4894</v>
       </c>
       <c r="J235" t="n">
-        <v>-15.534</v>
+        <v>-14.682</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.8028</v>
+        <v>-0.7423999999999999</v>
       </c>
       <c r="J236" t="n">
-        <v>-24.084</v>
+        <v>-22.272</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5124</v>
+        <v>0.5689</v>
       </c>
       <c r="J237" t="n">
-        <v>15.372</v>
+        <v>17.067</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0385</v>
+        <v>0.0439</v>
       </c>
       <c r="J238" t="n">
-        <v>1.155</v>
+        <v>1.317</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1336</v>
+        <v>-0.1464</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.008</v>
+        <v>-4.392</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1554</v>
+        <v>-0.1688</v>
       </c>
       <c r="J240" t="n">
-        <v>-4.662</v>
+        <v>-5.064</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1662</v>
+        <v>-0.1797</v>
       </c>
       <c r="J241" t="n">
-        <v>-4.986</v>
+        <v>-5.391</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.9</v>
       </c>
       <c r="I242" t="n">
-        <v>1.2872</v>
+        <v>1.4124</v>
       </c>
       <c r="J242" t="n">
-        <v>28.3184</v>
+        <v>31.0728</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.84</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2191</v>
+        <v>1.3408</v>
       </c>
       <c r="J243" t="n">
-        <v>26.8202</v>
+        <v>29.4976</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>0.8711</v>
+        <v>0.9698</v>
       </c>
       <c r="J244" t="n">
-        <v>19.1642</v>
+        <v>21.3356</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1569</v>
+        <v>0.1881</v>
       </c>
       <c r="J245" t="n">
-        <v>3.4518</v>
+        <v>4.1382</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3704</v>
+        <v>-0.3368</v>
       </c>
       <c r="J246" t="n">
-        <v>-8.1488</v>
+        <v>-7.4096</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1133</v>
       </c>
       <c r="J247" t="n">
-        <v>-1.9228</v>
+        <v>-2.4926</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2629</v>
+        <v>-0.2852</v>
       </c>
       <c r="J248" t="n">
-        <v>-5.7838</v>
+        <v>-6.2744</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.6</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.3826</v>
+        <v>-0.4007</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.417199999999999</v>
+        <v>-8.8154</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4198</v>
+        <v>-0.4359</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.2356</v>
+        <v>-9.5898</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.52</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4572</v>
+        <v>-0.4711</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.0584</v>
+        <v>-10.3642</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6284</v>
+        <v>0.6887</v>
       </c>
       <c r="J252" t="n">
-        <v>25.7644</v>
+        <v>28.2367</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.5406</v>
+        <v>0.592</v>
       </c>
       <c r="J253" t="n">
-        <v>22.1646</v>
+        <v>24.272</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1374</v>
+        <v>-0.1405</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.6334</v>
+        <v>-5.7605</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2052</v>
+        <v>-0.2057</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.4132</v>
+        <v>-8.4337</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.8577</v>
+        <v>-0.7937</v>
       </c>
       <c r="J256" t="n">
-        <v>-35.1657</v>
+        <v>-32.5417</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5163</v>
+        <v>0.5725</v>
       </c>
       <c r="J257" t="n">
-        <v>21.1683</v>
+        <v>23.4725</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4</v>
+        <v>0.4362</v>
       </c>
       <c r="J258" t="n">
-        <v>16.4</v>
+        <v>17.8842</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0859</v>
+        <v>-0.0973</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.5219</v>
+        <v>-3.9893</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1536</v>
+        <v>-0.1674</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.2976</v>
+        <v>-6.8634</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4634</v>
+        <v>-0.4701</v>
       </c>
       <c r="J261" t="n">
-        <v>-18.9994</v>
+        <v>-19.2741</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.81</v>
       </c>
       <c r="I262" t="n">
-        <v>1.2139</v>
+        <v>1.3303</v>
       </c>
       <c r="J262" t="n">
-        <v>27.9197</v>
+        <v>30.5969</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.55</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9024</v>
+        <v>0.9996</v>
       </c>
       <c r="J263" t="n">
-        <v>20.7552</v>
+        <v>22.9908</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.6284</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="J264" t="n">
-        <v>14.4532</v>
+        <v>16.1253</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5369</v>
+        <v>0.5992</v>
       </c>
       <c r="J265" t="n">
-        <v>12.3487</v>
+        <v>13.7816</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.7</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.9507</v>
+        <v>-0.8635</v>
       </c>
       <c r="J266" t="n">
-        <v>-21.8661</v>
+        <v>-19.8605</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.91</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.114</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.1896</v>
+        <v>-2.622</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.09520000000000001</v>
+        <v>-0.114</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.1896</v>
+        <v>-2.622</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1731</v>
+        <v>-0.1925</v>
       </c>
       <c r="J269" t="n">
-        <v>-3.9813</v>
+        <v>-4.4275</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3546</v>
+        <v>-0.3706</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.155799999999999</v>
+        <v>-8.5238</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4202</v>
+        <v>-0.4331</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.6646</v>
+        <v>-9.9613</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.85</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.1412</v>
+        <v>-0.1653</v>
       </c>
       <c r="J272" t="n">
-        <v>-2.9652</v>
+        <v>-3.4713</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.68</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.3132</v>
+        <v>-0.3333</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.5772</v>
+        <v>-6.9993</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.67</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.322</v>
+        <v>-0.3419</v>
       </c>
       <c r="J274" t="n">
-        <v>-6.762</v>
+        <v>-7.1799</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3769</v>
+        <v>-0.3946</v>
       </c>
       <c r="J275" t="n">
-        <v>-7.9149</v>
+        <v>-8.2866</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.3862</v>
+        <v>-0.4035</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.110200000000001</v>
+        <v>-8.4735</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.93</v>
       </c>
       <c r="I277" t="n">
-        <v>1.3215</v>
+        <v>1.4483</v>
       </c>
       <c r="J277" t="n">
-        <v>27.7515</v>
+        <v>30.4143</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.85</v>
       </c>
       <c r="I278" t="n">
-        <v>1.2309</v>
+        <v>1.3531</v>
       </c>
       <c r="J278" t="n">
-        <v>25.8489</v>
+        <v>28.4151</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.4941</v>
+        <v>0.5552</v>
       </c>
       <c r="J279" t="n">
-        <v>10.3761</v>
+        <v>11.6592</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.19</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4223</v>
+        <v>0.4746</v>
       </c>
       <c r="J280" t="n">
-        <v>8.8683</v>
+        <v>9.9666</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.06</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1265</v>
+        <v>0.1593</v>
       </c>
       <c r="J281" t="n">
-        <v>2.6565</v>
+        <v>3.3453</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0655</v>
+        <v>-0.0934</v>
       </c>
       <c r="J282" t="n">
-        <v>-1.2445</v>
+        <v>-1.7746</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1605</v>
+        <v>-0.1872</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.0495</v>
+        <v>-3.5568</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.71</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.2771</v>
+        <v>-0.3</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.2649</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.4</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.5659</v>
+        <v>-0.573</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.7521</v>
+        <v>-10.887</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6229</v>
+        <v>-0.6254999999999999</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.8351</v>
+        <v>-11.8845</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.88</v>
       </c>
       <c r="I287" t="n">
-        <v>1.2607</v>
+        <v>1.3852</v>
       </c>
       <c r="J287" t="n">
-        <v>23.9533</v>
+        <v>26.3188</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.54</v>
       </c>
       <c r="I288" t="n">
-        <v>0.869</v>
+        <v>0.968</v>
       </c>
       <c r="J288" t="n">
-        <v>16.511</v>
+        <v>18.392</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>0.7758</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="J289" t="n">
-        <v>14.7402</v>
+        <v>16.4616</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.42</v>
       </c>
       <c r="I290" t="n">
-        <v>0.7277</v>
+        <v>0.8137</v>
       </c>
       <c r="J290" t="n">
-        <v>13.8263</v>
+        <v>15.4603</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.07</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1532</v>
+        <v>0.1855</v>
       </c>
       <c r="J291" t="n">
-        <v>2.9108</v>
+        <v>3.5245</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I292" t="n">
-        <v>0.1445</v>
+        <v>0.153</v>
       </c>
       <c r="J292" t="n">
-        <v>4.913</v>
+        <v>5.202</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1001</v>
       </c>
       <c r="J293" t="n">
-        <v>3.1382</v>
+        <v>3.4034</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.0735</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="J294" t="n">
-        <v>2.499</v>
+        <v>2.7438</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.0978</v>
+        <v>-0.1098</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.3252</v>
+        <v>-3.7332</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2163</v>
+        <v>-0.2304</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.3542</v>
+        <v>-7.8336</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.32</v>
       </c>
       <c r="I297" t="n">
-        <v>0.3984</v>
+        <v>0.4465</v>
       </c>
       <c r="J297" t="n">
-        <v>13.5456</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.19</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2831</v>
+        <v>0.2973</v>
       </c>
       <c r="J298" t="n">
-        <v>9.625400000000001</v>
+        <v>10.1082</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>0.018</v>
+        <v>0.0257</v>
       </c>
       <c r="J299" t="n">
-        <v>0.612</v>
+        <v>0.8738</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0441</v>
+        <v>-0.0489</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.4994</v>
+        <v>-1.6626</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1207</v>
+        <v>-0.1307</v>
       </c>
       <c r="J301" t="n">
-        <v>-4.1038</v>
+        <v>-4.4438</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.436</v>
+        <v>0.4786</v>
       </c>
       <c r="J302" t="n">
-        <v>12.644</v>
+        <v>13.8794</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4056</v>
+        <v>0.4422</v>
       </c>
       <c r="J303" t="n">
-        <v>11.7624</v>
+        <v>12.8238</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3747</v>
+        <v>0.3981</v>
       </c>
       <c r="J304" t="n">
-        <v>10.8663</v>
+        <v>11.5449</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.09</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2958</v>
+        <v>0.2988</v>
       </c>
       <c r="J305" t="n">
-        <v>8.578200000000001</v>
+        <v>8.6652</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1909</v>
+        <v>-0.1871</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.5361</v>
+        <v>-5.4259</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.29</v>
       </c>
       <c r="I307" t="n">
-        <v>0.499</v>
+        <v>0.5521</v>
       </c>
       <c r="J307" t="n">
-        <v>14.471</v>
+        <v>16.0109</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.03</v>
       </c>
       <c r="I308" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1052</v>
       </c>
       <c r="J308" t="n">
-        <v>2.8739</v>
+        <v>3.0508</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.86</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1733</v>
+        <v>-0.1877</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.0257</v>
+        <v>-5.4433</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.84</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.1941</v>
+        <v>-0.2086</v>
       </c>
       <c r="J310" t="n">
-        <v>-5.6289</v>
+        <v>-6.0494</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2348</v>
+        <v>-0.2491</v>
       </c>
       <c r="J311" t="n">
-        <v>-6.8092</v>
+        <v>-7.2239</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.5986</v>
+        <v>0.6594</v>
       </c>
       <c r="J312" t="n">
-        <v>17.958</v>
+        <v>19.782</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4528</v>
+        <v>0.4971</v>
       </c>
       <c r="J313" t="n">
-        <v>13.584</v>
+        <v>14.913</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3761</v>
+        <v>0.3997</v>
       </c>
       <c r="J314" t="n">
-        <v>11.283</v>
+        <v>11.991</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2402</v>
+        <v>0.2461</v>
       </c>
       <c r="J315" t="n">
-        <v>7.206</v>
+        <v>7.383</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.79</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="J316" t="n">
-        <v>-20.187</v>
+        <v>-18.855</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.41</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6041</v>
+        <v>0.6743</v>
       </c>
       <c r="J317" t="n">
-        <v>18.123</v>
+        <v>20.229</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.4</v>
       </c>
       <c r="I318" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.6633</v>
       </c>
       <c r="J318" t="n">
-        <v>17.829</v>
+        <v>19.899</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1779</v>
+        <v>0.1875</v>
       </c>
       <c r="J319" t="n">
-        <v>5.337</v>
+        <v>5.625</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.74</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3011</v>
+        <v>-0.3129</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.032999999999999</v>
+        <v>-9.387</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.52</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5041</v>
+        <v>-0.5081</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.123</v>
+        <v>-15.243</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.35</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4115</v>
+        <v>0.4651</v>
       </c>
       <c r="J322" t="n">
-        <v>11.9335</v>
+        <v>13.4879</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.28</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3632</v>
+        <v>0.3964</v>
       </c>
       <c r="J323" t="n">
-        <v>10.5328</v>
+        <v>11.4956</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.09</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1439</v>
+        <v>0.1603</v>
       </c>
       <c r="J324" t="n">
-        <v>4.1731</v>
+        <v>4.6487</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.049</v>
+        <v>0.0621</v>
       </c>
       <c r="J325" t="n">
-        <v>1.421</v>
+        <v>1.8009</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.0347</v>
+        <v>-0.0361</v>
       </c>
       <c r="J326" t="n">
-        <v>-1.0063</v>
+        <v>-1.0469</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0366</v>
+        <v>0.0396</v>
       </c>
       <c r="J327" t="n">
-        <v>1.0614</v>
+        <v>1.1484</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.0069</v>
+        <v>0.0051</v>
       </c>
       <c r="J328" t="n">
-        <v>0.2001</v>
+        <v>0.1479</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.99</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0161</v>
+        <v>-0.0219</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.4669</v>
+        <v>-0.6351</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.9</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J330" t="n">
-        <v>-3.7236</v>
+        <v>-4.1296</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.83</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2022</v>
+        <v>-0.2172</v>
       </c>
       <c r="J331" t="n">
-        <v>-5.8638</v>
+        <v>-6.2988</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.13</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3444</v>
+        <v>0.3437</v>
       </c>
       <c r="J332" t="n">
-        <v>8.9544</v>
+        <v>8.936199999999999</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1272</v>
+        <v>0.1257</v>
       </c>
       <c r="J333" t="n">
-        <v>3.3072</v>
+        <v>3.2682</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.79</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2328</v>
+        <v>-0.2497</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.0528</v>
+        <v>-6.4922</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.32</v>
+        <v>-0.3349</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.32</v>
+        <v>-8.7074</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3295</v>
+        <v>-0.3441</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.567</v>
+        <v>-8.9466</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.37</v>
       </c>
       <c r="I337" t="n">
-        <v>0.6973</v>
+        <v>0.7729</v>
       </c>
       <c r="J337" t="n">
-        <v>18.1298</v>
+        <v>20.0954</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.34</v>
       </c>
       <c r="I338" t="n">
-        <v>0.6575</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="J338" t="n">
-        <v>17.095</v>
+        <v>18.9618</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.25</v>
       </c>
       <c r="I339" t="n">
-        <v>0.5356</v>
+        <v>0.5945</v>
       </c>
       <c r="J339" t="n">
-        <v>13.9256</v>
+        <v>15.457</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.3787</v>
+        <v>0.4087</v>
       </c>
       <c r="J340" t="n">
-        <v>9.8462</v>
+        <v>10.6262</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.93</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.3154</v>
+        <v>-0.2982</v>
       </c>
       <c r="J341" t="n">
-        <v>-8.2004</v>
+        <v>-7.7532</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I342" t="n">
-        <v>0.1513</v>
+        <v>0.1502</v>
       </c>
       <c r="J342" t="n">
-        <v>3.9338</v>
+        <v>3.9052</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0293</v>
+        <v>0.0211</v>
       </c>
       <c r="J343" t="n">
-        <v>0.7618</v>
+        <v>0.5486</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1532</v>
+        <v>-0.1697</v>
       </c>
       <c r="J344" t="n">
-        <v>-3.9832</v>
+        <v>-4.4122</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.1632</v>
+        <v>-0.18</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.2432</v>
+        <v>-4.68</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.59</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4238</v>
+        <v>-0.4344</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.0188</v>
+        <v>-11.2944</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.66</v>
       </c>
       <c r="I347" t="n">
-        <v>1.0699</v>
+        <v>1.1722</v>
       </c>
       <c r="J347" t="n">
-        <v>27.8174</v>
+        <v>30.4772</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3281</v>
+        <v>0.3363</v>
       </c>
       <c r="J348" t="n">
-        <v>8.5306</v>
+        <v>8.7438</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.11</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3281</v>
+        <v>0.3363</v>
       </c>
       <c r="J349" t="n">
-        <v>8.5306</v>
+        <v>8.7438</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.08</v>
       </c>
       <c r="I350" t="n">
-        <v>0.2453</v>
+        <v>0.257</v>
       </c>
       <c r="J350" t="n">
-        <v>6.3778</v>
+        <v>6.682</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.03</v>
       </c>
       <c r="I351" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.1045</v>
       </c>
       <c r="J351" t="n">
-        <v>2.21</v>
+        <v>2.717</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/4162/event_4162_evp_summary.xlsx
+++ b/database/event/4162/event_4162_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.5044</v>
+        <v>7.6511</v>
       </c>
       <c r="C2" t="n">
-        <v>1.0621</v>
+        <v>1.0829</v>
       </c>
       <c r="D2" t="n">
-        <v>2.792</v>
+        <v>2.8797</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5044</v>
+        <v>7.6511</v>
       </c>
       <c r="F2" t="n">
-        <v>2.31</v>
+        <v>2.3297</v>
       </c>
       <c r="G2" t="n">
-        <v>5.1943</v>
+        <v>5.3214</v>
       </c>
       <c r="H2" t="n">
-        <v>2.331</v>
+        <v>2.3888</v>
       </c>
       <c r="I2" t="n">
-        <v>2.4527</v>
+        <v>2.5182</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1943</v>
+        <v>5.3214</v>
       </c>
       <c r="K2" t="n">
         <v>66</v>
@@ -529,7 +529,7 @@
         <v>200</v>
       </c>
       <c r="M2" t="n">
-        <v>7.647</v>
+        <v>7.8396</v>
       </c>
       <c r="N2" t="n">
         <v>266</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5518</v>
+        <v>5.5111</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7857</v>
+        <v>0.78</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9031</v>
+        <v>1.9048</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5518</v>
+        <v>5.5111</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2081</v>
+        <v>2.2084</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3437</v>
+        <v>3.3027</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2081</v>
+        <v>2.2084</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3234</v>
+        <v>2.328</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3437</v>
+        <v>3.3027</v>
       </c>
       <c r="K3" t="n">
         <v>66</v>
@@ -575,7 +575,7 @@
         <v>200</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6671</v>
+        <v>5.6307</v>
       </c>
       <c r="N3" t="n">
         <v>266</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.3166</v>
+        <v>5.1705</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.7318</v>
       </c>
       <c r="D4" t="n">
-        <v>1.796</v>
+        <v>1.7496</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3166</v>
+        <v>5.1705</v>
       </c>
       <c r="F4" t="n">
-        <v>2.908</v>
+        <v>2.8684</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4086</v>
+        <v>2.3021</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6399</v>
+        <v>3.6233</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0298</v>
+        <v>4.0264</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4086</v>
+        <v>2.3021</v>
       </c>
       <c r="K4" t="n">
         <v>115</v>
@@ -621,7 +621,7 @@
         <v>275</v>
       </c>
       <c r="M4" t="n">
-        <v>6.4384</v>
+        <v>6.3285</v>
       </c>
       <c r="N4" t="n">
         <v>390</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8619</v>
+        <v>4.6538</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6881</v>
+        <v>0.6587</v>
       </c>
       <c r="D5" t="n">
-        <v>1.589</v>
+        <v>1.5142</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8619</v>
+        <v>4.6538</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5159</v>
+        <v>2.5141</v>
       </c>
       <c r="G5" t="n">
-        <v>2.346</v>
+        <v>2.1397</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7815</v>
+        <v>2.8114</v>
       </c>
       <c r="I5" t="n">
-        <v>2.9267</v>
+        <v>2.9637</v>
       </c>
       <c r="J5" t="n">
-        <v>2.346</v>
+        <v>2.1397</v>
       </c>
       <c r="K5" t="n">
         <v>66</v>
@@ -667,7 +667,7 @@
         <v>200</v>
       </c>
       <c r="M5" t="n">
-        <v>5.2727</v>
+        <v>5.1034</v>
       </c>
       <c r="N5" t="n">
         <v>266</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2774</v>
+        <v>4.1169</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6054</v>
+        <v>0.5827</v>
       </c>
       <c r="D6" t="n">
-        <v>1.323</v>
+        <v>1.2697</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2774</v>
+        <v>4.1169</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8541</v>
+        <v>2.8262</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4233</v>
+        <v>1.2907</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5219</v>
+        <v>3.5267</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8992</v>
+        <v>3.9191</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4233</v>
+        <v>1.2907</v>
       </c>
       <c r="K6" t="n">
         <v>115</v>
@@ -713,7 +713,7 @@
         <v>275</v>
       </c>
       <c r="M6" t="n">
-        <v>5.3225</v>
+        <v>5.2098</v>
       </c>
       <c r="N6" t="n">
         <v>390</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.2278</v>
+        <v>4.028</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5984</v>
+        <v>0.5701000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3004</v>
+        <v>1.2292</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2278</v>
+        <v>4.028</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7055</v>
+        <v>1.6364</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5223</v>
+        <v>2.3916</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7055</v>
+        <v>1.6364</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7945</v>
+        <v>1.725</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5223</v>
+        <v>2.3916</v>
       </c>
       <c r="K7" t="n">
         <v>162</v>
@@ -759,7 +759,7 @@
         <v>163</v>
       </c>
       <c r="M7" t="n">
-        <v>4.3168</v>
+        <v>4.1166</v>
       </c>
       <c r="N7" t="n">
         <v>325</v>
@@ -768,139 +768,139 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tabseN</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.9975</v>
+        <v>3.8597</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5658</v>
+        <v>0.5463</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1955</v>
+        <v>1.1525</v>
       </c>
       <c r="E8" t="n">
-        <v>3.9975</v>
+        <v>3.8597</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0013</v>
+        <v>0.2238</v>
       </c>
       <c r="G8" t="n">
-        <v>2.9962</v>
+        <v>3.6359</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0013</v>
+        <v>0.2238</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0271</v>
+        <v>0.2359</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9962</v>
+        <v>3.6359</v>
       </c>
       <c r="K8" t="n">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="L8" t="n">
-        <v>144</v>
+        <v>200</v>
       </c>
       <c r="M8" t="n">
-        <v>4.0233</v>
+        <v>3.8718</v>
       </c>
       <c r="N8" t="n">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>mertz</t>
+          <t>tabseN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.824</v>
+        <v>3.8551</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5412</v>
+        <v>0.5456</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1166</v>
+        <v>1.1504</v>
       </c>
       <c r="E9" t="n">
-        <v>3.824</v>
+        <v>3.8551</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>0.9194</v>
       </c>
       <c r="G9" t="n">
-        <v>3.824</v>
+        <v>2.9357</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.9194</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.9439</v>
       </c>
       <c r="J9" t="n">
-        <v>3.824</v>
+        <v>2.9357</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="L9" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="M9" t="n">
-        <v>3.824</v>
+        <v>3.8796</v>
       </c>
       <c r="N9" t="n">
-        <v>174</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>mertz</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.779</v>
+        <v>3.6817</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5348000000000001</v>
+        <v>0.5211</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0961</v>
+        <v>1.0714</v>
       </c>
       <c r="E10" t="n">
-        <v>3.779</v>
+        <v>3.6817</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1851</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5939</v>
+        <v>3.6817</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1851</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1948</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5939</v>
+        <v>3.6817</v>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7887</v>
+        <v>3.6817</v>
       </c>
       <c r="N10" t="n">
-        <v>266</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2973</v>
+        <v>3.0885</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4667</v>
+        <v>0.4371</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8768</v>
+        <v>0.8012</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2973</v>
+        <v>3.0885</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2772</v>
+        <v>1.215</v>
       </c>
       <c r="G11" t="n">
-        <v>2.0201</v>
+        <v>1.8735</v>
       </c>
       <c r="H11" t="n">
-        <v>1.2772</v>
+        <v>1.215</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3439</v>
+        <v>1.2808</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0201</v>
+        <v>1.8735</v>
       </c>
       <c r="K11" t="n">
         <v>57</v>
@@ -943,7 +943,7 @@
         <v>152</v>
       </c>
       <c r="M11" t="n">
-        <v>3.364</v>
+        <v>3.1543</v>
       </c>
       <c r="N11" t="n">
         <v>209</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8741</v>
+        <v>2.7688</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4068</v>
+        <v>0.3919</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6841</v>
+        <v>0.6555</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8741</v>
+        <v>2.7688</v>
       </c>
       <c r="F12" t="n">
-        <v>1.3461</v>
+        <v>1.3274</v>
       </c>
       <c r="G12" t="n">
-        <v>1.528</v>
+        <v>1.4414</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3461</v>
+        <v>1.3274</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4903</v>
+        <v>1.4751</v>
       </c>
       <c r="J12" t="n">
-        <v>1.528</v>
+        <v>1.4414</v>
       </c>
       <c r="K12" t="n">
         <v>115</v>
@@ -989,7 +989,7 @@
         <v>275</v>
       </c>
       <c r="M12" t="n">
-        <v>3.0183</v>
+        <v>2.9165</v>
       </c>
       <c r="N12" t="n">
         <v>390</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6531</v>
+        <v>2.5196</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3755</v>
+        <v>0.3566</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5835</v>
+        <v>0.542</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6531</v>
+        <v>2.5196</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3381</v>
+        <v>1.3396</v>
       </c>
       <c r="G13" t="n">
-        <v>1.315</v>
+        <v>1.18</v>
       </c>
       <c r="H13" t="n">
-        <v>1.3381</v>
+        <v>1.3396</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4814</v>
+        <v>1.4886</v>
       </c>
       <c r="J13" t="n">
-        <v>1.315</v>
+        <v>1.18</v>
       </c>
       <c r="K13" t="n">
         <v>115</v>
@@ -1035,7 +1035,7 @@
         <v>275</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7964</v>
+        <v>2.6686</v>
       </c>
       <c r="N13" t="n">
         <v>390</v>
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4475</v>
+        <v>2.3131</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3464</v>
+        <v>0.3274</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4899</v>
+        <v>0.4479</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4475</v>
+        <v>2.3131</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4475</v>
+        <v>2.3131</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2.4475</v>
+        <v>2.3131</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>174</v>
       </c>
       <c r="M14" t="n">
-        <v>2.4475</v>
+        <v>2.3131</v>
       </c>
       <c r="N14" t="n">
         <v>174</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.7624</v>
+        <v>1.6409</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2494</v>
+        <v>0.2322</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1781</v>
+        <v>0.1417</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7624</v>
+        <v>1.6409</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3824</v>
+        <v>1.2729</v>
       </c>
       <c r="G15" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3824</v>
+        <v>1.2729</v>
       </c>
       <c r="I15" t="n">
-        <v>1.418</v>
+        <v>1.3069</v>
       </c>
       <c r="J15" t="n">
-        <v>0.38</v>
+        <v>0.368</v>
       </c>
       <c r="K15" t="n">
         <v>94</v>
@@ -1127,7 +1127,7 @@
         <v>64</v>
       </c>
       <c r="M15" t="n">
-        <v>1.798</v>
+        <v>1.6749</v>
       </c>
       <c r="N15" t="n">
         <v>158</v>
@@ -1140,22 +1140,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4294</v>
+        <v>1.4573</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2023</v>
+        <v>0.2063</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0265</v>
+        <v>0.0581</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4294</v>
+        <v>1.4573</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4294</v>
+        <v>1.4573</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1164,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4294</v>
+        <v>1.4573</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
         <v>174</v>
       </c>
       <c r="M16" t="n">
-        <v>1.4294</v>
+        <v>1.4573</v>
       </c>
       <c r="N16" t="n">
         <v>174</v>
@@ -1182,93 +1182,93 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>smooya</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3006</v>
+        <v>1.2333</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1841</v>
+        <v>0.1745</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0321</v>
+        <v>-0.044</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3006</v>
+        <v>1.2333</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0454</v>
+        <v>-0.9689</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2552</v>
+        <v>2.2022</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0454</v>
+        <v>-0.9689</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>-0.9948</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2552</v>
+        <v>2.2022</v>
       </c>
       <c r="K17" t="n">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="L17" t="n">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3552</v>
+        <v>1.2074</v>
       </c>
       <c r="N17" t="n">
-        <v>325</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>smooya</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2466</v>
+        <v>1.1641</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1764</v>
+        <v>0.1648</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0567</v>
+        <v>-0.0755</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2466</v>
+        <v>1.1641</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9946</v>
+        <v>0.9467</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2411</v>
+        <v>0.2174</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9946</v>
+        <v>0.9467</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0202</v>
+        <v>0.998</v>
       </c>
       <c r="J18" t="n">
-        <v>2.2411</v>
+        <v>0.2174</v>
       </c>
       <c r="K18" t="n">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="L18" t="n">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2209</v>
+        <v>1.2154</v>
       </c>
       <c r="N18" t="n">
-        <v>257</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9581</v>
+        <v>0.8904</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1356</v>
+        <v>0.126</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1881</v>
+        <v>-0.2002</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9581</v>
+        <v>0.8904</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4226</v>
+        <v>0.462</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5355</v>
+        <v>0.4284</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4226</v>
+        <v>0.462</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4447</v>
+        <v>0.487</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5355</v>
+        <v>0.4284</v>
       </c>
       <c r="K19" t="n">
         <v>57</v>
@@ -1311,7 +1311,7 @@
         <v>152</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9802</v>
+        <v>0.9154</v>
       </c>
       <c r="N19" t="n">
         <v>209</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8509</v>
+        <v>0.8437</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1204</v>
+        <v>0.1194</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2369</v>
+        <v>-0.2214</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8509</v>
+        <v>0.8437</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9048</v>
+        <v>-0.857</v>
       </c>
       <c r="G20" t="n">
-        <v>1.7557</v>
+        <v>1.7007</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9048</v>
+        <v>-0.857</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.952</v>
+        <v>-0.9034</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7557</v>
+        <v>1.7007</v>
       </c>
       <c r="K20" t="n">
         <v>162</v>
@@ -1357,7 +1357,7 @@
         <v>163</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8037000000000001</v>
+        <v>0.7973000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>325</v>
@@ -1370,31 +1370,31 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7887</v>
+        <v>0.6845</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1116</v>
+        <v>0.0969</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2652</v>
+        <v>-0.294</v>
       </c>
       <c r="E21" t="n">
-        <v>0.7887</v>
+        <v>0.6845</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4665</v>
+        <v>0.4042</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3222</v>
+        <v>0.2802</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4665</v>
+        <v>0.4042</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4785</v>
+        <v>0.415</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3222</v>
+        <v>0.2802</v>
       </c>
       <c r="K21" t="n">
         <v>94</v>
@@ -1403,7 +1403,7 @@
         <v>64</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8007</v>
+        <v>0.6952</v>
       </c>
       <c r="N21" t="n">
         <v>158</v>
@@ -1416,22 +1416,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.546</v>
+        <v>0.5004</v>
       </c>
       <c r="C22" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0708</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3757</v>
+        <v>-0.3778</v>
       </c>
       <c r="E22" t="n">
-        <v>0.546</v>
+        <v>0.5004</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.546</v>
+        <v>0.5004</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1440,7 +1440,7 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.546</v>
+        <v>0.5004</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>174</v>
       </c>
       <c r="M22" t="n">
-        <v>0.546</v>
+        <v>0.5004</v>
       </c>
       <c r="N22" t="n">
         <v>174</v>
@@ -1462,22 +1462,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4433</v>
+        <v>0.3421</v>
       </c>
       <c r="C23" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0484</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4224</v>
+        <v>-0.4499</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4433</v>
+        <v>0.3421</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4433</v>
+        <v>0.3421</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1486,7 +1486,7 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4433</v>
+        <v>0.3421</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>174</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4433</v>
+        <v>0.3421</v>
       </c>
       <c r="N23" t="n">
         <v>174</v>
@@ -1508,31 +1508,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1706</v>
+        <v>0.094</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0241</v>
+        <v>0.0133</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5465</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1706</v>
+        <v>0.094</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6586</v>
+        <v>0.5512</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.488</v>
+        <v>-0.4572</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6586</v>
+        <v>0.5512</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6586</v>
+        <v>0.5512</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.488</v>
+        <v>-0.4572</v>
       </c>
       <c r="K24" t="n">
         <v>57</v>
@@ -1541,7 +1541,7 @@
         <v>40</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1706</v>
+        <v>0.09400000000000003</v>
       </c>
       <c r="N24" t="n">
         <v>97</v>
@@ -1554,31 +1554,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1326</v>
+        <v>0.0805</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0188</v>
+        <v>0.0114</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5638</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1326</v>
+        <v>0.0805</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0835</v>
+        <v>-0.0629</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2161</v>
+        <v>0.1434</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0835</v>
+        <v>-0.0629</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0925</v>
+        <v>-0.0699</v>
       </c>
       <c r="J25" t="n">
-        <v>0.2161</v>
+        <v>0.1434</v>
       </c>
       <c r="K25" t="n">
         <v>115</v>
@@ -1587,7 +1587,7 @@
         <v>275</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1236</v>
+        <v>0.0735</v>
       </c>
       <c r="N25" t="n">
         <v>390</v>
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0733</v>
+        <v>0.0578</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0104</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5908</v>
+        <v>-0.5795</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0733</v>
+        <v>0.0578</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4258</v>
+        <v>0.3776</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.3525</v>
+        <v>-0.3198</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4258</v>
+        <v>0.3776</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4258</v>
+        <v>0.3776</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.3525</v>
+        <v>-0.3198</v>
       </c>
       <c r="K26" t="n">
         <v>57</v>
@@ -1633,7 +1633,7 @@
         <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>0.07330000000000003</v>
+        <v>0.05780000000000002</v>
       </c>
       <c r="N26" t="n">
         <v>97</v>
@@ -1646,31 +1646,31 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0065</v>
+        <v>-0.0625</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0009</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6212</v>
+        <v>-0.6343</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0065</v>
+        <v>-0.0625</v>
       </c>
       <c r="F27" t="n">
-        <v>1.3638</v>
+        <v>1.2751</v>
       </c>
       <c r="G27" t="n">
-        <v>-1.3573</v>
+        <v>-1.3376</v>
       </c>
       <c r="H27" t="n">
-        <v>1.3638</v>
+        <v>1.2751</v>
       </c>
       <c r="I27" t="n">
-        <v>1.435</v>
+        <v>1.3442</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.3573</v>
+        <v>-1.3376</v>
       </c>
       <c r="K27" t="n">
         <v>162</v>
@@ -1679,7 +1679,7 @@
         <v>163</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0777000000000001</v>
+        <v>0.006600000000000161</v>
       </c>
       <c r="N27" t="n">
         <v>325</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0591</v>
+        <v>-0.067</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6511</v>
+        <v>-0.6363</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0591</v>
+        <v>-0.067</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.7649</v>
+        <v>-0.7703</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7058</v>
+        <v>0.7033</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7649</v>
+        <v>-0.7703</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.7846</v>
+        <v>-0.7909</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7058</v>
+        <v>0.7033</v>
       </c>
       <c r="K28" t="n">
         <v>113</v>
@@ -1725,7 +1725,7 @@
         <v>144</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.07879999999999998</v>
+        <v>-0.08760000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>257</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0136</v>
+        <v>-0.01</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.668</v>
+        <v>-0.6379</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3166</v>
+        <v>0.3054</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.4128</v>
+        <v>-0.3759</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3166</v>
+        <v>0.3054</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3331</v>
+        <v>0.3219</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.4128</v>
+        <v>-0.3759</v>
       </c>
       <c r="K29" t="n">
         <v>57</v>
@@ -1771,7 +1771,7 @@
         <v>152</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.07969999999999999</v>
+        <v>-0.05399999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>209</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1318</v>
+        <v>-0.1855</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0187</v>
+        <v>-0.0263</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6842</v>
+        <v>-0.6903</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1318</v>
+        <v>-0.1855</v>
       </c>
       <c r="F30" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5161</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.716</v>
+        <v>-0.7016</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.5161</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6147</v>
+        <v>0.5441</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.716</v>
+        <v>-0.7016</v>
       </c>
       <c r="K30" t="n">
         <v>57</v>
@@ -1817,7 +1817,7 @@
         <v>152</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1012999999999999</v>
+        <v>-0.1575</v>
       </c>
       <c r="N30" t="n">
         <v>209</v>
@@ -1830,31 +1830,31 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.243</v>
+        <v>-0.2469</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0344</v>
+        <v>-0.0349</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7348</v>
+        <v>-0.7183</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.243</v>
+        <v>-0.2469</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0317</v>
+        <v>-0.0665</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.2113</v>
+        <v>-0.1804</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.0317</v>
+        <v>-0.0665</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.0325</v>
+        <v>-0.0683</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.2113</v>
+        <v>-0.1804</v>
       </c>
       <c r="K31" t="n">
         <v>94</v>
@@ -1863,7 +1863,7 @@
         <v>64</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2438</v>
+        <v>-0.2487</v>
       </c>
       <c r="N31" t="n">
         <v>158</v>
@@ -1876,31 +1876,31 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3235</v>
+        <v>-0.3297</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0458</v>
+        <v>-0.0467</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7715</v>
+        <v>-0.756</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3235</v>
+        <v>-0.3297</v>
       </c>
       <c r="F32" t="n">
-        <v>0.2145</v>
+        <v>0.1746</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.538</v>
+        <v>-0.5043</v>
       </c>
       <c r="H32" t="n">
-        <v>0.2145</v>
+        <v>0.1746</v>
       </c>
       <c r="I32" t="n">
-        <v>0.22</v>
+        <v>0.1793</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.538</v>
+        <v>-0.5043</v>
       </c>
       <c r="K32" t="n">
         <v>94</v>
@@ -1909,7 +1909,7 @@
         <v>64</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3180000000000001</v>
+        <v>-0.325</v>
       </c>
       <c r="N32" t="n">
         <v>158</v>
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.5292</v>
+        <v>-0.5134</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.07489999999999999</v>
+        <v>-0.0727</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8651</v>
+        <v>-0.8397</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.5292</v>
+        <v>-0.5134</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1781</v>
+        <v>-0.1827</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.3511</v>
+        <v>-0.3307</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1781</v>
+        <v>-0.1827</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1874</v>
+        <v>-0.1926</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.3511</v>
+        <v>-0.3307</v>
       </c>
       <c r="K33" t="n">
         <v>57</v>
@@ -1955,7 +1955,7 @@
         <v>152</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.5385</v>
+        <v>-0.5233</v>
       </c>
       <c r="N33" t="n">
         <v>209</v>
@@ -1968,31 +1968,31 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6086</v>
+        <v>-0.5573</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0861</v>
+        <v>-0.0789</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9013</v>
+        <v>-0.8597</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6086</v>
+        <v>-0.5573</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.9545</v>
+        <v>-0.9061</v>
       </c>
       <c r="G34" t="n">
-        <v>0.3459</v>
+        <v>0.3488</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9545</v>
+        <v>-0.9061</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.0043</v>
+        <v>-0.9552</v>
       </c>
       <c r="J34" t="n">
-        <v>0.3459</v>
+        <v>0.3488</v>
       </c>
       <c r="K34" t="n">
         <v>162</v>
@@ -2001,7 +2001,7 @@
         <v>163</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6584</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="N34" t="n">
         <v>325</v>
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7265</v>
+        <v>-0.7407</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1028</v>
+        <v>-0.1048</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9549</v>
+        <v>-0.9432</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7265</v>
+        <v>-0.7407</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1767</v>
+        <v>0.1514</v>
       </c>
       <c r="G35" t="n">
-        <v>-0.9032</v>
+        <v>-0.8921</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1767</v>
+        <v>0.1514</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1813</v>
+        <v>0.1554</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9032</v>
+        <v>-0.8921</v>
       </c>
       <c r="K35" t="n">
         <v>94</v>
@@ -2047,7 +2047,7 @@
         <v>64</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7219</v>
+        <v>-0.7367</v>
       </c>
       <c r="N35" t="n">
         <v>158</v>
@@ -2056,35 +2056,35 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>rallen</t>
+          <t>mouz</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8729</v>
+        <v>-0.8702</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1235</v>
+        <v>-0.1232</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0216</v>
+        <v>-1.0022</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8729</v>
+        <v>-0.8702</v>
       </c>
       <c r="F36" t="n">
-        <v>0.042</v>
+        <v>-0.1889</v>
       </c>
       <c r="G36" t="n">
-        <v>-0.9149</v>
+        <v>-0.6813</v>
       </c>
       <c r="H36" t="n">
-        <v>0.042</v>
+        <v>-0.1889</v>
       </c>
       <c r="I36" t="n">
-        <v>0.042</v>
+        <v>-0.1889</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.9149</v>
+        <v>-0.6813</v>
       </c>
       <c r="K36" t="n">
         <v>57</v>
@@ -2093,7 +2093,7 @@
         <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8729</v>
+        <v>-0.8702000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>97</v>
@@ -2102,35 +2102,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mouz</t>
+          <t>rallen</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9095</v>
+        <v>-0.891</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1287</v>
+        <v>-0.1261</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0382</v>
+        <v>-1.0117</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9095</v>
+        <v>-0.891</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.206</v>
+        <v>0.0188</v>
       </c>
       <c r="G37" t="n">
-        <v>-0.7035</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.206</v>
+        <v>0.0188</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.206</v>
+        <v>0.0188</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.7035</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="K37" t="n">
         <v>57</v>
@@ -2139,7 +2139,7 @@
         <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9095</v>
+        <v>-0.891</v>
       </c>
       <c r="N37" t="n">
         <v>97</v>
@@ -2148,35 +2148,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>tiziaN</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9202</v>
+        <v>-0.894</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1302</v>
+        <v>-0.1265</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0431</v>
+        <v>-1.013</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9202</v>
+        <v>-0.894</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.2517</v>
+        <v>-1.9479</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3315</v>
+        <v>1.0539</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.2517</v>
+        <v>-1.9479</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.284</v>
+        <v>-2</v>
       </c>
       <c r="J38" t="n">
-        <v>0.3315</v>
+        <v>1.0539</v>
       </c>
       <c r="K38" t="n">
         <v>113</v>
@@ -2185,7 +2185,7 @@
         <v>144</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9525</v>
+        <v>-0.9460999999999999</v>
       </c>
       <c r="N38" t="n">
         <v>257</v>
@@ -2194,35 +2194,35 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>tiziaN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.9555</v>
+        <v>-0.9268</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1352</v>
+        <v>-0.1312</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0592</v>
+        <v>-1.028</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.9555</v>
+        <v>-0.9268</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.9498</v>
+        <v>-1.2485</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9943</v>
+        <v>0.3217</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.9498</v>
+        <v>-1.2485</v>
       </c>
       <c r="I39" t="n">
-        <v>-2</v>
+        <v>-1.2819</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9943</v>
+        <v>0.3217</v>
       </c>
       <c r="K39" t="n">
         <v>113</v>
@@ -2231,7 +2231,7 @@
         <v>144</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.0057</v>
+        <v>-0.9602000000000001</v>
       </c>
       <c r="N39" t="n">
         <v>257</v>
@@ -2244,31 +2244,31 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4874</v>
+        <v>-1.4528</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2105</v>
+        <v>-0.2056</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.3013</v>
+        <v>-1.2676</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4874</v>
+        <v>-1.4528</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.5286</v>
+        <v>-0.4905</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.9588</v>
+        <v>-0.9623</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5286</v>
+        <v>-0.4905</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5286</v>
+        <v>-0.4905</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.9588</v>
+        <v>-0.9623</v>
       </c>
       <c r="K40" t="n">
         <v>57</v>
@@ -2277,7 +2277,7 @@
         <v>40</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4874</v>
+        <v>-1.4528</v>
       </c>
       <c r="N40" t="n">
         <v>97</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.6771</v>
+        <v>-1.7205</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2374</v>
+        <v>-0.2435</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3877</v>
+        <v>-1.3896</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.6771</v>
+        <v>-1.7205</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1141</v>
+        <v>0.0593</v>
       </c>
       <c r="G41" t="n">
-        <v>-1.7912</v>
+        <v>-1.7798</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1141</v>
+        <v>0.0593</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1201</v>
+        <v>0.0625</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.7912</v>
+        <v>-1.7798</v>
       </c>
       <c r="K41" t="n">
         <v>66</v>
@@ -2323,7 +2323,7 @@
         <v>200</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.6711</v>
+        <v>-1.7173</v>
       </c>
       <c r="N41" t="n">
         <v>266</v>
@@ -2429,10 +2429,10 @@
         <v>1.35</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8872</v>
+        <v>0.8681</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8872</v>
+        <v>0.8681</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8462</v>
+        <v>0.8234</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8462</v>
+        <v>0.8234</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.03</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1257</v>
+        <v>0.1022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1257</v>
+        <v>0.1022</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.91</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3297</v>
+        <v>-0.2876</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.3297</v>
+        <v>-0.2876</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.75</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.6844</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-0.6844</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.28</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5507</v>
+        <v>0.4909</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5507</v>
+        <v>0.4909</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.08</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2042</v>
+        <v>0.1644</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2042</v>
+        <v>0.1644</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.05</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1417</v>
+        <v>0.1105</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1417</v>
+        <v>0.1105</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.03</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0944</v>
+        <v>0.0711</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0944</v>
+        <v>0.0711</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1962</v>
+        <v>-0.1755</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1962</v>
+        <v>-0.1755</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8307</v>
+        <v>0.8964</v>
       </c>
       <c r="J12" t="n">
-        <v>24.921</v>
+        <v>26.892</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.21</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3259</v>
+        <v>0.3206</v>
       </c>
       <c r="J13" t="n">
-        <v>9.776999999999999</v>
+        <v>9.618</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.17</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2748</v>
+        <v>0.2667</v>
       </c>
       <c r="J14" t="n">
-        <v>8.244</v>
+        <v>8.000999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>1.12</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2059</v>
+        <v>0.195</v>
       </c>
       <c r="J15" t="n">
-        <v>6.177</v>
+        <v>5.85</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.99</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0425</v>
+        <v>-0.0332</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.275</v>
+        <v>-0.996</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.07</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1604</v>
+        <v>0.1219</v>
       </c>
       <c r="J17" t="n">
-        <v>4.812</v>
+        <v>3.657</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0133</v>
+        <v>0.0091</v>
       </c>
       <c r="J18" t="n">
-        <v>0.399</v>
+        <v>0.273</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2015</v>
+        <v>-0.1821</v>
       </c>
       <c r="J19" t="n">
-        <v>-6.045</v>
+        <v>-5.463</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.83</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2117</v>
+        <v>-0.1922</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.351</v>
+        <v>-5.766</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.346</v>
+        <v>-0.3305</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.38</v>
+        <v>-9.914999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.13</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8453</v>
+        <v>1.9822</v>
       </c>
       <c r="J22" t="n">
-        <v>44.2872</v>
+        <v>47.5728</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.29</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7127</v>
+        <v>0.6915</v>
       </c>
       <c r="J23" t="n">
-        <v>17.1048</v>
+        <v>16.596</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.24</v>
       </c>
       <c r="I24" t="n">
-        <v>0.61</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>14.64</v>
+        <v>14.0208</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.13</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3606</v>
+        <v>0.3286</v>
       </c>
       <c r="J25" t="n">
-        <v>8.654400000000001</v>
+        <v>7.8864</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0002</v>
+        <v>-0.0119</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0048</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1167</v>
+        <v>0.1016</v>
       </c>
       <c r="J27" t="n">
-        <v>2.8008</v>
+        <v>2.4384</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.2157</v>
+        <v>-0.2004</v>
       </c>
       <c r="J28" t="n">
-        <v>-5.1768</v>
+        <v>-4.8096</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.68</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3371</v>
+        <v>-0.323</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.090400000000001</v>
+        <v>-7.752</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.67</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3461</v>
+        <v>-0.3322</v>
       </c>
       <c r="J30" t="n">
-        <v>-8.3064</v>
+        <v>-7.9728</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.44</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.554</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.1736</v>
+        <v>-13.296</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.2998</v>
+        <v>-0.2883</v>
       </c>
       <c r="J32" t="n">
-        <v>-5.996</v>
+        <v>-5.766</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.68</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3098</v>
+        <v>-0.2992</v>
       </c>
       <c r="J33" t="n">
-        <v>-6.196</v>
+        <v>-5.984</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.62</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3679</v>
+        <v>-0.3611</v>
       </c>
       <c r="J34" t="n">
-        <v>-7.358</v>
+        <v>-7.222</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.43</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5333</v>
+        <v>-0.5353</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.666</v>
+        <v>-10.706</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.31</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6405</v>
+        <v>-0.658</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.81</v>
+        <v>-13.16</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>2.11</v>
       </c>
       <c r="I37" t="n">
-        <v>1.7647</v>
+        <v>1.8183</v>
       </c>
       <c r="J37" t="n">
-        <v>35.294</v>
+        <v>36.366</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>2.03</v>
       </c>
       <c r="I38" t="n">
-        <v>1.6753</v>
+        <v>1.7212</v>
       </c>
       <c r="J38" t="n">
-        <v>33.506</v>
+        <v>34.424</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.55</v>
       </c>
       <c r="I39" t="n">
-        <v>1.1147</v>
+        <v>1.1374</v>
       </c>
       <c r="J39" t="n">
-        <v>22.294</v>
+        <v>22.748</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.53</v>
       </c>
       <c r="I40" t="n">
-        <v>1.0893</v>
+        <v>1.1113</v>
       </c>
       <c r="J40" t="n">
-        <v>21.786</v>
+        <v>22.226</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1.07</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1616</v>
+        <v>0.1251</v>
       </c>
       <c r="J41" t="n">
-        <v>3.232</v>
+        <v>2.502</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.23</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5334</v>
+        <v>0.4814</v>
       </c>
       <c r="J42" t="n">
-        <v>14.4018</v>
+        <v>12.9978</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.89</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1465</v>
+        <v>-0.13</v>
       </c>
       <c r="J43" t="n">
-        <v>-3.9555</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2282</v>
+        <v>-0.2094</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.1614</v>
+        <v>-5.6538</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.67</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3603</v>
+        <v>-0.3457</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.7281</v>
+        <v>-9.3339</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.64</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3874</v>
+        <v>-0.3749</v>
       </c>
       <c r="J46" t="n">
-        <v>-10.4598</v>
+        <v>-10.1223</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.68</v>
       </c>
       <c r="I47" t="n">
-        <v>1.329</v>
+        <v>1.3501</v>
       </c>
       <c r="J47" t="n">
-        <v>35.883</v>
+        <v>36.4527</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.31</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7623</v>
+        <v>0.7386</v>
       </c>
       <c r="J48" t="n">
-        <v>20.5821</v>
+        <v>19.9422</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.28</v>
       </c>
       <c r="I49" t="n">
-        <v>0.703</v>
+        <v>0.6767</v>
       </c>
       <c r="J49" t="n">
-        <v>18.981</v>
+        <v>18.2709</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.06</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1889</v>
+        <v>0.1612</v>
       </c>
       <c r="J50" t="n">
-        <v>5.1003</v>
+        <v>4.3524</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.99</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.1044</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J51" t="n">
-        <v>-2.8188</v>
+        <v>-2.2707</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3862</v>
+        <v>0.3443</v>
       </c>
       <c r="J52" t="n">
-        <v>15.8342</v>
+        <v>14.1163</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.04</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1639</v>
+        <v>0.1343</v>
       </c>
       <c r="J53" t="n">
-        <v>6.7199</v>
+        <v>5.5063</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.03</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1314</v>
+        <v>0.1055</v>
       </c>
       <c r="J54" t="n">
-        <v>5.3874</v>
+        <v>4.3255</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.99</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0634</v>
+        <v>-0.0456</v>
       </c>
       <c r="J55" t="n">
-        <v>-2.5994</v>
+        <v>-1.8696</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.98</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.1045</v>
+        <v>-0.0799</v>
       </c>
       <c r="J56" t="n">
-        <v>-4.2845</v>
+        <v>-3.2759</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.28</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5507</v>
+        <v>0.4909</v>
       </c>
       <c r="J57" t="n">
-        <v>22.5787</v>
+        <v>20.1269</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.2</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4211</v>
+        <v>0.3643</v>
       </c>
       <c r="J58" t="n">
-        <v>17.2651</v>
+        <v>14.9363</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.18</v>
       </c>
       <c r="I59" t="n">
-        <v>0.3872</v>
+        <v>0.332</v>
       </c>
       <c r="J59" t="n">
-        <v>15.8752</v>
+        <v>13.612</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.9</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1521</v>
+        <v>-0.1321</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.2361</v>
+        <v>-5.4161</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.74</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3156</v>
+        <v>-0.2991</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.9396</v>
+        <v>-12.2631</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.66</v>
       </c>
       <c r="I62" t="n">
-        <v>1.3302</v>
+        <v>1.3538</v>
       </c>
       <c r="J62" t="n">
-        <v>35.9154</v>
+        <v>36.5526</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.2</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5137</v>
       </c>
       <c r="J63" t="n">
-        <v>14.8473</v>
+        <v>13.8699</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3166</v>
+        <v>0.2825</v>
       </c>
       <c r="J64" t="n">
-        <v>8.5482</v>
+        <v>7.6275</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.0863</v>
+        <v>-0.0653</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.3301</v>
+        <v>-1.7631</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.85</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5002</v>
+        <v>-0.4598</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.5054</v>
+        <v>-12.4146</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.13</v>
       </c>
       <c r="I67" t="n">
-        <v>0.3431</v>
+        <v>0.2919</v>
       </c>
       <c r="J67" t="n">
-        <v>9.2637</v>
+        <v>7.8813</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.076</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="J68" t="n">
-        <v>-2.052</v>
+        <v>-1.7199</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.88</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.1593</v>
+        <v>-0.1416</v>
       </c>
       <c r="J69" t="n">
-        <v>-4.3011</v>
+        <v>-3.8232</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.72</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3166</v>
+        <v>-0.2994</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.5482</v>
+        <v>-8.0838</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.67</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3626</v>
+        <v>-0.3482</v>
       </c>
       <c r="J71" t="n">
-        <v>-9.7902</v>
+        <v>-9.401400000000001</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.96</v>
       </c>
       <c r="I72" t="n">
-        <v>1.6206</v>
+        <v>1.6613</v>
       </c>
       <c r="J72" t="n">
-        <v>32.412</v>
+        <v>33.226</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.6</v>
       </c>
       <c r="I73" t="n">
-        <v>1.1875</v>
+        <v>1.2064</v>
       </c>
       <c r="J73" t="n">
-        <v>23.75</v>
+        <v>24.128</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1251</v>
+        <v>1.1433</v>
       </c>
       <c r="J74" t="n">
-        <v>22.502</v>
+        <v>22.866</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.31</v>
       </c>
       <c r="I75" t="n">
-        <v>0.7327</v>
+        <v>0.7166</v>
       </c>
       <c r="J75" t="n">
-        <v>14.654</v>
+        <v>14.332</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.11</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2888</v>
+        <v>0.2549</v>
       </c>
       <c r="J76" t="n">
-        <v>5.776</v>
+        <v>5.098</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.91</v>
       </c>
       <c r="I77" t="n">
-        <v>-0.0861</v>
+        <v>-0.0673</v>
       </c>
       <c r="J77" t="n">
-        <v>-1.722</v>
+        <v>-1.346</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.86</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.1467</v>
+        <v>-0.1293</v>
       </c>
       <c r="J78" t="n">
-        <v>-2.934</v>
+        <v>-2.586</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.62</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.3822</v>
+        <v>-0.3717</v>
       </c>
       <c r="J79" t="n">
-        <v>-7.644</v>
+        <v>-7.434</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.52</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.47</v>
+        <v>-0.4651</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.4</v>
+        <v>-9.302</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.35</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6189</v>
+        <v>-0.6342</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.378</v>
+        <v>-12.684</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.3</v>
       </c>
       <c r="I82" t="n">
-        <v>0.4809</v>
+        <v>0.49</v>
       </c>
       <c r="J82" t="n">
-        <v>11.5416</v>
+        <v>11.76</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.07</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1579</v>
+        <v>0.1405</v>
       </c>
       <c r="J83" t="n">
-        <v>3.7896</v>
+        <v>3.372</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.88</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1646</v>
+        <v>-0.145</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.9504</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.1646</v>
+        <v>-0.145</v>
       </c>
       <c r="J85" t="n">
-        <v>-3.9504</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.6</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4326</v>
+        <v>-0.4252</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.3824</v>
+        <v>-10.2048</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.82</v>
       </c>
       <c r="I87" t="n">
-        <v>0.9265</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="J87" t="n">
-        <v>22.236</v>
+        <v>20.6496</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.28</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3867</v>
+        <v>0.3271</v>
       </c>
       <c r="J88" t="n">
-        <v>9.280799999999999</v>
+        <v>7.8504</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.1</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1659</v>
+        <v>0.1306</v>
       </c>
       <c r="J89" t="n">
-        <v>3.9816</v>
+        <v>3.1344</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.05</v>
       </c>
       <c r="I90" t="n">
-        <v>0.0885</v>
+        <v>0.0654</v>
       </c>
       <c r="J90" t="n">
-        <v>2.124</v>
+        <v>1.5696</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.99</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0437</v>
+        <v>-0.0344</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.0488</v>
+        <v>-0.8256</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.77</v>
       </c>
       <c r="I92" t="n">
-        <v>1.4298</v>
+        <v>1.4568</v>
       </c>
       <c r="J92" t="n">
-        <v>31.4556</v>
+        <v>32.0496</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.55</v>
       </c>
       <c r="I93" t="n">
-        <v>1.1482</v>
+        <v>1.1619</v>
       </c>
       <c r="J93" t="n">
-        <v>25.2604</v>
+        <v>25.5618</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.29</v>
       </c>
       <c r="I94" t="n">
-        <v>0.7174</v>
+        <v>0.6947</v>
       </c>
       <c r="J94" t="n">
-        <v>15.7828</v>
+        <v>15.2834</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>1.09</v>
       </c>
       <c r="I95" t="n">
-        <v>0.2639</v>
+        <v>0.2328</v>
       </c>
       <c r="J95" t="n">
-        <v>5.8058</v>
+        <v>5.1216</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.91</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3733</v>
+        <v>-0.3357</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.2126</v>
+        <v>-7.3854</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>0.96</v>
       </c>
       <c r="I97" t="n">
-        <v>-0.0469</v>
+        <v>-0.0357</v>
       </c>
       <c r="J97" t="n">
-        <v>-1.0318</v>
+        <v>-0.7854</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>0.92</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.1007</v>
+        <v>-0.08649999999999999</v>
       </c>
       <c r="J98" t="n">
-        <v>-2.2154</v>
+        <v>-1.903</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.76</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.2693</v>
+        <v>-0.2527</v>
       </c>
       <c r="J99" t="n">
-        <v>-5.9246</v>
+        <v>-5.5594</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.63</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3879</v>
+        <v>-0.3755</v>
       </c>
       <c r="J100" t="n">
-        <v>-8.533799999999999</v>
+        <v>-8.260999999999999</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.59</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4236</v>
+        <v>-0.4141</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.3192</v>
+        <v>-9.110200000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.21</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4481</v>
+        <v>0.3951</v>
       </c>
       <c r="J102" t="n">
-        <v>12.9949</v>
+        <v>11.4579</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.15</v>
       </c>
       <c r="I103" t="n">
-        <v>0.3483</v>
+        <v>0.2945</v>
       </c>
       <c r="J103" t="n">
-        <v>10.1007</v>
+        <v>8.5405</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.07</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1932</v>
+        <v>0.1529</v>
       </c>
       <c r="J104" t="n">
-        <v>5.6028</v>
+        <v>4.4341</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.87</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.1793</v>
+        <v>-0.1589</v>
       </c>
       <c r="J105" t="n">
-        <v>-5.1997</v>
+        <v>-4.6081</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.65</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3922</v>
+        <v>-0.3811</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.3738</v>
+        <v>-11.0519</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.48</v>
       </c>
       <c r="I107" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9336</v>
       </c>
       <c r="J107" t="n">
-        <v>27.4659</v>
+        <v>27.0744</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.33</v>
       </c>
       <c r="I108" t="n">
-        <v>0.7291</v>
+        <v>0.7133</v>
       </c>
       <c r="J108" t="n">
-        <v>21.1439</v>
+        <v>20.6857</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.98</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1212</v>
+        <v>-0.0941</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.5148</v>
+        <v>-2.7289</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.98</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1212</v>
+        <v>-0.0941</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.5148</v>
+        <v>-2.7289</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.85</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4936</v>
+        <v>-0.4523</v>
       </c>
       <c r="J111" t="n">
-        <v>-14.3144</v>
+        <v>-13.1167</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.39</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4974</v>
+        <v>0.4491</v>
       </c>
       <c r="J112" t="n">
-        <v>13.4298</v>
+        <v>12.1257</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.28</v>
       </c>
       <c r="I113" t="n">
-        <v>0.3964</v>
+        <v>0.334</v>
       </c>
       <c r="J113" t="n">
-        <v>10.7028</v>
+        <v>9.018000000000001</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.17</v>
       </c>
       <c r="I114" t="n">
-        <v>0.266</v>
+        <v>0.216</v>
       </c>
       <c r="J114" t="n">
-        <v>7.182</v>
+        <v>5.832</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.12</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2023</v>
+        <v>0.1606</v>
       </c>
       <c r="J115" t="n">
-        <v>5.4621</v>
+        <v>4.3362</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.78</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.2844</v>
+        <v>-0.2669</v>
       </c>
       <c r="J116" t="n">
-        <v>-7.6788</v>
+        <v>-7.2063</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.24</v>
       </c>
       <c r="I117" t="n">
-        <v>0.3966</v>
+        <v>0.3937</v>
       </c>
       <c r="J117" t="n">
-        <v>10.7082</v>
+        <v>10.6299</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.08</v>
       </c>
       <c r="I118" t="n">
-        <v>0.1694</v>
+        <v>0.1522</v>
       </c>
       <c r="J118" t="n">
-        <v>4.5738</v>
+        <v>4.1094</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.0973</v>
+        <v>-0.081</v>
       </c>
       <c r="J119" t="n">
-        <v>-2.6271</v>
+        <v>-2.187</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.82</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2304</v>
+        <v>-0.21</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.2208</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2404</v>
+        <v>-0.2202</v>
       </c>
       <c r="J121" t="n">
-        <v>-6.4908</v>
+        <v>-5.9454</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.3</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5508</v>
+        <v>0.524</v>
       </c>
       <c r="J122" t="n">
-        <v>14.3208</v>
+        <v>13.624</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.13</v>
       </c>
       <c r="I123" t="n">
-        <v>0.3047</v>
+        <v>0.2542</v>
       </c>
       <c r="J123" t="n">
-        <v>7.9222</v>
+        <v>6.6092</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.11</v>
       </c>
       <c r="I124" t="n">
-        <v>0.2673</v>
+        <v>0.2199</v>
       </c>
       <c r="J124" t="n">
-        <v>6.9498</v>
+        <v>5.7174</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.89</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1605</v>
+        <v>-0.1403</v>
       </c>
       <c r="J125" t="n">
-        <v>-4.173</v>
+        <v>-3.6478</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.7</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3499</v>
+        <v>-0.3355</v>
       </c>
       <c r="J126" t="n">
-        <v>-9.0974</v>
+        <v>-8.723000000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.44</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8694</v>
+        <v>0.8542</v>
       </c>
       <c r="J127" t="n">
-        <v>22.6044</v>
+        <v>22.2092</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.38</v>
       </c>
       <c r="I128" t="n">
-        <v>0.7847</v>
+        <v>0.7696</v>
       </c>
       <c r="J128" t="n">
-        <v>20.4022</v>
+        <v>20.0096</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.31</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6829</v>
+        <v>0.6701</v>
       </c>
       <c r="J129" t="n">
-        <v>17.7554</v>
+        <v>17.4226</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.22</v>
       </c>
       <c r="I130" t="n">
-        <v>0.5472</v>
+        <v>0.5407999999999999</v>
       </c>
       <c r="J130" t="n">
-        <v>14.2272</v>
+        <v>14.0608</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.7189</v>
+        <v>-0.6922</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.6914</v>
+        <v>-17.9972</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.23</v>
       </c>
       <c r="I132" t="n">
-        <v>0.5679</v>
+        <v>0.5587</v>
       </c>
       <c r="J132" t="n">
-        <v>19.3086</v>
+        <v>18.9958</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.2</v>
       </c>
       <c r="I133" t="n">
-        <v>0.52</v>
+        <v>0.5093</v>
       </c>
       <c r="J133" t="n">
-        <v>17.68</v>
+        <v>17.3162</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.17</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4712</v>
+        <v>0.4465</v>
       </c>
       <c r="J134" t="n">
-        <v>16.0208</v>
+        <v>15.181</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.14</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4138</v>
+        <v>0.3785</v>
       </c>
       <c r="J135" t="n">
-        <v>14.0692</v>
+        <v>12.869</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>1.1</v>
       </c>
       <c r="I136" t="n">
-        <v>0.3153</v>
+        <v>0.2816</v>
       </c>
       <c r="J136" t="n">
-        <v>10.7202</v>
+        <v>9.574400000000001</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.36</v>
       </c>
       <c r="I137" t="n">
-        <v>0.6367</v>
+        <v>0.6087</v>
       </c>
       <c r="J137" t="n">
-        <v>21.6478</v>
+        <v>20.6958</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>0.97</v>
       </c>
       <c r="I138" t="n">
-        <v>-0.0556</v>
+        <v>-0.0443</v>
       </c>
       <c r="J138" t="n">
-        <v>-1.8904</v>
+        <v>-1.5062</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.92</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1198</v>
+        <v>-0.1023</v>
       </c>
       <c r="J139" t="n">
-        <v>-4.0732</v>
+        <v>-3.4782</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.82</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2279</v>
+        <v>-0.2076</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.7486</v>
+        <v>-7.0584</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3525</v>
+        <v>-0.3377</v>
       </c>
       <c r="J141" t="n">
-        <v>-11.985</v>
+        <v>-11.4818</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.42</v>
       </c>
       <c r="I142" t="n">
-        <v>0.8466</v>
+        <v>0.8309</v>
       </c>
       <c r="J142" t="n">
-        <v>21.165</v>
+        <v>20.7725</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.22</v>
       </c>
       <c r="I143" t="n">
-        <v>0.5492</v>
+        <v>0.5417</v>
       </c>
       <c r="J143" t="n">
-        <v>13.73</v>
+        <v>13.5425</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.18</v>
       </c>
       <c r="I144" t="n">
-        <v>0.4859</v>
+        <v>0.4676</v>
       </c>
       <c r="J144" t="n">
-        <v>12.1475</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.11</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3369</v>
+        <v>0.3034</v>
       </c>
       <c r="J145" t="n">
-        <v>8.422499999999999</v>
+        <v>7.585</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>1.04</v>
       </c>
       <c r="I146" t="n">
-        <v>0.1388</v>
+        <v>0.1151</v>
       </c>
       <c r="J146" t="n">
-        <v>3.47</v>
+        <v>2.8775</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.25</v>
       </c>
       <c r="I147" t="n">
-        <v>0.5117</v>
+        <v>0.4798</v>
       </c>
       <c r="J147" t="n">
-        <v>12.7925</v>
+        <v>11.995</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.03</v>
       </c>
       <c r="I148" t="n">
-        <v>0.1114</v>
+        <v>0.0823</v>
       </c>
       <c r="J148" t="n">
-        <v>2.785</v>
+        <v>2.0575</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.92</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1183</v>
+        <v>-0.1014</v>
       </c>
       <c r="J149" t="n">
-        <v>-2.9575</v>
+        <v>-2.535</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.9</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.1412</v>
+        <v>-0.1228</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.53</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.55</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4747</v>
+        <v>-0.4722</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.8675</v>
+        <v>-11.805</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.02</v>
       </c>
       <c r="I152" t="n">
-        <v>0.0975</v>
+        <v>0.0877</v>
       </c>
       <c r="J152" t="n">
-        <v>2.34</v>
+        <v>2.1048</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.89</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.1383</v>
+        <v>-0.123</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.3192</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.76</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.2701</v>
+        <v>-0.2532</v>
       </c>
       <c r="J154" t="n">
-        <v>-6.4824</v>
+        <v>-6.0768</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3347</v>
+        <v>-0.3192</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.0328</v>
+        <v>-7.6608</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.55</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.46</v>
+        <v>-0.4542</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.04</v>
+        <v>-10.9008</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.86</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9517</v>
+        <v>0.8869</v>
       </c>
       <c r="J157" t="n">
-        <v>22.8408</v>
+        <v>21.2856</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.32</v>
       </c>
       <c r="I158" t="n">
-        <v>0.4264</v>
+        <v>0.365</v>
       </c>
       <c r="J158" t="n">
-        <v>10.2336</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.28</v>
       </c>
       <c r="I159" t="n">
-        <v>0.384</v>
+        <v>0.3259</v>
       </c>
       <c r="J159" t="n">
-        <v>9.215999999999999</v>
+        <v>7.8216</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.04</v>
       </c>
       <c r="I160" t="n">
-        <v>0.0664</v>
+        <v>0.0469</v>
       </c>
       <c r="J160" t="n">
-        <v>1.5936</v>
+        <v>1.1256</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.0217</v>
+        <v>-0.0195</v>
       </c>
       <c r="J161" t="n">
-        <v>-0.5208</v>
+        <v>-0.468</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.38</v>
       </c>
       <c r="I162" t="n">
-        <v>0.9283</v>
+        <v>0.9134</v>
       </c>
       <c r="J162" t="n">
-        <v>31.5622</v>
+        <v>31.0556</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.17</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4869</v>
+        <v>0.4487</v>
       </c>
       <c r="J163" t="n">
-        <v>16.5546</v>
+        <v>15.2558</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.3705</v>
+        <v>0.3337</v>
       </c>
       <c r="J164" t="n">
-        <v>12.597</v>
+        <v>11.3458</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.09</v>
       </c>
       <c r="I165" t="n">
-        <v>0.2943</v>
+        <v>0.2601</v>
       </c>
       <c r="J165" t="n">
-        <v>10.0062</v>
+        <v>8.843400000000001</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.91</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3412</v>
+        <v>-0.2994</v>
       </c>
       <c r="J166" t="n">
-        <v>-11.6008</v>
+        <v>-10.1796</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.32</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6354</v>
+        <v>0.5779</v>
       </c>
       <c r="J167" t="n">
-        <v>21.6036</v>
+        <v>19.6486</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.98</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.0416</v>
+        <v>-0.0319</v>
       </c>
       <c r="J168" t="n">
-        <v>-1.4144</v>
+        <v>-1.0846</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.93</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1098</v>
+        <v>-0.0924</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.7332</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.92</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.1218</v>
+        <v>-0.1037</v>
       </c>
       <c r="J170" t="n">
-        <v>-4.1412</v>
+        <v>-3.5258</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.74</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3084</v>
+        <v>-0.2909</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.4856</v>
+        <v>-9.890599999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.39</v>
       </c>
       <c r="I172" t="n">
-        <v>0.9484</v>
+        <v>0.9363</v>
       </c>
       <c r="J172" t="n">
-        <v>34.1424</v>
+        <v>33.7068</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.32</v>
       </c>
       <c r="I173" t="n">
-        <v>0.8095</v>
+        <v>0.7839</v>
       </c>
       <c r="J173" t="n">
-        <v>29.142</v>
+        <v>28.2204</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.22</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5989</v>
+        <v>0.5624</v>
       </c>
       <c r="J174" t="n">
-        <v>21.5604</v>
+        <v>20.2464</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.89</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.3938</v>
+        <v>-0.3514</v>
       </c>
       <c r="J175" t="n">
-        <v>-14.1768</v>
+        <v>-12.6504</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.83</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.5429</v>
+        <v>-0.5034</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.5444</v>
+        <v>-18.1224</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.27</v>
       </c>
       <c r="I177" t="n">
-        <v>0.5501</v>
+        <v>0.4909</v>
       </c>
       <c r="J177" t="n">
-        <v>19.8036</v>
+        <v>17.6724</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.26</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5339</v>
+        <v>0.4747</v>
       </c>
       <c r="J178" t="n">
-        <v>19.2204</v>
+        <v>17.0892</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.91</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1353</v>
+        <v>-0.1161</v>
       </c>
       <c r="J179" t="n">
-        <v>-4.8708</v>
+        <v>-4.1796</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.88</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.1691</v>
+        <v>-0.1488</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.0876</v>
+        <v>-5.3568</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.67</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3749</v>
+        <v>-0.3623</v>
       </c>
       <c r="J181" t="n">
-        <v>-13.4964</v>
+        <v>-13.0428</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.16</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4865</v>
+        <v>0.4444</v>
       </c>
       <c r="J182" t="n">
-        <v>14.595</v>
+        <v>13.332</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.12</v>
       </c>
       <c r="I183" t="n">
-        <v>0.3881</v>
+        <v>0.3459</v>
       </c>
       <c r="J183" t="n">
-        <v>11.643</v>
+        <v>10.377</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.06</v>
       </c>
       <c r="I184" t="n">
-        <v>0.2259</v>
+        <v>0.1904</v>
       </c>
       <c r="J184" t="n">
-        <v>6.777</v>
+        <v>5.712</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.98</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1032</v>
+        <v>-0.0789</v>
       </c>
       <c r="J185" t="n">
-        <v>-3.096</v>
+        <v>-2.367</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.8</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.5925</v>
+        <v>-0.5535</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.775</v>
+        <v>-16.605</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.25</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5074</v>
+        <v>0.4481</v>
       </c>
       <c r="J187" t="n">
-        <v>15.222</v>
+        <v>13.443</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.18</v>
       </c>
       <c r="I188" t="n">
-        <v>0.3909</v>
+        <v>0.3353</v>
       </c>
       <c r="J188" t="n">
-        <v>11.727</v>
+        <v>10.059</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.09</v>
       </c>
       <c r="I189" t="n">
-        <v>0.2265</v>
+        <v>0.1835</v>
       </c>
       <c r="J189" t="n">
-        <v>6.795</v>
+        <v>5.505</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.84</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.2155</v>
+        <v>-0.1949</v>
       </c>
       <c r="J190" t="n">
-        <v>-6.465</v>
+        <v>-5.847</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.84</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2155</v>
+        <v>-0.1949</v>
       </c>
       <c r="J191" t="n">
-        <v>-6.465</v>
+        <v>-5.847</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.45</v>
       </c>
       <c r="I192" t="n">
-        <v>1.0372</v>
+        <v>1.0405</v>
       </c>
       <c r="J192" t="n">
-        <v>28.0044</v>
+        <v>28.0935</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.35</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8574000000000001</v>
+        <v>0.8364</v>
       </c>
       <c r="J193" t="n">
-        <v>23.1498</v>
+        <v>22.5828</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.15</v>
       </c>
       <c r="I194" t="n">
-        <v>0.4363</v>
+        <v>0.4008</v>
       </c>
       <c r="J194" t="n">
-        <v>11.7801</v>
+        <v>10.8216</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.13</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3888</v>
+        <v>0.3537</v>
       </c>
       <c r="J195" t="n">
-        <v>10.4976</v>
+        <v>9.549899999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.82</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.5755</v>
+        <v>-0.5385</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.5385</v>
+        <v>-14.5395</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.1</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2677</v>
+        <v>0.2197</v>
       </c>
       <c r="J197" t="n">
-        <v>7.2279</v>
+        <v>5.9319</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>0.0095</v>
+        <v>0.006</v>
       </c>
       <c r="J198" t="n">
-        <v>0.2565</v>
+        <v>0.162</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.95</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.0679</v>
       </c>
       <c r="J199" t="n">
-        <v>-2.2032</v>
+        <v>-1.8333</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.86</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.1845</v>
+        <v>-0.1646</v>
       </c>
       <c r="J200" t="n">
-        <v>-4.9815</v>
+        <v>-4.4442</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.73</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.3131</v>
+        <v>-0.2956</v>
       </c>
       <c r="J201" t="n">
-        <v>-8.4537</v>
+        <v>-7.9812</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.65</v>
       </c>
       <c r="I202" t="n">
-        <v>0.6975</v>
+        <v>0.6539</v>
       </c>
       <c r="J202" t="n">
-        <v>20.2275</v>
+        <v>18.9631</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.2</v>
       </c>
       <c r="I203" t="n">
-        <v>0.304</v>
+        <v>0.2494</v>
       </c>
       <c r="J203" t="n">
-        <v>8.816000000000001</v>
+        <v>7.2326</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.06</v>
       </c>
       <c r="I204" t="n">
-        <v>0.1156</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>3.3524</v>
+        <v>2.5346</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.0094</v>
+        <v>-0.007</v>
       </c>
       <c r="J205" t="n">
-        <v>-0.2726</v>
+        <v>-0.203</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.76</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.3026</v>
+        <v>-0.2859</v>
       </c>
       <c r="J206" t="n">
-        <v>-8.775399999999999</v>
+        <v>-8.2911</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>1.14</v>
       </c>
       <c r="I207" t="n">
-        <v>0.2727</v>
+        <v>0.2595</v>
       </c>
       <c r="J207" t="n">
-        <v>7.9083</v>
+        <v>7.5255</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.14</v>
       </c>
       <c r="I208" t="n">
-        <v>0.2727</v>
+        <v>0.2595</v>
       </c>
       <c r="J208" t="n">
-        <v>7.9083</v>
+        <v>7.5255</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>0.0092</v>
+        <v>0.0068</v>
       </c>
       <c r="J209" t="n">
-        <v>0.2668</v>
+        <v>0.1972</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.349</v>
+        <v>-0.3338</v>
       </c>
       <c r="J210" t="n">
-        <v>-10.121</v>
+        <v>-9.680199999999999</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.61</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.421</v>
+        <v>-0.4121</v>
       </c>
       <c r="J211" t="n">
-        <v>-12.209</v>
+        <v>-11.9509</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.13</v>
       </c>
       <c r="I212" t="n">
-        <v>0.3344</v>
+        <v>0.2826</v>
       </c>
       <c r="J212" t="n">
-        <v>8.6944</v>
+        <v>7.3476</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.11</v>
       </c>
       <c r="I213" t="n">
-        <v>0.2955</v>
+        <v>0.246</v>
       </c>
       <c r="J213" t="n">
-        <v>7.683</v>
+        <v>6.396</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>0.97</v>
       </c>
       <c r="I214" t="n">
-        <v>-0.0508</v>
+        <v>-0.0409</v>
       </c>
       <c r="J214" t="n">
-        <v>-1.3208</v>
+        <v>-1.0634</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>0.67</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.3655</v>
+        <v>-0.3514</v>
       </c>
       <c r="J215" t="n">
-        <v>-9.503</v>
+        <v>-9.1364</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.61</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.4193</v>
+        <v>-0.4101</v>
       </c>
       <c r="J216" t="n">
-        <v>-10.9018</v>
+        <v>-10.6626</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.3</v>
       </c>
       <c r="I217" t="n">
-        <v>0.6765</v>
+        <v>0.6625</v>
       </c>
       <c r="J217" t="n">
-        <v>17.589</v>
+        <v>17.225</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.26</v>
       </c>
       <c r="I218" t="n">
-        <v>0.6153</v>
+        <v>0.6036</v>
       </c>
       <c r="J218" t="n">
-        <v>15.9978</v>
+        <v>15.6936</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1.25</v>
       </c>
       <c r="I219" t="n">
-        <v>0.5998</v>
+        <v>0.5888</v>
       </c>
       <c r="J219" t="n">
-        <v>15.5948</v>
+        <v>15.3088</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>1.08</v>
       </c>
       <c r="I220" t="n">
-        <v>0.2626</v>
+        <v>0.2307</v>
       </c>
       <c r="J220" t="n">
-        <v>6.8276</v>
+        <v>5.9982</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.93</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.2907</v>
+        <v>-0.2507</v>
       </c>
       <c r="J221" t="n">
-        <v>-7.5582</v>
+        <v>-6.5182</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>0.86</v>
       </c>
       <c r="I222" t="n">
-        <v>-0.1695</v>
+        <v>-0.1537</v>
       </c>
       <c r="J222" t="n">
-        <v>-4.2375</v>
+        <v>-3.8425</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>0.79</v>
       </c>
       <c r="I223" t="n">
-        <v>-0.2413</v>
+        <v>-0.2249</v>
       </c>
       <c r="J223" t="n">
-        <v>-6.0325</v>
+        <v>-5.6225</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>0.76</v>
       </c>
       <c r="I224" t="n">
-        <v>-0.2689</v>
+        <v>-0.2525</v>
       </c>
       <c r="J224" t="n">
-        <v>-6.7225</v>
+        <v>-6.3125</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>0.73</v>
       </c>
       <c r="I225" t="n">
-        <v>-0.2963</v>
+        <v>-0.2801</v>
       </c>
       <c r="J225" t="n">
-        <v>-7.4075</v>
+        <v>-7.0025</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.3329</v>
+        <v>-0.3176</v>
       </c>
       <c r="J226" t="n">
-        <v>-8.3225</v>
+        <v>-7.94</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.65</v>
       </c>
       <c r="I227" t="n">
-        <v>1.1372</v>
+        <v>1.1302</v>
       </c>
       <c r="J227" t="n">
-        <v>28.43</v>
+        <v>28.255</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>1.42</v>
       </c>
       <c r="I228" t="n">
-        <v>0.8306</v>
+        <v>0.8167</v>
       </c>
       <c r="J228" t="n">
-        <v>20.765</v>
+        <v>20.4175</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>1.38</v>
       </c>
       <c r="I229" t="n">
-        <v>0.7749</v>
+        <v>0.7618</v>
       </c>
       <c r="J229" t="n">
-        <v>19.3725</v>
+        <v>19.045</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>1</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.0489</v>
+        <v>-0.0441</v>
       </c>
       <c r="J230" t="n">
-        <v>-1.2225</v>
+        <v>-1.1025</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.0489</v>
+        <v>-0.0441</v>
       </c>
       <c r="J231" t="n">
-        <v>-1.2225</v>
+        <v>-1.1025</v>
       </c>
     </row>
     <row r="232">
@@ -11629,10 +11629,10 @@
         <v>1.78</v>
       </c>
       <c r="I232" t="n">
-        <v>1.3606</v>
+        <v>1.378</v>
       </c>
       <c r="J232" t="n">
-        <v>40.818</v>
+        <v>41.34</v>
       </c>
     </row>
     <row r="233">
@@ -11669,10 +11669,10 @@
         <v>1.14</v>
       </c>
       <c r="I233" t="n">
-        <v>0.4209</v>
+        <v>0.3825</v>
       </c>
       <c r="J233" t="n">
-        <v>12.627</v>
+        <v>11.475</v>
       </c>
     </row>
     <row r="234">
@@ -11709,10 +11709,10 @@
         <v>1</v>
       </c>
       <c r="I234" t="n">
-        <v>-0.016</v>
+        <v>-0.0114</v>
       </c>
       <c r="J234" t="n">
-        <v>-0.48</v>
+        <v>-0.342</v>
       </c>
     </row>
     <row r="235">
@@ -11749,10 +11749,10 @@
         <v>0.85</v>
       </c>
       <c r="I235" t="n">
-        <v>-0.4894</v>
+        <v>-0.4477</v>
       </c>
       <c r="J235" t="n">
-        <v>-14.682</v>
+        <v>-13.431</v>
       </c>
     </row>
     <row r="236">
@@ -11789,10 +11789,10 @@
         <v>0.74</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.7423999999999999</v>
+        <v>-0.7144</v>
       </c>
       <c r="J236" t="n">
-        <v>-22.272</v>
+        <v>-21.432</v>
       </c>
     </row>
     <row r="237">
@@ -11829,10 +11829,10 @@
         <v>1.31</v>
       </c>
       <c r="I237" t="n">
-        <v>0.5689</v>
+        <v>0.5431</v>
       </c>
       <c r="J237" t="n">
-        <v>17.067</v>
+        <v>16.293</v>
       </c>
     </row>
     <row r="238">
@@ -11869,10 +11869,10 @@
         <v>1.01</v>
       </c>
       <c r="I238" t="n">
-        <v>0.0439</v>
+        <v>0.0296</v>
       </c>
       <c r="J238" t="n">
-        <v>1.317</v>
+        <v>0.888</v>
       </c>
     </row>
     <row r="239">
@@ -11909,10 +11909,10 @@
         <v>0.9</v>
       </c>
       <c r="I239" t="n">
-        <v>-0.1464</v>
+        <v>-0.1269</v>
       </c>
       <c r="J239" t="n">
-        <v>-4.392</v>
+        <v>-3.807</v>
       </c>
     </row>
     <row r="240">
@@ -11949,10 +11949,10 @@
         <v>0.88</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.1688</v>
+        <v>-0.1485</v>
       </c>
       <c r="J240" t="n">
-        <v>-5.064</v>
+        <v>-4.455</v>
       </c>
     </row>
     <row r="241">
@@ -11989,10 +11989,10 @@
         <v>0.87</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.1797</v>
+        <v>-0.1592</v>
       </c>
       <c r="J241" t="n">
-        <v>-5.391</v>
+        <v>-4.776</v>
       </c>
     </row>
     <row r="242">
@@ -12029,10 +12029,10 @@
         <v>1.9</v>
       </c>
       <c r="I242" t="n">
-        <v>1.4124</v>
+        <v>1.4227</v>
       </c>
       <c r="J242" t="n">
-        <v>31.0728</v>
+        <v>31.2994</v>
       </c>
     </row>
     <row r="243">
@@ -12069,10 +12069,10 @@
         <v>1.84</v>
       </c>
       <c r="I243" t="n">
-        <v>1.3408</v>
+        <v>1.3459</v>
       </c>
       <c r="J243" t="n">
-        <v>29.4976</v>
+        <v>29.6098</v>
       </c>
     </row>
     <row r="244">
@@ -12109,10 +12109,10 @@
         <v>1.54</v>
       </c>
       <c r="I244" t="n">
-        <v>0.9698</v>
+        <v>0.9607</v>
       </c>
       <c r="J244" t="n">
-        <v>21.3356</v>
+        <v>21.1354</v>
       </c>
     </row>
     <row r="245">
@@ -12149,10 +12149,10 @@
         <v>1.07</v>
       </c>
       <c r="I245" t="n">
-        <v>0.1881</v>
+        <v>0.1567</v>
       </c>
       <c r="J245" t="n">
-        <v>4.1382</v>
+        <v>3.4474</v>
       </c>
     </row>
     <row r="246">
@@ -12189,10 +12189,10 @@
         <v>0.93</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.3368</v>
+        <v>-0.3044</v>
       </c>
       <c r="J246" t="n">
-        <v>-7.4096</v>
+        <v>-6.6968</v>
       </c>
     </row>
     <row r="247">
@@ -12229,10 +12229,10 @@
         <v>0.89</v>
       </c>
       <c r="I247" t="n">
-        <v>-0.1133</v>
+        <v>-0.0954</v>
       </c>
       <c r="J247" t="n">
-        <v>-2.4926</v>
+        <v>-2.0988</v>
       </c>
     </row>
     <row r="248">
@@ -12269,10 +12269,10 @@
         <v>0.73</v>
       </c>
       <c r="I248" t="n">
-        <v>-0.2852</v>
+        <v>-0.2724</v>
       </c>
       <c r="J248" t="n">
-        <v>-6.2744</v>
+        <v>-5.9928</v>
       </c>
     </row>
     <row r="249">
@@ -12309,10 +12309,10 @@
         <v>0.6</v>
       </c>
       <c r="I249" t="n">
-        <v>-0.4007</v>
+        <v>-0.3906</v>
       </c>
       <c r="J249" t="n">
-        <v>-8.8154</v>
+        <v>-8.5932</v>
       </c>
     </row>
     <row r="250">
@@ -12349,10 +12349,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.4359</v>
+        <v>-0.428</v>
       </c>
       <c r="J250" t="n">
-        <v>-9.5898</v>
+        <v>-9.416</v>
       </c>
     </row>
     <row r="251">
@@ -12389,10 +12389,10 @@
         <v>0.52</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.4711</v>
+        <v>-0.4662</v>
       </c>
       <c r="J251" t="n">
-        <v>-10.3642</v>
+        <v>-10.2564</v>
       </c>
     </row>
     <row r="252">
@@ -12429,10 +12429,10 @@
         <v>1.29</v>
       </c>
       <c r="I252" t="n">
-        <v>0.6887</v>
+        <v>0.6736</v>
       </c>
       <c r="J252" t="n">
-        <v>28.2367</v>
+        <v>27.6176</v>
       </c>
     </row>
     <row r="253">
@@ -12469,10 +12469,10 @@
         <v>1.23</v>
       </c>
       <c r="I253" t="n">
-        <v>0.592</v>
+        <v>0.5793</v>
       </c>
       <c r="J253" t="n">
-        <v>24.272</v>
+        <v>23.7513</v>
       </c>
     </row>
     <row r="254">
@@ -12509,10 +12509,10 @@
         <v>0.97</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.1405</v>
+        <v>-0.1112</v>
       </c>
       <c r="J254" t="n">
-        <v>-5.7605</v>
+        <v>-4.5592</v>
       </c>
     </row>
     <row r="255">
@@ -12549,10 +12549,10 @@
         <v>0.95</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.2057</v>
+        <v>-0.1701</v>
       </c>
       <c r="J255" t="n">
-        <v>-8.4337</v>
+        <v>-6.9741</v>
       </c>
     </row>
     <row r="256">
@@ -12589,10 +12589,10 @@
         <v>0.71</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.7937</v>
+        <v>-0.7684</v>
       </c>
       <c r="J256" t="n">
-        <v>-32.5417</v>
+        <v>-31.5044</v>
       </c>
     </row>
     <row r="257">
@@ -12629,10 +12629,10 @@
         <v>1.31</v>
       </c>
       <c r="I257" t="n">
-        <v>0.5725</v>
+        <v>0.5469000000000001</v>
       </c>
       <c r="J257" t="n">
-        <v>23.4725</v>
+        <v>22.4229</v>
       </c>
     </row>
     <row r="258">
@@ -12669,10 +12669,10 @@
         <v>1.2</v>
       </c>
       <c r="I258" t="n">
-        <v>0.4362</v>
+        <v>0.3816</v>
       </c>
       <c r="J258" t="n">
-        <v>17.8842</v>
+        <v>15.6456</v>
       </c>
     </row>
     <row r="259">
@@ -12709,10 +12709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I259" t="n">
-        <v>-0.0973</v>
+        <v>-0.081</v>
       </c>
       <c r="J259" t="n">
-        <v>-3.9893</v>
+        <v>-3.321</v>
       </c>
     </row>
     <row r="260">
@@ -12749,10 +12749,10 @@
         <v>0.88</v>
       </c>
       <c r="I260" t="n">
-        <v>-0.1674</v>
+        <v>-0.1473</v>
       </c>
       <c r="J260" t="n">
-        <v>-6.8634</v>
+        <v>-6.0393</v>
       </c>
     </row>
     <row r="261">
@@ -12789,10 +12789,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.4701</v>
+        <v>-0.4676</v>
       </c>
       <c r="J261" t="n">
-        <v>-19.2741</v>
+        <v>-19.1716</v>
       </c>
     </row>
     <row r="262">
@@ -12829,10 +12829,10 @@
         <v>1.81</v>
       </c>
       <c r="I262" t="n">
-        <v>1.3303</v>
+        <v>1.3352</v>
       </c>
       <c r="J262" t="n">
-        <v>30.5969</v>
+        <v>30.7096</v>
       </c>
     </row>
     <row r="263">
@@ -12869,10 +12869,10 @@
         <v>1.55</v>
       </c>
       <c r="I263" t="n">
-        <v>0.9996</v>
+        <v>0.9878</v>
       </c>
       <c r="J263" t="n">
-        <v>22.9908</v>
+        <v>22.7194</v>
       </c>
     </row>
     <row r="264">
@@ -12909,10 +12909,10 @@
         <v>1.33</v>
       </c>
       <c r="I264" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.6914</v>
       </c>
       <c r="J264" t="n">
-        <v>16.1253</v>
+        <v>15.9022</v>
       </c>
     </row>
     <row r="265">
@@ -12949,10 +12949,10 @@
         <v>1.26</v>
       </c>
       <c r="I265" t="n">
-        <v>0.5992</v>
+        <v>0.5938</v>
       </c>
       <c r="J265" t="n">
-        <v>13.7816</v>
+        <v>13.6574</v>
       </c>
     </row>
     <row r="266">
@@ -12989,10 +12989,10 @@
         <v>0.7</v>
       </c>
       <c r="I266" t="n">
-        <v>-0.8635</v>
+        <v>-0.8534</v>
       </c>
       <c r="J266" t="n">
-        <v>-19.8605</v>
+        <v>-19.6282</v>
       </c>
     </row>
     <row r="267">
@@ -13029,10 +13029,10 @@
         <v>0.91</v>
       </c>
       <c r="I267" t="n">
-        <v>-0.114</v>
+        <v>-0.0994</v>
       </c>
       <c r="J267" t="n">
-        <v>-2.622</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="268">
@@ -13069,10 +13069,10 @@
         <v>0.91</v>
       </c>
       <c r="I268" t="n">
-        <v>-0.114</v>
+        <v>-0.0994</v>
       </c>
       <c r="J268" t="n">
-        <v>-2.622</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="269">
@@ -13109,10 +13109,10 @@
         <v>0.84</v>
       </c>
       <c r="I269" t="n">
-        <v>-0.1925</v>
+        <v>-0.1763</v>
       </c>
       <c r="J269" t="n">
-        <v>-4.4275</v>
+        <v>-4.0549</v>
       </c>
     </row>
     <row r="270">
@@ -13149,10 +13149,10 @@
         <v>0.65</v>
       </c>
       <c r="I270" t="n">
-        <v>-0.3706</v>
+        <v>-0.357</v>
       </c>
       <c r="J270" t="n">
-        <v>-8.5238</v>
+        <v>-8.211</v>
       </c>
     </row>
     <row r="271">
@@ -13189,10 +13189,10 @@
         <v>0.58</v>
       </c>
       <c r="I271" t="n">
-        <v>-0.4331</v>
+        <v>-0.4245</v>
       </c>
       <c r="J271" t="n">
-        <v>-9.9613</v>
+        <v>-9.763500000000001</v>
       </c>
     </row>
     <row r="272">
@@ -13229,10 +13229,10 @@
         <v>0.85</v>
       </c>
       <c r="I272" t="n">
-        <v>-0.1653</v>
+        <v>-0.1492</v>
       </c>
       <c r="J272" t="n">
-        <v>-3.4713</v>
+        <v>-3.1332</v>
       </c>
     </row>
     <row r="273">
@@ -13269,10 +13269,10 @@
         <v>0.68</v>
       </c>
       <c r="I273" t="n">
-        <v>-0.3333</v>
+        <v>-0.3206</v>
       </c>
       <c r="J273" t="n">
-        <v>-6.9993</v>
+        <v>-6.7326</v>
       </c>
     </row>
     <row r="274">
@@ -13309,10 +13309,10 @@
         <v>0.67</v>
       </c>
       <c r="I274" t="n">
-        <v>-0.3419</v>
+        <v>-0.3293</v>
       </c>
       <c r="J274" t="n">
-        <v>-7.1799</v>
+        <v>-6.9153</v>
       </c>
     </row>
     <row r="275">
@@ -13349,10 +13349,10 @@
         <v>0.61</v>
       </c>
       <c r="I275" t="n">
-        <v>-0.3946</v>
+        <v>-0.3838</v>
       </c>
       <c r="J275" t="n">
-        <v>-8.2866</v>
+        <v>-8.059799999999999</v>
       </c>
     </row>
     <row r="276">
@@ -13389,10 +13389,10 @@
         <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>-0.4035</v>
+        <v>-0.3931</v>
       </c>
       <c r="J276" t="n">
-        <v>-8.4735</v>
+        <v>-8.255100000000001</v>
       </c>
     </row>
     <row r="277">
@@ -13429,10 +13429,10 @@
         <v>1.93</v>
       </c>
       <c r="I277" t="n">
-        <v>1.4483</v>
+        <v>1.4615</v>
       </c>
       <c r="J277" t="n">
-        <v>30.4143</v>
+        <v>30.6915</v>
       </c>
     </row>
     <row r="278">
@@ -13469,10 +13469,10 @@
         <v>1.85</v>
       </c>
       <c r="I278" t="n">
-        <v>1.3531</v>
+        <v>1.3591</v>
       </c>
       <c r="J278" t="n">
-        <v>28.4151</v>
+        <v>28.5411</v>
       </c>
     </row>
     <row r="279">
@@ -13509,10 +13509,10 @@
         <v>1.24</v>
       </c>
       <c r="I279" t="n">
-        <v>0.5552</v>
+        <v>0.5537</v>
       </c>
       <c r="J279" t="n">
-        <v>11.6592</v>
+        <v>11.6277</v>
       </c>
     </row>
     <row r="280">
@@ -13549,10 +13549,10 @@
         <v>1.19</v>
       </c>
       <c r="I280" t="n">
-        <v>0.4746</v>
+        <v>0.4579</v>
       </c>
       <c r="J280" t="n">
-        <v>9.9666</v>
+        <v>9.6159</v>
       </c>
     </row>
     <row r="281">
@@ -13589,10 +13589,10 @@
         <v>1.06</v>
       </c>
       <c r="I281" t="n">
-        <v>0.1593</v>
+        <v>0.1291</v>
       </c>
       <c r="J281" t="n">
-        <v>3.3453</v>
+        <v>2.7111</v>
       </c>
     </row>
     <row r="282">
@@ -13629,10 +13629,10 @@
         <v>0.9</v>
       </c>
       <c r="I282" t="n">
-        <v>-0.0934</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="J282" t="n">
-        <v>-1.7746</v>
+        <v>-1.3946</v>
       </c>
     </row>
     <row r="283">
@@ -13669,10 +13669,10 @@
         <v>0.82</v>
       </c>
       <c r="I283" t="n">
-        <v>-0.1872</v>
+        <v>-0.1706</v>
       </c>
       <c r="J283" t="n">
-        <v>-3.5568</v>
+        <v>-3.2414</v>
       </c>
     </row>
     <row r="284">
@@ -13709,10 +13709,10 @@
         <v>0.71</v>
       </c>
       <c r="I284" t="n">
-        <v>-0.3</v>
+        <v>-0.2882</v>
       </c>
       <c r="J284" t="n">
-        <v>-5.7</v>
+        <v>-5.4758</v>
       </c>
     </row>
     <row r="285">
@@ -13749,10 +13749,10 @@
         <v>0.4</v>
       </c>
       <c r="I285" t="n">
-        <v>-0.573</v>
+        <v>-0.5805</v>
       </c>
       <c r="J285" t="n">
-        <v>-10.887</v>
+        <v>-11.0295</v>
       </c>
     </row>
     <row r="286">
@@ -13789,10 +13789,10 @@
         <v>0.34</v>
       </c>
       <c r="I286" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.6417</v>
       </c>
       <c r="J286" t="n">
-        <v>-11.8845</v>
+        <v>-12.1923</v>
       </c>
     </row>
     <row r="287">
@@ -13829,10 +13829,10 @@
         <v>1.88</v>
       </c>
       <c r="I287" t="n">
-        <v>1.3852</v>
+        <v>1.3935</v>
       </c>
       <c r="J287" t="n">
-        <v>26.3188</v>
+        <v>26.4765</v>
       </c>
     </row>
     <row r="288">
@@ -13869,10 +13869,10 @@
         <v>1.54</v>
       </c>
       <c r="I288" t="n">
-        <v>0.968</v>
+        <v>0.9595</v>
       </c>
       <c r="J288" t="n">
-        <v>18.392</v>
+        <v>18.2305</v>
       </c>
     </row>
     <row r="289">
@@ -13909,10 +13909,10 @@
         <v>1.46</v>
       </c>
       <c r="I289" t="n">
-        <v>0.8663999999999999</v>
+        <v>0.8581</v>
       </c>
       <c r="J289" t="n">
-        <v>16.4616</v>
+        <v>16.3039</v>
       </c>
     </row>
     <row r="290">
@@ -13949,10 +13949,10 @@
         <v>1.42</v>
       </c>
       <c r="I290" t="n">
-        <v>0.8137</v>
+        <v>0.8061</v>
       </c>
       <c r="J290" t="n">
-        <v>15.4603</v>
+        <v>15.3159</v>
       </c>
     </row>
     <row r="291">
@@ -13989,10 +13989,10 @@
         <v>1.07</v>
       </c>
       <c r="I291" t="n">
-        <v>0.1855</v>
+        <v>0.1538</v>
       </c>
       <c r="J291" t="n">
-        <v>3.5245</v>
+        <v>2.9222</v>
       </c>
     </row>
     <row r="292">
@@ -14029,10 +14029,10 @@
         <v>1.07</v>
       </c>
       <c r="I292" t="n">
-        <v>0.153</v>
+        <v>0.1359</v>
       </c>
       <c r="J292" t="n">
-        <v>5.202</v>
+        <v>4.6206</v>
       </c>
     </row>
     <row r="293">
@@ -14069,10 +14069,10 @@
         <v>1.04</v>
       </c>
       <c r="I293" t="n">
-        <v>0.1001</v>
+        <v>0.0848</v>
       </c>
       <c r="J293" t="n">
-        <v>3.4034</v>
+        <v>2.8832</v>
       </c>
     </row>
     <row r="294">
@@ -14109,10 +14109,10 @@
         <v>1.03</v>
       </c>
       <c r="I294" t="n">
-        <v>0.08069999999999999</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="J294" t="n">
-        <v>2.7438</v>
+        <v>2.2644</v>
       </c>
     </row>
     <row r="295">
@@ -14149,10 +14149,10 @@
         <v>0.93</v>
       </c>
       <c r="I295" t="n">
-        <v>-0.1098</v>
+        <v>-0.0924</v>
       </c>
       <c r="J295" t="n">
-        <v>-3.7332</v>
+        <v>-3.1416</v>
       </c>
     </row>
     <row r="296">
@@ -14189,10 +14189,10 @@
         <v>0.82</v>
       </c>
       <c r="I296" t="n">
-        <v>-0.2304</v>
+        <v>-0.21</v>
       </c>
       <c r="J296" t="n">
-        <v>-7.8336</v>
+        <v>-7.14</v>
       </c>
     </row>
     <row r="297">
@@ -14229,10 +14229,10 @@
         <v>1.32</v>
       </c>
       <c r="I297" t="n">
-        <v>0.4465</v>
+        <v>0.3849</v>
       </c>
       <c r="J297" t="n">
-        <v>15.181</v>
+        <v>13.0866</v>
       </c>
     </row>
     <row r="298">
@@ -14269,10 +14269,10 @@
         <v>1.19</v>
       </c>
       <c r="I298" t="n">
-        <v>0.2973</v>
+        <v>0.2424</v>
       </c>
       <c r="J298" t="n">
-        <v>10.1082</v>
+        <v>8.2416</v>
       </c>
     </row>
     <row r="299">
@@ -14309,10 +14309,10 @@
         <v>1.01</v>
       </c>
       <c r="I299" t="n">
-        <v>0.0257</v>
+        <v>0.017</v>
       </c>
       <c r="J299" t="n">
-        <v>0.8738</v>
+        <v>0.578</v>
       </c>
     </row>
     <row r="300">
@@ -14349,10 +14349,10 @@
         <v>0.98</v>
       </c>
       <c r="I300" t="n">
-        <v>-0.0489</v>
+        <v>-0.0371</v>
       </c>
       <c r="J300" t="n">
-        <v>-1.6626</v>
+        <v>-1.2614</v>
       </c>
     </row>
     <row r="301">
@@ -14389,10 +14389,10 @@
         <v>0.92</v>
       </c>
       <c r="I301" t="n">
-        <v>-0.1307</v>
+        <v>-0.1115</v>
       </c>
       <c r="J301" t="n">
-        <v>-4.4438</v>
+        <v>-3.791</v>
       </c>
     </row>
     <row r="302">
@@ -14429,10 +14429,10 @@
         <v>1.17</v>
       </c>
       <c r="I302" t="n">
-        <v>0.4786</v>
+        <v>0.453</v>
       </c>
       <c r="J302" t="n">
-        <v>13.8794</v>
+        <v>13.137</v>
       </c>
     </row>
     <row r="303">
@@ -14469,10 +14469,10 @@
         <v>1.15</v>
       </c>
       <c r="I303" t="n">
-        <v>0.4422</v>
+        <v>0.4062</v>
       </c>
       <c r="J303" t="n">
-        <v>12.8238</v>
+        <v>11.7798</v>
       </c>
     </row>
     <row r="304">
@@ -14509,10 +14509,10 @@
         <v>1.13</v>
       </c>
       <c r="I304" t="n">
-        <v>0.3981</v>
+        <v>0.359</v>
       </c>
       <c r="J304" t="n">
-        <v>11.5449</v>
+        <v>10.411</v>
       </c>
     </row>
     <row r="305">
@@ -14549,10 +14549,10 @@
         <v>1.09</v>
       </c>
       <c r="I305" t="n">
-        <v>0.2988</v>
+        <v>0.2628</v>
       </c>
       <c r="J305" t="n">
-        <v>8.6652</v>
+        <v>7.6212</v>
       </c>
     </row>
     <row r="306">
@@ -14589,10 +14589,10 @@
         <v>0.96</v>
       </c>
       <c r="I306" t="n">
-        <v>-0.1871</v>
+        <v>-0.1526</v>
       </c>
       <c r="J306" t="n">
-        <v>-5.4259</v>
+        <v>-4.4254</v>
       </c>
     </row>
     <row r="307">
@@ -14629,10 +14629,10 @@
         <v>1.29</v>
       </c>
       <c r="I307" t="n">
-        <v>0.5521</v>
+        <v>0.5266</v>
       </c>
       <c r="J307" t="n">
-        <v>16.0109</v>
+        <v>15.2714</v>
       </c>
     </row>
     <row r="308">
@@ -14669,10 +14669,10 @@
         <v>1.03</v>
       </c>
       <c r="I308" t="n">
-        <v>0.1052</v>
+        <v>0.0774</v>
       </c>
       <c r="J308" t="n">
-        <v>3.0508</v>
+        <v>2.2446</v>
       </c>
     </row>
     <row r="309">
@@ -14709,10 +14709,10 @@
         <v>0.86</v>
       </c>
       <c r="I309" t="n">
-        <v>-0.1877</v>
+        <v>-0.1673</v>
       </c>
       <c r="J309" t="n">
-        <v>-5.4433</v>
+        <v>-4.8517</v>
       </c>
     </row>
     <row r="310">
@@ -14749,10 +14749,10 @@
         <v>0.84</v>
       </c>
       <c r="I310" t="n">
-        <v>-0.2086</v>
+        <v>-0.1881</v>
       </c>
       <c r="J310" t="n">
-        <v>-6.0494</v>
+        <v>-5.4549</v>
       </c>
     </row>
     <row r="311">
@@ -14789,10 +14789,10 @@
         <v>0.8</v>
       </c>
       <c r="I311" t="n">
-        <v>-0.2491</v>
+        <v>-0.2291</v>
       </c>
       <c r="J311" t="n">
-        <v>-7.2239</v>
+        <v>-6.6439</v>
       </c>
     </row>
     <row r="312">
@@ -14829,10 +14829,10 @@
         <v>1.28</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6594</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="J312" t="n">
-        <v>19.782</v>
+        <v>19.341</v>
       </c>
     </row>
     <row r="313">
@@ -14869,10 +14869,10 @@
         <v>1.18</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4971</v>
+        <v>0.4774</v>
       </c>
       <c r="J313" t="n">
-        <v>14.913</v>
+        <v>14.322</v>
       </c>
     </row>
     <row r="314">
@@ -14909,10 +14909,10 @@
         <v>1.13</v>
       </c>
       <c r="I314" t="n">
-        <v>0.3997</v>
+        <v>0.36</v>
       </c>
       <c r="J314" t="n">
-        <v>11.991</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="315">
@@ -14949,10 +14949,10 @@
         <v>1.07</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2461</v>
+        <v>0.2125</v>
       </c>
       <c r="J315" t="n">
-        <v>7.383</v>
+        <v>6.375</v>
       </c>
     </row>
     <row r="316">
@@ -14989,10 +14989,10 @@
         <v>0.79</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.6284999999999999</v>
+        <v>-0.5924</v>
       </c>
       <c r="J316" t="n">
-        <v>-18.855</v>
+        <v>-17.772</v>
       </c>
     </row>
     <row r="317">
@@ -15029,10 +15029,10 @@
         <v>1.41</v>
       </c>
       <c r="I317" t="n">
-        <v>0.6743</v>
+        <v>0.6422</v>
       </c>
       <c r="J317" t="n">
-        <v>20.229</v>
+        <v>19.266</v>
       </c>
     </row>
     <row r="318">
@@ -15069,10 +15069,10 @@
         <v>1.4</v>
       </c>
       <c r="I318" t="n">
-        <v>0.6633</v>
+        <v>0.6317</v>
       </c>
       <c r="J318" t="n">
-        <v>19.899</v>
+        <v>18.951</v>
       </c>
     </row>
     <row r="319">
@@ -15109,10 +15109,10 @@
         <v>1.07</v>
       </c>
       <c r="I319" t="n">
-        <v>0.1875</v>
+        <v>0.1488</v>
       </c>
       <c r="J319" t="n">
-        <v>5.625</v>
+        <v>4.464</v>
       </c>
     </row>
     <row r="320">
@@ -15149,10 +15149,10 @@
         <v>0.74</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.3129</v>
+        <v>-0.2959</v>
       </c>
       <c r="J320" t="n">
-        <v>-9.387</v>
+        <v>-8.877000000000001</v>
       </c>
     </row>
     <row r="321">
@@ -15189,10 +15189,10 @@
         <v>0.52</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.5081</v>
+        <v>-0.5112</v>
       </c>
       <c r="J321" t="n">
-        <v>-15.243</v>
+        <v>-15.336</v>
       </c>
     </row>
     <row r="322">
@@ -15229,10 +15229,10 @@
         <v>1.35</v>
       </c>
       <c r="I322" t="n">
-        <v>0.4651</v>
+        <v>0.4075</v>
       </c>
       <c r="J322" t="n">
-        <v>13.4879</v>
+        <v>11.8175</v>
       </c>
     </row>
     <row r="323">
@@ -15269,10 +15269,10 @@
         <v>1.28</v>
       </c>
       <c r="I323" t="n">
-        <v>0.3964</v>
+        <v>0.334</v>
       </c>
       <c r="J323" t="n">
-        <v>11.4956</v>
+        <v>9.686</v>
       </c>
     </row>
     <row r="324">
@@ -15309,10 +15309,10 @@
         <v>1.09</v>
       </c>
       <c r="I324" t="n">
-        <v>0.1603</v>
+        <v>0.1248</v>
       </c>
       <c r="J324" t="n">
-        <v>4.6487</v>
+        <v>3.6192</v>
       </c>
     </row>
     <row r="325">
@@ -15349,10 +15349,10 @@
         <v>1.03</v>
       </c>
       <c r="I325" t="n">
-        <v>0.0621</v>
+        <v>0.0445</v>
       </c>
       <c r="J325" t="n">
-        <v>1.8009</v>
+        <v>1.2905</v>
       </c>
     </row>
     <row r="326">
@@ -15389,10 +15389,10 @@
         <v>0.99</v>
       </c>
       <c r="I326" t="n">
-        <v>-0.0361</v>
+        <v>-0.0268</v>
       </c>
       <c r="J326" t="n">
-        <v>-1.0469</v>
+        <v>-0.7772</v>
       </c>
     </row>
     <row r="327">
@@ -15429,10 +15429,10 @@
         <v>1.01</v>
       </c>
       <c r="I327" t="n">
-        <v>0.0396</v>
+        <v>0.0298</v>
       </c>
       <c r="J327" t="n">
-        <v>1.1484</v>
+        <v>0.8642</v>
       </c>
     </row>
     <row r="328">
@@ -15469,10 +15469,10 @@
         <v>1</v>
       </c>
       <c r="I328" t="n">
-        <v>0.0051</v>
+        <v>0.0033</v>
       </c>
       <c r="J328" t="n">
-        <v>0.1479</v>
+        <v>0.09569999999999999</v>
       </c>
     </row>
     <row r="329">
@@ -15509,10 +15509,10 @@
         <v>0.99</v>
       </c>
       <c r="I329" t="n">
-        <v>-0.0219</v>
+        <v>-0.0163</v>
       </c>
       <c r="J329" t="n">
-        <v>-0.6351</v>
+        <v>-0.4727</v>
       </c>
     </row>
     <row r="330">
@@ -15549,10 +15549,10 @@
         <v>0.9</v>
       </c>
       <c r="I330" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J330" t="n">
-        <v>-4.1296</v>
+        <v>-3.5873</v>
       </c>
     </row>
     <row r="331">
@@ -15589,10 +15589,10 @@
         <v>0.83</v>
       </c>
       <c r="I331" t="n">
-        <v>-0.2172</v>
+        <v>-0.1969</v>
       </c>
       <c r="J331" t="n">
-        <v>-6.2988</v>
+        <v>-5.7101</v>
       </c>
     </row>
     <row r="332">
@@ -15629,10 +15629,10 @@
         <v>1.13</v>
       </c>
       <c r="I332" t="n">
-        <v>0.3437</v>
+        <v>0.2926</v>
       </c>
       <c r="J332" t="n">
-        <v>8.936199999999999</v>
+        <v>7.6076</v>
       </c>
     </row>
     <row r="333">
@@ -15669,10 +15669,10 @@
         <v>1.03</v>
       </c>
       <c r="I333" t="n">
-        <v>0.1257</v>
+        <v>0.0953</v>
       </c>
       <c r="J333" t="n">
-        <v>3.2682</v>
+        <v>2.4778</v>
       </c>
     </row>
     <row r="334">
@@ -15709,10 +15709,10 @@
         <v>0.79</v>
       </c>
       <c r="I334" t="n">
-        <v>-0.2497</v>
+        <v>-0.2305</v>
       </c>
       <c r="J334" t="n">
-        <v>-6.4922</v>
+        <v>-5.993</v>
       </c>
     </row>
     <row r="335">
@@ -15749,10 +15749,10 @@
         <v>0.7</v>
       </c>
       <c r="I335" t="n">
-        <v>-0.3349</v>
+        <v>-0.3187</v>
       </c>
       <c r="J335" t="n">
-        <v>-8.7074</v>
+        <v>-8.286199999999999</v>
       </c>
     </row>
     <row r="336">
@@ -15789,10 +15789,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I336" t="n">
-        <v>-0.3441</v>
+        <v>-0.3285</v>
       </c>
       <c r="J336" t="n">
-        <v>-8.9466</v>
+        <v>-8.541</v>
       </c>
     </row>
     <row r="337">
@@ -15829,10 +15829,10 @@
         <v>1.37</v>
       </c>
       <c r="I337" t="n">
-        <v>0.7729</v>
+        <v>0.7577</v>
       </c>
       <c r="J337" t="n">
-        <v>20.0954</v>
+        <v>19.7002</v>
       </c>
     </row>
     <row r="338">
@@ -15869,10 +15869,10 @@
         <v>1.34</v>
       </c>
       <c r="I338" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7148</v>
       </c>
       <c r="J338" t="n">
-        <v>18.9618</v>
+        <v>18.5848</v>
       </c>
     </row>
     <row r="339">
@@ -15909,10 +15909,10 @@
         <v>1.25</v>
       </c>
       <c r="I339" t="n">
-        <v>0.5945</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="J339" t="n">
-        <v>15.457</v>
+        <v>15.2152</v>
       </c>
     </row>
     <row r="340">
@@ -15949,10 +15949,10 @@
         <v>1.14</v>
       </c>
       <c r="I340" t="n">
-        <v>0.4087</v>
+        <v>0.3748</v>
       </c>
       <c r="J340" t="n">
-        <v>10.6262</v>
+        <v>9.7448</v>
       </c>
     </row>
     <row r="341">
@@ -15989,10 +15989,10 @@
         <v>0.93</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.2982</v>
+        <v>-0.2589</v>
       </c>
       <c r="J341" t="n">
-        <v>-7.7532</v>
+        <v>-6.7314</v>
       </c>
     </row>
     <row r="342">
@@ -16029,10 +16029,10 @@
         <v>1.04</v>
       </c>
       <c r="I342" t="n">
-        <v>0.1502</v>
+        <v>0.116</v>
       </c>
       <c r="J342" t="n">
-        <v>3.9052</v>
+        <v>3.016</v>
       </c>
     </row>
     <row r="343">
@@ -16069,10 +16069,10 @@
         <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>0.0211</v>
+        <v>0.0158</v>
       </c>
       <c r="J343" t="n">
-        <v>0.5486</v>
+        <v>0.4108</v>
       </c>
     </row>
     <row r="344">
@@ -16109,10 +16109,10 @@
         <v>0.87</v>
       </c>
       <c r="I344" t="n">
-        <v>-0.1697</v>
+        <v>-0.1516</v>
       </c>
       <c r="J344" t="n">
-        <v>-4.4122</v>
+        <v>-3.9416</v>
       </c>
     </row>
     <row r="345">
@@ -16149,10 +16149,10 @@
         <v>0.86</v>
       </c>
       <c r="I345" t="n">
-        <v>-0.18</v>
+        <v>-0.1615</v>
       </c>
       <c r="J345" t="n">
-        <v>-4.68</v>
+        <v>-4.199</v>
       </c>
     </row>
     <row r="346">
@@ -16189,10 +16189,10 @@
         <v>0.59</v>
       </c>
       <c r="I346" t="n">
-        <v>-0.4344</v>
+        <v>-0.4265</v>
       </c>
       <c r="J346" t="n">
-        <v>-11.2944</v>
+        <v>-11.089</v>
       </c>
     </row>
     <row r="347">
@@ -16229,10 +16229,10 @@
         <v>1.66</v>
       </c>
       <c r="I347" t="n">
-        <v>1.1722</v>
+        <v>1.1684</v>
       </c>
       <c r="J347" t="n">
-        <v>30.4772</v>
+        <v>30.3784</v>
       </c>
     </row>
     <row r="348">
@@ -16269,10 +16269,10 @@
         <v>1.11</v>
       </c>
       <c r="I348" t="n">
-        <v>0.3363</v>
+        <v>0.3029</v>
       </c>
       <c r="J348" t="n">
-        <v>8.7438</v>
+        <v>7.8754</v>
       </c>
     </row>
     <row r="349">
@@ -16309,10 +16309,10 @@
         <v>1.11</v>
       </c>
       <c r="I349" t="n">
-        <v>0.3363</v>
+        <v>0.3029</v>
       </c>
       <c r="J349" t="n">
-        <v>8.7438</v>
+        <v>7.8754</v>
       </c>
     </row>
     <row r="350">
@@ -16349,10 +16349,10 @@
         <v>1.08</v>
       </c>
       <c r="I350" t="n">
-        <v>0.257</v>
+        <v>0.226</v>
       </c>
       <c r="J350" t="n">
-        <v>6.682</v>
+        <v>5.876</v>
       </c>
     </row>
     <row r="351">
@@ -16389,10 +16389,10 @@
         <v>1.03</v>
       </c>
       <c r="I351" t="n">
-        <v>0.1045</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J351" t="n">
-        <v>2.717</v>
+        <v>2.184</v>
       </c>
     </row>
   </sheetData>
